--- a/数据/水稻点位148.xlsx
+++ b/数据/水稻点位148.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Codes\Mission\agricultural-decision-system\数据\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2B8229-E8CE-4F79-86C5-E1DE626BE09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9420"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原始数据" sheetId="1" r:id="rId1"/>
     <sheet name="均值" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -98,7 +103,6 @@
         <b/>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
       </rPr>
       <t>Cd</t>
     </r>
@@ -111,7 +115,6 @@
       <rPr>
         <sz val="10"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
       </rPr>
       <t>Cd</t>
     </r>
@@ -630,14 +633,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -648,24 +645,17 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -673,151 +663,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -830,194 +687,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1025,251 +696,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1280,76 +709,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1636,19 +1021,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA151"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="27" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="1" max="27" width="9.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1731,7 +1116,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>62</v>
       </c>
@@ -1739,7 +1124,7 @@
         <v>112.9365</v>
       </c>
       <c r="C2" s="3">
-        <v>27.4716</v>
+        <v>27.471599999999999</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>27</v>
@@ -1772,19 +1157,19 @@
         <v>32</v>
       </c>
       <c r="N2" s="3">
-        <v>0.498229652643</v>
+        <v>0.49822965264300001</v>
       </c>
       <c r="O2" s="3">
-        <v>0.942270696163</v>
+        <v>0.94227069616299997</v>
       </c>
       <c r="P2" s="3">
-        <v>863.929138184</v>
+        <v>863.92913818399995</v>
       </c>
       <c r="Q2" s="3">
         <v>10.2679729462</v>
       </c>
       <c r="R2" s="3">
-        <v>271.196868896</v>
+        <v>271.19686889600001</v>
       </c>
       <c r="S2" s="3">
         <v>321.2684021</v>
@@ -1799,13 +1184,13 @@
         <v>0.6819075</v>
       </c>
       <c r="W2" s="3">
-        <v>230.0185</v>
+        <v>230.01849999999999</v>
       </c>
       <c r="X2" s="3">
-        <v>175.1159</v>
+        <v>175.11590000000001</v>
       </c>
       <c r="Y2" s="3">
-        <v>0.338351011276245</v>
+        <v>0.33835101127624501</v>
       </c>
       <c r="Z2" s="1">
         <v>1</v>
@@ -1814,15 +1199,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>63</v>
       </c>
       <c r="B3" s="3">
-        <v>112.894</v>
+        <v>112.89400000000001</v>
       </c>
       <c r="C3" s="3">
-        <v>27.4501</v>
+        <v>27.450099999999999</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -1867,13 +1252,13 @@
         <v>10.564</v>
       </c>
       <c r="R3" s="3">
-        <v>269.203</v>
+        <v>269.20299999999997</v>
       </c>
       <c r="S3" s="3">
         <v>213</v>
       </c>
       <c r="T3" s="3">
-        <v>22.774</v>
+        <v>22.774000000000001</v>
       </c>
       <c r="U3" s="3">
         <v>0.15</v>
@@ -1885,10 +1270,10 @@
         <v>143</v>
       </c>
       <c r="X3" s="3">
-        <v>176.3894</v>
+        <v>176.38939999999999</v>
       </c>
       <c r="Y3" s="3">
-        <v>0.281450986862183</v>
+        <v>0.28145098686218301</v>
       </c>
       <c r="Z3" s="1">
         <v>0.82</v>
@@ -1897,7 +1282,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>64</v>
       </c>
@@ -1905,7 +1290,7 @@
         <v>112.8526</v>
       </c>
       <c r="C4" s="3">
-        <v>27.4783</v>
+        <v>27.478300000000001</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>30</v>
@@ -1938,40 +1323,40 @@
         <v>30</v>
       </c>
       <c r="N4" s="3">
-        <v>0.49080696702</v>
+        <v>0.49080696701999998</v>
       </c>
       <c r="O4" s="3">
-        <v>1.04740357399</v>
+        <v>1.0474035739900001</v>
       </c>
       <c r="P4" s="3">
-        <v>1047.66845703</v>
+        <v>1047.6684570299999</v>
       </c>
       <c r="Q4" s="3">
-        <v>10.8621721268</v>
+        <v>10.862172126800001</v>
       </c>
       <c r="R4" s="3">
-        <v>261.878540039</v>
+        <v>261.87854003899997</v>
       </c>
       <c r="S4" s="3">
         <v>292.833892822</v>
       </c>
       <c r="T4" s="3">
-        <v>25.0118694305</v>
+        <v>25.011869430499999</v>
       </c>
       <c r="U4" s="3">
         <v>0.16</v>
       </c>
       <c r="V4" s="3">
-        <v>0.5424837</v>
+        <v>0.54248370000000001</v>
       </c>
       <c r="W4" s="3">
-        <v>338.0825</v>
+        <v>338.08249999999998</v>
       </c>
       <c r="X4" s="3">
-        <v>193.6333</v>
+        <v>193.63329999999999</v>
       </c>
       <c r="Y4" s="3">
-        <v>0.270184010267258</v>
+        <v>0.27018401026725802</v>
       </c>
       <c r="Z4" s="1">
         <v>0.01</v>
@@ -1980,12 +1365,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>65</v>
       </c>
       <c r="B5" s="3">
-        <v>112.9124</v>
+        <v>112.91240000000001</v>
       </c>
       <c r="C5" s="3">
         <v>27.4815</v>
@@ -2030,19 +1415,19 @@
         <v>799</v>
       </c>
       <c r="Q5" s="3">
-        <v>9.894</v>
+        <v>9.8940000000000001</v>
       </c>
       <c r="R5" s="3">
-        <v>279.547</v>
+        <v>279.54700000000003</v>
       </c>
       <c r="S5" s="3">
         <v>389</v>
       </c>
       <c r="T5" s="3">
-        <v>24.257</v>
+        <v>24.257000000000001</v>
       </c>
       <c r="U5" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="V5" s="3">
         <v>0.76</v>
@@ -2054,7 +1439,7 @@
         <v>165</v>
       </c>
       <c r="Y5" s="3">
-        <v>0.290040999650955</v>
+        <v>0.29004099965095498</v>
       </c>
       <c r="Z5" s="1">
         <v>0.47</v>
@@ -2063,15 +1448,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>66</v>
       </c>
       <c r="B6" s="3">
-        <v>112.9386</v>
+        <v>112.93859999999999</v>
       </c>
       <c r="C6" s="3">
-        <v>27.4779</v>
+        <v>27.477900000000002</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>32</v>
@@ -2104,13 +1489,13 @@
         <v>61</v>
       </c>
       <c r="N6" s="3">
-        <v>0.492896944284</v>
+        <v>0.49289694428399999</v>
       </c>
       <c r="O6" s="3">
-        <v>0.925150752068</v>
+        <v>0.92515075206800002</v>
       </c>
       <c r="P6" s="3">
-        <v>863.025817871</v>
+        <v>863.02581787099996</v>
       </c>
       <c r="Q6" s="3">
         <v>10.2485589981</v>
@@ -2119,34 +1504,34 @@
         <v>271.413330078</v>
       </c>
       <c r="S6" s="3">
-        <v>325.594268799</v>
+        <v>325.59426879900002</v>
       </c>
       <c r="T6" s="3">
-        <v>24.7742862701</v>
+        <v>24.774286270099999</v>
       </c>
       <c r="U6" s="3">
         <v>0.19</v>
       </c>
       <c r="V6" s="3">
-        <v>0.6793606</v>
+        <v>0.67936059999999998</v>
       </c>
       <c r="W6" s="3">
-        <v>237.0561</v>
+        <v>237.05609999999999</v>
       </c>
       <c r="X6" s="3">
         <v>175.7713</v>
       </c>
       <c r="Y6" s="3">
-        <v>0.768467009067535</v>
+        <v>0.76846700906753496</v>
       </c>
       <c r="Z6" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA6" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>139</v>
       </c>
@@ -2154,7 +1539,7 @@
         <v>112.8126</v>
       </c>
       <c r="C7" s="3">
-        <v>27.4091</v>
+        <v>27.409099999999999</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>33</v>
@@ -2187,19 +1572,19 @@
         <v>29</v>
       </c>
       <c r="N7" s="3">
-        <v>0.474022626877</v>
+        <v>0.47402262687699998</v>
       </c>
       <c r="O7" s="3">
-        <v>0.74544519186</v>
+        <v>0.74544519186000002</v>
       </c>
       <c r="P7" s="3">
-        <v>1131.30908203</v>
+        <v>1131.3090820299999</v>
       </c>
       <c r="Q7" s="3">
-        <v>11.7901058197</v>
+        <v>11.790105819700001</v>
       </c>
       <c r="R7" s="3">
-        <v>252.147064209</v>
+        <v>252.14706420900001</v>
       </c>
       <c r="S7" s="3">
         <v>271.571533203</v>
@@ -2211,16 +1596,16 @@
         <v>0.12</v>
       </c>
       <c r="V7" s="3">
-        <v>0.7437702</v>
+        <v>0.74377020000000005</v>
       </c>
       <c r="W7" s="3">
-        <v>386.8822</v>
+        <v>386.88220000000001</v>
       </c>
       <c r="X7" s="3">
         <v>196.739</v>
       </c>
       <c r="Y7" s="3">
-        <v>0.419780999422073</v>
+        <v>0.41978099942207298</v>
       </c>
       <c r="Z7" s="1">
         <v>0.01</v>
@@ -2229,7 +1614,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>140</v>
       </c>
@@ -2237,13 +1622,13 @@
         <v>112.790924</v>
       </c>
       <c r="C8" s="3">
-        <v>27.394529</v>
+        <v>27.394528999999999</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="3">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="F8" s="3">
         <v>57</v>
@@ -2273,37 +1658,37 @@
         <v>0.454064190388</v>
       </c>
       <c r="O8" s="3">
-        <v>0.784106850624</v>
+        <v>0.78410685062399998</v>
       </c>
       <c r="P8" s="3">
-        <v>1260.93762207</v>
+        <v>1260.9376220700001</v>
       </c>
       <c r="Q8" s="3">
-        <v>11.9998111725</v>
+        <v>11.999811172499999</v>
       </c>
       <c r="R8" s="3">
-        <v>252.181411743</v>
+        <v>252.18141174300001</v>
       </c>
       <c r="S8" s="3">
-        <v>310.011688232</v>
+        <v>310.01168823199998</v>
       </c>
       <c r="T8" s="3">
-        <v>26.7639942169</v>
+        <v>26.763994216899999</v>
       </c>
       <c r="U8" s="3">
-        <v>0.1371673</v>
+        <v>0.13716729999999999</v>
       </c>
       <c r="V8" s="3">
-        <v>0.6218191</v>
+        <v>0.62181909999999996</v>
       </c>
       <c r="W8" s="3">
         <v>494.6789</v>
       </c>
       <c r="X8" s="3">
-        <v>199.1168</v>
+        <v>199.11680000000001</v>
       </c>
       <c r="Y8" s="3">
-        <v>0.260594993829727</v>
+        <v>0.26059499382972701</v>
       </c>
       <c r="Z8" s="1">
         <v>0.39</v>
@@ -2312,7 +1697,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>141</v>
       </c>
@@ -2320,7 +1705,7 @@
         <v>112.8747</v>
       </c>
       <c r="C9" s="3">
-        <v>27.3941</v>
+        <v>27.394100000000002</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>36</v>
@@ -2353,7 +1738,7 @@
         <v>39</v>
       </c>
       <c r="N9" s="3">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O9" s="3">
         <v>0.7</v>
@@ -2362,7 +1747,7 @@
         <v>684</v>
       </c>
       <c r="Q9" s="3">
-        <v>11.152</v>
+        <v>11.151999999999999</v>
       </c>
       <c r="R9" s="3">
         <v>234.983</v>
@@ -2371,22 +1756,22 @@
         <v>133</v>
       </c>
       <c r="T9" s="3">
-        <v>33.281</v>
+        <v>33.280999999999999</v>
       </c>
       <c r="U9" s="3">
         <v>0.12</v>
       </c>
       <c r="V9" s="3">
-        <v>1.131981</v>
+        <v>1.1319809999999999</v>
       </c>
       <c r="W9" s="3">
-        <v>196.5302</v>
+        <v>196.53020000000001</v>
       </c>
       <c r="X9" s="3">
         <v>168</v>
       </c>
       <c r="Y9" s="3">
-        <v>0.280620008707047</v>
+        <v>0.28062000870704701</v>
       </c>
       <c r="Z9" s="1">
         <v>0.45</v>
@@ -2395,7 +1780,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>142</v>
       </c>
@@ -2403,7 +1788,7 @@
         <v>112.8575</v>
       </c>
       <c r="C10" s="3">
-        <v>27.3839</v>
+        <v>27.383900000000001</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>37</v>
@@ -2445,10 +1830,10 @@
         <v>1011</v>
       </c>
       <c r="Q10" s="3">
-        <v>12.046</v>
+        <v>12.045999999999999</v>
       </c>
       <c r="R10" s="3">
-        <v>256.881</v>
+        <v>256.88099999999997</v>
       </c>
       <c r="S10" s="3">
         <v>197</v>
@@ -2466,10 +1851,10 @@
         <v>162</v>
       </c>
       <c r="X10" s="3">
-        <v>171.588</v>
+        <v>171.58799999999999</v>
       </c>
       <c r="Y10" s="3">
-        <v>0.329374998807907</v>
+        <v>0.32937499880790699</v>
       </c>
       <c r="Z10" s="1">
         <v>0.53</v>
@@ -2478,15 +1863,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>143</v>
       </c>
       <c r="B11" s="3">
-        <v>112.912805</v>
+        <v>112.91280500000001</v>
       </c>
       <c r="C11" s="3">
-        <v>27.420666</v>
+        <v>27.420666000000001</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>38</v>
@@ -2519,7 +1904,7 @@
         <v>40</v>
       </c>
       <c r="N11" s="3">
-        <v>0.535905838013</v>
+        <v>0.53590583801299996</v>
       </c>
       <c r="O11" s="3">
         <v>1.04331564903</v>
@@ -2528,7 +1913,7 @@
         <v>882.124511719</v>
       </c>
       <c r="Q11" s="3">
-        <v>10.8305892944</v>
+        <v>10.830589294399999</v>
       </c>
       <c r="R11" s="3">
         <v>258.753173828</v>
@@ -2537,13 +1922,13 @@
         <v>227.229568481</v>
       </c>
       <c r="T11" s="3">
-        <v>26.3619766235</v>
+        <v>26.361976623499999</v>
       </c>
       <c r="U11" s="3">
-        <v>0.1594916</v>
+        <v>0.15949160000000001</v>
       </c>
       <c r="V11" s="3">
-        <v>0.7012441</v>
+        <v>0.70124410000000004</v>
       </c>
       <c r="W11" s="3">
         <v>222.7276</v>
@@ -2552,7 +1937,7 @@
         <v>179.8417</v>
       </c>
       <c r="Y11" s="3">
-        <v>0.399848014116287</v>
+        <v>0.39984801411628701</v>
       </c>
       <c r="Z11" s="1">
         <v>0.01</v>
@@ -2561,12 +1946,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>144</v>
       </c>
       <c r="B12" s="3">
-        <v>112.81785</v>
+        <v>112.81785000000001</v>
       </c>
       <c r="C12" s="3">
         <v>27.367321</v>
@@ -2575,7 +1960,7 @@
         <v>39</v>
       </c>
       <c r="E12" s="3">
-        <v>9.3</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F12" s="3">
         <v>54</v>
@@ -2605,7 +1990,7 @@
         <v>0.495559424162</v>
       </c>
       <c r="O12" s="3">
-        <v>0.624109148979</v>
+        <v>0.62410914897900005</v>
       </c>
       <c r="P12" s="3">
         <v>1074.08862305</v>
@@ -2614,10 +1999,10 @@
         <v>11.7596120834</v>
       </c>
       <c r="R12" s="3">
-        <v>253.112731934</v>
+        <v>253.11273193400001</v>
       </c>
       <c r="S12" s="3">
-        <v>240.488830566</v>
+        <v>240.48883056599999</v>
       </c>
       <c r="T12" s="3">
         <v>26.8234958649</v>
@@ -2626,16 +2011,16 @@
         <v>0.16</v>
       </c>
       <c r="V12" s="3">
-        <v>0.9328237</v>
+        <v>0.93282370000000003</v>
       </c>
       <c r="W12" s="3">
-        <v>310.2992</v>
+        <v>310.29919999999998</v>
       </c>
       <c r="X12" s="3">
         <v>187.2073</v>
       </c>
       <c r="Y12" s="3">
-        <v>0.240983992815018</v>
+        <v>0.24098399281501801</v>
       </c>
       <c r="Z12" s="1">
         <v>0.8</v>
@@ -2644,7 +2029,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>67</v>
       </c>
@@ -2685,22 +2070,22 @@
         <v>46</v>
       </c>
       <c r="N13" s="3">
-        <v>0.278109461069</v>
+        <v>0.27810946106899997</v>
       </c>
       <c r="O13" s="3">
-        <v>0.868572711945</v>
+        <v>0.86857271194499996</v>
       </c>
       <c r="P13" s="3">
         <v>1207.69799805</v>
       </c>
       <c r="Q13" s="3">
-        <v>11.9652299881</v>
+        <v>11.965229988100001</v>
       </c>
       <c r="R13" s="3">
-        <v>233.398300171</v>
+        <v>233.39830017099999</v>
       </c>
       <c r="S13" s="3">
-        <v>217.453140259</v>
+        <v>217.45314025900001</v>
       </c>
       <c r="T13" s="3">
         <v>20.6923961639</v>
@@ -2709,33 +2094,33 @@
         <v>0.15</v>
       </c>
       <c r="V13" s="3">
-        <v>0.177248</v>
+        <v>0.17724799999999999</v>
       </c>
       <c r="W13" s="3">
-        <v>200.2248</v>
+        <v>200.22479999999999</v>
       </c>
       <c r="X13" s="3">
         <v>180.2713</v>
       </c>
       <c r="Y13" s="3">
-        <v>0.294874012470245</v>
+        <v>0.29487401247024497</v>
       </c>
       <c r="Z13" s="1">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA13" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>68</v>
       </c>
       <c r="B14" s="3">
-        <v>112.55679</v>
+        <v>112.55679000000001</v>
       </c>
       <c r="C14" s="3">
-        <v>27.53282</v>
+        <v>27.532820000000001</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>42</v>
@@ -2762,7 +2147,7 @@
         <v>9.4</v>
       </c>
       <c r="L14" s="3">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M14" s="3">
         <v>40</v>
@@ -2771,10 +2156,10 @@
         <v>0.283606648445</v>
       </c>
       <c r="O14" s="3">
-        <v>0.942421317101</v>
+        <v>0.94242131710099997</v>
       </c>
       <c r="P14" s="3">
-        <v>1204.28015137</v>
+        <v>1204.2801513700001</v>
       </c>
       <c r="Q14" s="3">
         <v>11.8916292191</v>
@@ -2783,25 +2168,25 @@
         <v>237.628616333</v>
       </c>
       <c r="S14" s="3">
-        <v>216.759429932</v>
+        <v>216.75942993199999</v>
       </c>
       <c r="T14" s="3">
-        <v>20.0608997345</v>
+        <v>20.060899734500001</v>
       </c>
       <c r="U14" s="3">
         <v>0.1</v>
       </c>
       <c r="V14" s="3">
-        <v>0.1810276</v>
+        <v>0.18102760000000001</v>
       </c>
       <c r="W14" s="3">
-        <v>194.5747</v>
+        <v>194.57470000000001</v>
       </c>
       <c r="X14" s="3">
         <v>180.2835</v>
       </c>
       <c r="Y14" s="3">
-        <v>0.251821011304855</v>
+        <v>0.25182101130485501</v>
       </c>
       <c r="Z14" s="1">
         <v>0.49</v>
@@ -2810,7 +2195,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>69</v>
       </c>
@@ -2818,7 +2203,7 @@
         <v>112.55153</v>
       </c>
       <c r="C15" s="3">
-        <v>27.54742</v>
+        <v>27.547419999999999</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>43</v>
@@ -2851,7 +2236,7 @@
         <v>51</v>
       </c>
       <c r="N15" s="3">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O15" s="3">
         <v>0.93</v>
@@ -2863,7 +2248,7 @@
         <v>12.391</v>
       </c>
       <c r="R15" s="3">
-        <v>227.563</v>
+        <v>227.56299999999999</v>
       </c>
       <c r="S15" s="3">
         <v>228</v>
@@ -2872,7 +2257,7 @@
         <v>23.14</v>
       </c>
       <c r="U15" s="3">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="V15" s="3">
         <v>0.19</v>
@@ -2884,7 +2269,7 @@
         <v>184</v>
       </c>
       <c r="Y15" s="3">
-        <v>0.477629005908966</v>
+        <v>0.47762900590896601</v>
       </c>
       <c r="Z15" s="1">
         <v>0.24</v>
@@ -2893,7 +2278,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>70</v>
       </c>
@@ -2901,7 +2286,7 @@
         <v>112.50533</v>
       </c>
       <c r="C16" s="3">
-        <v>27.5588</v>
+        <v>27.558800000000002</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>44</v>
@@ -2934,25 +2319,25 @@
         <v>44</v>
       </c>
       <c r="N16" s="3">
-        <v>0.271506309509</v>
+        <v>0.27150630950900001</v>
       </c>
       <c r="O16" s="3">
-        <v>0.672897219658</v>
+        <v>0.67289721965799998</v>
       </c>
       <c r="P16" s="3">
-        <v>1488.39562988</v>
+        <v>1488.3956298799999</v>
       </c>
       <c r="Q16" s="3">
         <v>11.3330507278</v>
       </c>
       <c r="R16" s="3">
-        <v>233.343444824</v>
+        <v>233.34344482399999</v>
       </c>
       <c r="S16" s="3">
-        <v>208.312805176</v>
+        <v>208.31280517600001</v>
       </c>
       <c r="T16" s="3">
-        <v>19.6846103668</v>
+        <v>19.684610366800001</v>
       </c>
       <c r="U16" s="3">
         <v>0.1</v>
@@ -2961,13 +2346,13 @@
         <v>0.1412881</v>
       </c>
       <c r="W16" s="3">
-        <v>272.6989</v>
+        <v>272.69889999999998</v>
       </c>
       <c r="X16" s="3">
-        <v>172.5073</v>
+        <v>172.50729999999999</v>
       </c>
       <c r="Y16" s="3">
-        <v>0.389461010694504</v>
+        <v>0.38946101069450401</v>
       </c>
       <c r="Z16" s="1">
         <v>0.1</v>
@@ -2976,7 +2361,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>71</v>
       </c>
@@ -2984,7 +2369,7 @@
         <v>112.58108</v>
       </c>
       <c r="C17" s="3">
-        <v>27.5429</v>
+        <v>27.542899999999999</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>45</v>
@@ -3017,10 +2402,10 @@
         <v>42</v>
       </c>
       <c r="N17" s="3">
-        <v>0.295982658863</v>
+        <v>0.29598265886300001</v>
       </c>
       <c r="O17" s="3">
-        <v>0.915255308151</v>
+        <v>0.91525530815099998</v>
       </c>
       <c r="P17" s="3">
         <v>1285.93652344</v>
@@ -3032,25 +2417,25 @@
         <v>246.762649536</v>
       </c>
       <c r="S17" s="3">
-        <v>260.662780762</v>
+        <v>260.66278076200001</v>
       </c>
       <c r="T17" s="3">
         <v>19.7658920288</v>
       </c>
       <c r="U17" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="V17" s="3">
-        <v>0.1888999</v>
+        <v>0.18889990000000001</v>
       </c>
       <c r="W17" s="3">
-        <v>255.1811</v>
+        <v>255.18109999999999</v>
       </c>
       <c r="X17" s="3">
         <v>178.1876</v>
       </c>
       <c r="Y17" s="3">
-        <v>0.339866995811462</v>
+        <v>0.33986699581146201</v>
       </c>
       <c r="Z17" s="1">
         <v>0.61</v>
@@ -3059,7 +2444,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>72</v>
       </c>
@@ -3100,7 +2485,7 @@
         <v>44</v>
       </c>
       <c r="N18" s="3">
-        <v>0.291230231524</v>
+        <v>0.29123023152400002</v>
       </c>
       <c r="O18" s="3">
         <v>0.909933805466</v>
@@ -3109,40 +2494,40 @@
         <v>1184.51745605</v>
       </c>
       <c r="Q18" s="3">
-        <v>12.1554918289</v>
+        <v>12.155491828900001</v>
       </c>
       <c r="R18" s="3">
-        <v>234.649078369</v>
+        <v>234.64907836899999</v>
       </c>
       <c r="S18" s="3">
         <v>235.242279053</v>
       </c>
       <c r="T18" s="3">
-        <v>21.7741298676</v>
+        <v>21.774129867599999</v>
       </c>
       <c r="U18" s="3">
         <v>0.15</v>
       </c>
       <c r="V18" s="3">
-        <v>0.1877563</v>
+        <v>0.18775629999999999</v>
       </c>
       <c r="W18" s="3">
         <v>194.7655</v>
       </c>
       <c r="X18" s="3">
-        <v>182.0331</v>
+        <v>182.03309999999999</v>
       </c>
       <c r="Y18" s="3">
-        <v>0.379941999912262</v>
+        <v>0.37994199991226202</v>
       </c>
       <c r="Z18" s="1">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3156,7 +2541,7 @@
         <v>47</v>
       </c>
       <c r="E19" s="3">
-        <v>16.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="F19" s="3">
         <v>72</v>
@@ -3177,46 +2562,46 @@
         <v>11</v>
       </c>
       <c r="L19" s="3">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M19" s="3">
         <v>34</v>
       </c>
       <c r="N19" s="3">
-        <v>0.731700479984</v>
+        <v>0.73170047998400001</v>
       </c>
       <c r="O19" s="3">
-        <v>1.0211327076</v>
+        <v>1.0211327076000001</v>
       </c>
       <c r="P19" s="3">
-        <v>1479.95776367</v>
+        <v>1479.9577636700001</v>
       </c>
       <c r="Q19" s="3">
-        <v>9.7571105957</v>
+        <v>9.7571105957000004</v>
       </c>
       <c r="R19" s="3">
-        <v>247.611312866</v>
+        <v>247.61131286599999</v>
       </c>
       <c r="S19" s="3">
-        <v>2345.53613281</v>
+        <v>2345.5361328099998</v>
       </c>
       <c r="T19" s="3">
-        <v>24.1873397827</v>
+        <v>24.187339782700001</v>
       </c>
       <c r="U19" s="3">
-        <v>0.1558888</v>
+        <v>0.15588879999999999</v>
       </c>
       <c r="V19" s="3">
-        <v>0.2530769</v>
+        <v>0.25307689999999999</v>
       </c>
       <c r="W19" s="3">
-        <v>252.5175</v>
+        <v>252.51750000000001</v>
       </c>
       <c r="X19" s="3">
-        <v>394.0714</v>
+        <v>394.07139999999998</v>
       </c>
       <c r="Y19" s="3">
-        <v>0.507022023200989</v>
+        <v>0.50702202320098899</v>
       </c>
       <c r="Z19" s="1">
         <v>0.91</v>
@@ -3225,7 +2610,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>2</v>
       </c>
@@ -3233,7 +2618,7 @@
         <v>112.8142</v>
       </c>
       <c r="C20" s="3">
-        <v>27.7067</v>
+        <v>27.706700000000001</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>49</v>
@@ -3266,7 +2651,7 @@
         <v>39</v>
       </c>
       <c r="N20" s="3">
-        <v>0.688992381096</v>
+        <v>0.68899238109600003</v>
       </c>
       <c r="O20" s="3">
         <v>0.41</v>
@@ -3275,10 +2660,10 @@
         <v>2054</v>
       </c>
       <c r="Q20" s="3">
-        <v>6.789</v>
+        <v>6.7889999999999997</v>
       </c>
       <c r="R20" s="3">
-        <v>258.723</v>
+        <v>258.72300000000001</v>
       </c>
       <c r="S20" s="3">
         <v>796</v>
@@ -3287,19 +2672,19 @@
         <v>15.827</v>
       </c>
       <c r="U20" s="3">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="V20" s="3">
-        <v>0.3017502</v>
+        <v>0.30175020000000002</v>
       </c>
       <c r="W20" s="3">
-        <v>419.2909</v>
+        <v>419.29090000000002</v>
       </c>
       <c r="X20" s="3">
         <v>156</v>
       </c>
       <c r="Y20" s="3">
-        <v>0.320836991071701</v>
+        <v>0.32083699107170099</v>
       </c>
       <c r="Z20" s="1">
         <v>0.34</v>
@@ -3308,7 +2693,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>3</v>
       </c>
@@ -3316,7 +2701,7 @@
         <v>112.8327</v>
       </c>
       <c r="C21" s="3">
-        <v>27.7268</v>
+        <v>27.726800000000001</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>50</v>
@@ -3349,31 +2734,31 @@
         <v>37</v>
       </c>
       <c r="N21" s="3">
-        <v>0.672700285912</v>
+        <v>0.67270028591200004</v>
       </c>
       <c r="O21" s="3">
-        <v>0.717199981213</v>
+        <v>0.71719998121299999</v>
       </c>
       <c r="P21" s="3">
         <v>1487.8671875</v>
       </c>
       <c r="Q21" s="3">
-        <v>8.61822319031</v>
+        <v>8.6182231903099993</v>
       </c>
       <c r="R21" s="3">
-        <v>260.803436279</v>
+        <v>260.80343627899998</v>
       </c>
       <c r="S21" s="3">
-        <v>932.813781738</v>
+        <v>932.81378173799999</v>
       </c>
       <c r="T21" s="3">
-        <v>21.2116775513</v>
+        <v>21.211677551299999</v>
       </c>
       <c r="U21" s="3">
         <v>0.12</v>
       </c>
       <c r="V21" s="3">
-        <v>0.2885135</v>
+        <v>0.28851349999999998</v>
       </c>
       <c r="W21" s="3">
         <v>350.8</v>
@@ -3382,7 +2767,7 @@
         <v>255.5771</v>
       </c>
       <c r="Y21" s="3">
-        <v>0.310907006263733</v>
+        <v>0.31090700626373302</v>
       </c>
       <c r="Z21" s="1">
         <v>2</v>
@@ -3391,7 +2776,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>4</v>
       </c>
@@ -3399,7 +2784,7 @@
         <v>112.872882</v>
       </c>
       <c r="C22" s="3">
-        <v>27.800226</v>
+        <v>27.800225999999999</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>51</v>
@@ -3441,7 +2826,7 @@
         <v>1829</v>
       </c>
       <c r="Q22" s="3">
-        <v>10.069</v>
+        <v>10.069000000000001</v>
       </c>
       <c r="R22" s="3">
         <v>218.917</v>
@@ -3474,7 +2859,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>5</v>
       </c>
@@ -3482,7 +2867,7 @@
         <v>112.8291</v>
       </c>
       <c r="C23" s="3">
-        <v>27.7479</v>
+        <v>27.747900000000001</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>52</v>
@@ -3515,40 +2900,40 @@
         <v>43</v>
       </c>
       <c r="N23" s="3">
-        <v>0.685625374317</v>
+        <v>0.68562537431699999</v>
       </c>
       <c r="O23" s="3">
-        <v>0.819753229618</v>
+        <v>0.81975322961800001</v>
       </c>
       <c r="P23" s="3">
-        <v>1413.89111328</v>
+        <v>1413.8911132799999</v>
       </c>
       <c r="Q23" s="3">
-        <v>9.32238960266</v>
+        <v>9.3223896026599995</v>
       </c>
       <c r="R23" s="3">
-        <v>259.11138916</v>
+        <v>259.11138915999999</v>
       </c>
       <c r="S23" s="3">
         <v>1224.52832031</v>
       </c>
       <c r="T23" s="3">
-        <v>22.0056667328</v>
+        <v>22.005666732800002</v>
       </c>
       <c r="U23" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="V23" s="3">
         <v>0.2793968</v>
       </c>
       <c r="W23" s="3">
-        <v>290.0029</v>
+        <v>290.00290000000001</v>
       </c>
       <c r="X23" s="3">
-        <v>285.2007</v>
+        <v>285.20069999999998</v>
       </c>
       <c r="Y23" s="3">
-        <v>0.397410005331039</v>
+        <v>0.39741000533103898</v>
       </c>
       <c r="Z23" s="1">
         <v>0.42</v>
@@ -3557,7 +2942,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>6</v>
       </c>
@@ -3565,7 +2950,7 @@
         <v>112.7911</v>
       </c>
       <c r="C24" s="3">
-        <v>27.7108</v>
+        <v>27.710799999999999</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>53</v>
@@ -3592,28 +2977,28 @@
         <v>13</v>
       </c>
       <c r="L24" s="3">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M24" s="3">
         <v>35</v>
       </c>
       <c r="N24" s="3">
-        <v>0.64593309164</v>
+        <v>0.64593309164000001</v>
       </c>
       <c r="O24" s="3">
         <v>0.60806196928</v>
       </c>
       <c r="P24" s="3">
-        <v>1690.42663574</v>
+        <v>1690.4266357399999</v>
       </c>
       <c r="Q24" s="3">
-        <v>8.34122943878</v>
+        <v>8.3412294387799992</v>
       </c>
       <c r="R24" s="3">
-        <v>261.392913818</v>
+        <v>261.39291381800001</v>
       </c>
       <c r="S24" s="3">
-        <v>864.092651367</v>
+        <v>864.09265136700003</v>
       </c>
       <c r="T24" s="3">
         <v>19.0296478271</v>
@@ -3625,13 +3010,13 @@
         <v>0.2874411</v>
       </c>
       <c r="W24" s="3">
-        <v>329.6996</v>
+        <v>329.69959999999998</v>
       </c>
       <c r="X24" s="3">
-        <v>207.6021</v>
+        <v>207.60210000000001</v>
       </c>
       <c r="Y24" s="3">
-        <v>0.406984001398087</v>
+        <v>0.40698400139808699</v>
       </c>
       <c r="Z24" s="1">
         <v>0.97</v>
@@ -3640,7 +3025,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>7</v>
       </c>
@@ -3648,7 +3033,7 @@
         <v>112.8582</v>
       </c>
       <c r="C25" s="3">
-        <v>27.7512</v>
+        <v>27.751200000000001</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>54</v>
@@ -3681,40 +3066,40 @@
         <v>41</v>
       </c>
       <c r="N25" s="3">
-        <v>0.675841629505</v>
+        <v>0.67584162950500004</v>
       </c>
       <c r="O25" s="3">
-        <v>0.905060768127</v>
+        <v>0.90506076812699998</v>
       </c>
       <c r="P25" s="3">
-        <v>1338.08996582</v>
+        <v>1338.0899658200001</v>
       </c>
       <c r="Q25" s="3">
-        <v>9.1068944931</v>
+        <v>9.1068944931000004</v>
       </c>
       <c r="R25" s="3">
-        <v>258.650360107</v>
+        <v>258.65036010699998</v>
       </c>
       <c r="S25" s="3">
-        <v>1397.29211426</v>
+        <v>1397.2921142600001</v>
       </c>
       <c r="T25" s="3">
-        <v>23.7096290588</v>
+        <v>23.709629058800001</v>
       </c>
       <c r="U25" s="3">
         <v>0.15</v>
       </c>
       <c r="V25" s="3">
-        <v>0.2654218</v>
+        <v>0.26542179999999999</v>
       </c>
       <c r="W25" s="3">
-        <v>260.8758</v>
+        <v>260.87580000000003</v>
       </c>
       <c r="X25" s="3">
-        <v>329.8332</v>
+        <v>329.83319999999998</v>
       </c>
       <c r="Y25" s="3">
-        <v>0.368562012910843</v>
+        <v>0.36856201291084301</v>
       </c>
       <c r="Z25" s="1">
         <v>0.32</v>
@@ -3723,15 +3108,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>8</v>
       </c>
       <c r="B26" s="3">
-        <v>112.8589</v>
+        <v>112.85890000000001</v>
       </c>
       <c r="C26" s="3">
-        <v>27.7616</v>
+        <v>27.761600000000001</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>55</v>
@@ -3764,40 +3149,40 @@
         <v>43</v>
       </c>
       <c r="N26" s="3">
-        <v>0.697020709515</v>
+        <v>0.69702070951499995</v>
       </c>
       <c r="O26" s="3">
-        <v>0.976207971573</v>
+        <v>0.97620797157299999</v>
       </c>
       <c r="P26" s="3">
-        <v>1409.71313477</v>
+        <v>1409.7131347699999</v>
       </c>
       <c r="Q26" s="3">
-        <v>9.38171958923</v>
+        <v>9.3817195892300003</v>
       </c>
       <c r="R26" s="3">
-        <v>253.401657104</v>
+        <v>253.40165710400001</v>
       </c>
       <c r="S26" s="3">
         <v>1866.32995605</v>
       </c>
       <c r="T26" s="3">
-        <v>24.022611618</v>
+        <v>24.022611617999999</v>
       </c>
       <c r="U26" s="3">
         <v>0.16</v>
       </c>
       <c r="V26" s="3">
-        <v>0.2575164</v>
+        <v>0.25751639999999998</v>
       </c>
       <c r="W26" s="3">
-        <v>252.0563</v>
+        <v>252.05629999999999</v>
       </c>
       <c r="X26" s="3">
-        <v>361.4657</v>
+        <v>361.46570000000003</v>
       </c>
       <c r="Y26" s="3">
-        <v>0.371239006519318</v>
+        <v>0.37123900651931802</v>
       </c>
       <c r="Z26" s="1">
         <v>0.87</v>
@@ -3806,7 +3191,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>9</v>
       </c>
@@ -3814,7 +3199,7 @@
         <v>112.857</v>
       </c>
       <c r="C27" s="3">
-        <v>27.7615</v>
+        <v>27.761500000000002</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>56</v>
@@ -3847,40 +3232,40 @@
         <v>41</v>
       </c>
       <c r="N27" s="3">
-        <v>0.697149991989</v>
+        <v>0.69714999198899996</v>
       </c>
       <c r="O27" s="3">
-        <v>0.970161139965</v>
+        <v>0.97016113996499997</v>
       </c>
       <c r="P27" s="3">
-        <v>1409.65222168</v>
+        <v>1409.6522216799999</v>
       </c>
       <c r="Q27" s="3">
-        <v>9.39900302887</v>
+        <v>9.3990030288700002</v>
       </c>
       <c r="R27" s="3">
-        <v>253.530258179</v>
+        <v>253.53025817899999</v>
       </c>
       <c r="S27" s="3">
-        <v>1845.26257324</v>
+        <v>1845.2625732399999</v>
       </c>
       <c r="T27" s="3">
-        <v>23.9501209259</v>
+        <v>23.950120925899999</v>
       </c>
       <c r="U27" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="V27" s="3">
-        <v>0.258483</v>
+        <v>0.25848300000000002</v>
       </c>
       <c r="W27" s="3">
         <v>253.6181</v>
       </c>
       <c r="X27" s="3">
-        <v>358.2487</v>
+        <v>358.24869999999999</v>
       </c>
       <c r="Y27" s="3">
-        <v>0.299347996711731</v>
+        <v>0.29934799671173101</v>
       </c>
       <c r="Z27" s="1">
         <v>0.35</v>
@@ -3889,7 +3274,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>10</v>
       </c>
@@ -3897,7 +3282,7 @@
         <v>112.8017</v>
       </c>
       <c r="C28" s="3">
-        <v>27.7238</v>
+        <v>27.723800000000001</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>57</v>
@@ -3930,34 +3315,34 @@
         <v>28</v>
       </c>
       <c r="N28" s="3">
-        <v>0.661136865616</v>
+        <v>0.66113686561600005</v>
       </c>
       <c r="O28" s="3">
-        <v>0.585066318512</v>
+        <v>0.58506631851199997</v>
       </c>
       <c r="P28" s="3">
         <v>1740.5871582</v>
       </c>
       <c r="Q28" s="3">
-        <v>8.11696815491</v>
+        <v>8.1169681549099995</v>
       </c>
       <c r="R28" s="3">
-        <v>260.594116211</v>
+        <v>260.59411621100003</v>
       </c>
       <c r="S28" s="3">
-        <v>880.366210938</v>
+        <v>880.36621093799999</v>
       </c>
       <c r="T28" s="3">
-        <v>18.6028118134</v>
+        <v>18.602811813399999</v>
       </c>
       <c r="U28" s="3">
         <v>0.13</v>
       </c>
       <c r="V28" s="3">
-        <v>0.2868055</v>
+        <v>0.28680549999999999</v>
       </c>
       <c r="W28" s="3">
-        <v>323.0826</v>
+        <v>323.08260000000001</v>
       </c>
       <c r="X28" s="3">
         <v>202.988</v>
@@ -3972,7 +3357,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>11</v>
       </c>
@@ -3980,7 +3365,7 @@
         <v>112.8963</v>
       </c>
       <c r="C29" s="3">
-        <v>27.7794</v>
+        <v>27.779399999999999</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>58</v>
@@ -4016,37 +3401,37 @@
         <v>0.692190527916</v>
       </c>
       <c r="O29" s="3">
-        <v>1.1468873024</v>
+        <v>1.1468873023999999</v>
       </c>
       <c r="P29" s="3">
         <v>1409.75488281</v>
       </c>
       <c r="Q29" s="3">
-        <v>9.06415843964</v>
+        <v>9.0641584396399999</v>
       </c>
       <c r="R29" s="3">
         <v>253.079788208</v>
       </c>
       <c r="S29" s="3">
-        <v>2206.43408203</v>
+        <v>2206.4340820299999</v>
       </c>
       <c r="T29" s="3">
-        <v>25.1458854675</v>
+        <v>25.145885467500001</v>
       </c>
       <c r="U29" s="3">
         <v>0.17</v>
       </c>
       <c r="V29" s="3">
-        <v>0.253688</v>
+        <v>0.25368800000000002</v>
       </c>
       <c r="W29" s="3">
-        <v>214.2025</v>
+        <v>214.20249999999999</v>
       </c>
       <c r="X29" s="3">
         <v>405.8623</v>
       </c>
       <c r="Y29" s="3">
-        <v>1.37365996837616</v>
+        <v>1.3736599683761599</v>
       </c>
       <c r="Z29" s="1">
         <v>0.86</v>
@@ -4055,7 +3440,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>12</v>
       </c>
@@ -4063,7 +3448,7 @@
         <v>112.9083</v>
       </c>
       <c r="C30" s="3">
-        <v>27.772</v>
+        <v>27.771999999999998</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>59</v>
@@ -4096,7 +3481,7 @@
         <v>82</v>
       </c>
       <c r="N30" s="3">
-        <v>0.609036743641</v>
+        <v>0.60903674364100002</v>
       </c>
       <c r="O30" s="3">
         <v>1.20894777775</v>
@@ -4105,31 +3490,31 @@
         <v>1196.40136719</v>
       </c>
       <c r="Q30" s="3">
-        <v>8.27745914459</v>
+        <v>8.2774591445900008</v>
       </c>
       <c r="R30" s="3">
-        <v>268.080688477</v>
+        <v>268.08068847700002</v>
       </c>
       <c r="S30" s="3">
         <v>1293.5012207</v>
       </c>
       <c r="T30" s="3">
-        <v>25.1947727203</v>
+        <v>25.194772720300001</v>
       </c>
       <c r="U30" s="3">
         <v>0.25</v>
       </c>
       <c r="V30" s="3">
-        <v>0.2551288</v>
+        <v>0.25512879999999999</v>
       </c>
       <c r="W30" s="3">
-        <v>183.0803</v>
+        <v>183.08029999999999</v>
       </c>
       <c r="X30" s="3">
-        <v>354.5422</v>
+        <v>354.54219999999998</v>
       </c>
       <c r="Y30" s="3">
-        <v>0.852805972099304</v>
+        <v>0.85280597209930398</v>
       </c>
       <c r="Z30" s="1">
         <v>0.99</v>
@@ -4138,7 +3523,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>13</v>
       </c>
@@ -4146,7 +3531,7 @@
         <v>112.81</v>
       </c>
       <c r="C31" s="3">
-        <v>27.7428</v>
+        <v>27.742799999999999</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>60</v>
@@ -4179,13 +3564,13 @@
         <v>31</v>
       </c>
       <c r="N31" s="3">
-        <v>0.685739457607</v>
+        <v>0.68573945760699995</v>
       </c>
       <c r="O31" s="3">
-        <v>0.756814777851</v>
+        <v>0.75681477785100004</v>
       </c>
       <c r="P31" s="3">
-        <v>1492.09399414</v>
+        <v>1492.0939941399999</v>
       </c>
       <c r="Q31" s="3">
         <v>9.34010314941</v>
@@ -4194,25 +3579,25 @@
         <v>261.058349609</v>
       </c>
       <c r="S31" s="3">
-        <v>1095.83056641</v>
+        <v>1095.8305664100001</v>
       </c>
       <c r="T31" s="3">
-        <v>20.7574443817</v>
+        <v>20.757444381700001</v>
       </c>
       <c r="U31" s="3">
         <v>0.16</v>
       </c>
       <c r="V31" s="3">
-        <v>0.2880018</v>
+        <v>0.28800179999999997</v>
       </c>
       <c r="W31" s="3">
-        <v>296.8036</v>
+        <v>296.80360000000002</v>
       </c>
       <c r="X31" s="3">
         <v>253.321</v>
       </c>
       <c r="Y31" s="3">
-        <v>0.291918009519577</v>
+        <v>0.29191800951957703</v>
       </c>
       <c r="Z31" s="1">
         <v>0.12</v>
@@ -4221,7 +3606,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>20</v>
       </c>
@@ -4229,13 +3614,13 @@
         <v>112.86478</v>
       </c>
       <c r="C32" s="3">
-        <v>27.7177</v>
+        <v>27.717700000000001</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>61</v>
       </c>
       <c r="E32" s="3">
-        <v>8.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="F32" s="3">
         <v>72</v>
@@ -4271,7 +3656,7 @@
         <v>1143</v>
       </c>
       <c r="Q32" s="3">
-        <v>8.427</v>
+        <v>8.4269999999999996</v>
       </c>
       <c r="R32" s="3">
         <v>265.791</v>
@@ -4295,7 +3680,7 @@
         <v>305</v>
       </c>
       <c r="Y32" s="3">
-        <v>0.678927004337311</v>
+        <v>0.67892700433731101</v>
       </c>
       <c r="Z32" s="1">
         <v>0.01</v>
@@ -4304,7 +3689,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>53</v>
       </c>
@@ -4312,7 +3697,7 @@
         <v>112.9071</v>
       </c>
       <c r="C33" s="3">
-        <v>27.7613</v>
+        <v>27.761299999999999</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>62</v>
@@ -4345,16 +3730,16 @@
         <v>63</v>
       </c>
       <c r="N33" s="3">
-        <v>0.583384692669</v>
+        <v>0.58338469266899995</v>
       </c>
       <c r="O33" s="3">
-        <v>1.24471175671</v>
+        <v>1.2447117567099999</v>
       </c>
       <c r="P33" s="3">
-        <v>1108.89306641</v>
+        <v>1108.8930664100001</v>
       </c>
       <c r="Q33" s="3">
-        <v>7.93437623978</v>
+        <v>7.9343762397799997</v>
       </c>
       <c r="R33" s="3">
         <v>273.192230225</v>
@@ -4363,22 +3748,22 @@
         <v>1014.33990479</v>
       </c>
       <c r="T33" s="3">
-        <v>25.3172550201</v>
+        <v>25.317255020099999</v>
       </c>
       <c r="U33" s="3">
         <v>0.2061482</v>
       </c>
       <c r="V33" s="3">
-        <v>0.2534269</v>
+        <v>0.25342690000000001</v>
       </c>
       <c r="W33" s="3">
-        <v>172.5037</v>
+        <v>172.50370000000001</v>
       </c>
       <c r="X33" s="3">
-        <v>342.3599</v>
+        <v>342.35989999999998</v>
       </c>
       <c r="Y33" s="3">
-        <v>0.76630300283432</v>
+        <v>0.76630300283431996</v>
       </c>
       <c r="Z33" s="1">
         <v>1.9</v>
@@ -4387,7 +3772,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>73</v>
       </c>
@@ -4401,7 +3786,7 @@
         <v>63</v>
       </c>
       <c r="E34" s="3">
-        <v>18.1</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="F34" s="3">
         <v>67</v>
@@ -4428,40 +3813,40 @@
         <v>46</v>
       </c>
       <c r="N34" s="3">
-        <v>0.34197717905</v>
+        <v>0.34197717905000002</v>
       </c>
       <c r="O34" s="3">
-        <v>0.725339472294</v>
+        <v>0.72533947229399998</v>
       </c>
       <c r="P34" s="3">
-        <v>1739.31384277</v>
+        <v>1739.3138427700001</v>
       </c>
       <c r="Q34" s="3">
         <v>10.8345775604</v>
       </c>
       <c r="R34" s="3">
-        <v>268.60144043</v>
+        <v>268.60144043000003</v>
       </c>
       <c r="S34" s="3">
-        <v>561.588012695</v>
+        <v>561.58801269499997</v>
       </c>
       <c r="T34" s="3">
-        <v>21.4305877686</v>
+        <v>21.430587768599999</v>
       </c>
       <c r="U34" s="3">
-        <v>0.1363515</v>
+        <v>0.13635149999999999</v>
       </c>
       <c r="V34" s="3">
-        <v>0.2192755</v>
+        <v>0.21927550000000001</v>
       </c>
       <c r="W34" s="3">
-        <v>500.0672</v>
+        <v>500.06720000000001</v>
       </c>
       <c r="X34" s="3">
-        <v>198.3248</v>
+        <v>198.32480000000001</v>
       </c>
       <c r="Y34" s="3">
-        <v>0.349842995405197</v>
+        <v>0.34984299540519698</v>
       </c>
       <c r="Z34" s="1">
         <v>0.95</v>
@@ -4470,12 +3855,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>74</v>
       </c>
       <c r="B35" s="3">
-        <v>112.73628</v>
+        <v>112.73627999999999</v>
       </c>
       <c r="C35" s="3">
         <v>27.51146</v>
@@ -4520,16 +3905,16 @@
         <v>2781</v>
       </c>
       <c r="Q35" s="3">
-        <v>9.405</v>
+        <v>9.4049999999999994</v>
       </c>
       <c r="R35" s="3">
-        <v>276.549</v>
+        <v>276.54899999999998</v>
       </c>
       <c r="S35" s="3">
         <v>863</v>
       </c>
       <c r="T35" s="3">
-        <v>14.736</v>
+        <v>14.736000000000001</v>
       </c>
       <c r="U35" s="3">
         <v>0.1371154</v>
@@ -4553,15 +3938,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>75</v>
       </c>
       <c r="B36" s="3">
-        <v>112.76198</v>
+        <v>112.76197999999999</v>
       </c>
       <c r="C36" s="3">
-        <v>27.58261</v>
+        <v>27.582609999999999</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>66</v>
@@ -4594,22 +3979,22 @@
         <v>34</v>
       </c>
       <c r="N36" s="3">
-        <v>0.313212871552</v>
+        <v>0.31321287155200001</v>
       </c>
       <c r="O36" s="3">
-        <v>0.751639246941</v>
+        <v>0.75163924694100004</v>
       </c>
       <c r="P36" s="3">
-        <v>1377.39526367</v>
+        <v>1377.3952636700001</v>
       </c>
       <c r="Q36" s="3">
         <v>10.1250162125</v>
       </c>
       <c r="R36" s="3">
-        <v>267.269866943</v>
+        <v>267.26986694300001</v>
       </c>
       <c r="S36" s="3">
-        <v>513.136413574</v>
+        <v>513.13641357400002</v>
       </c>
       <c r="T36" s="3">
         <v>22.6729698181</v>
@@ -4627,7 +4012,7 @@
         <v>244.8434</v>
       </c>
       <c r="Y36" s="3">
-        <v>0.320035994052887</v>
+        <v>0.32003599405288702</v>
       </c>
       <c r="Z36" s="1">
         <v>0.42</v>
@@ -4636,7 +4021,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>76</v>
       </c>
@@ -4686,7 +4071,7 @@
         <v>748</v>
       </c>
       <c r="Q37" s="3">
-        <v>13.492</v>
+        <v>13.492000000000001</v>
       </c>
       <c r="R37" s="3">
         <v>207.619</v>
@@ -4695,7 +4080,7 @@
         <v>295</v>
       </c>
       <c r="T37" s="3">
-        <v>38.77</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="U37" s="3">
         <v>0.11</v>
@@ -4704,13 +4089,13 @@
         <v>0.19</v>
       </c>
       <c r="W37" s="3">
-        <v>948.6034</v>
+        <v>948.60339999999997</v>
       </c>
       <c r="X37" s="3">
         <v>311</v>
       </c>
       <c r="Y37" s="3">
-        <v>0.319788992404938</v>
+        <v>0.31978899240493802</v>
       </c>
       <c r="Z37" s="1">
         <v>0.84</v>
@@ -4719,7 +4104,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:27">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>77</v>
       </c>
@@ -4727,13 +4112,13 @@
         <v>112.74683</v>
       </c>
       <c r="C38" s="3">
-        <v>27.53813</v>
+        <v>27.538129999999999</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>68</v>
       </c>
       <c r="E38" s="3">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F38" s="3">
         <v>59</v>
@@ -4760,10 +4145,10 @@
         <v>36</v>
       </c>
       <c r="N38" s="3">
-        <v>0.321907788515</v>
+        <v>0.32190778851500002</v>
       </c>
       <c r="O38" s="3">
-        <v>0.63482606411</v>
+        <v>0.63482606410999998</v>
       </c>
       <c r="P38" s="3">
         <v>2105.0065918</v>
@@ -4772,25 +4157,25 @@
         <v>10.821803093</v>
       </c>
       <c r="R38" s="3">
-        <v>271.348114014</v>
+        <v>271.34811401399998</v>
       </c>
       <c r="S38" s="3">
-        <v>656.038513184</v>
+        <v>656.03851318399995</v>
       </c>
       <c r="T38" s="3">
-        <v>19.5355434418</v>
+        <v>19.535543441800002</v>
       </c>
       <c r="U38" s="3">
         <v>0.12</v>
       </c>
       <c r="V38" s="3">
-        <v>0.1897813</v>
+        <v>0.18978129999999999</v>
       </c>
       <c r="W38" s="3">
-        <v>507.7926</v>
+        <v>507.79259999999999</v>
       </c>
       <c r="X38" s="3">
-        <v>172.9094</v>
+        <v>172.90940000000001</v>
       </c>
       <c r="Y38" s="3">
         <v>0.377561986446381</v>
@@ -4802,7 +4187,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>78</v>
       </c>
@@ -4810,13 +4195,13 @@
         <v>112.76925</v>
       </c>
       <c r="C39" s="3">
-        <v>27.52728</v>
+        <v>27.527280000000001</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E39" s="3">
-        <v>323.1</v>
+        <v>323.10000000000002</v>
       </c>
       <c r="F39" s="3">
         <v>117</v>
@@ -4846,37 +4231,37 @@
         <v>0.352784961462</v>
       </c>
       <c r="O39" s="3">
-        <v>0.735718786716</v>
+        <v>0.73571878671599999</v>
       </c>
       <c r="P39" s="3">
         <v>1855.1328125</v>
       </c>
       <c r="Q39" s="3">
-        <v>11.2770166397</v>
+        <v>11.277016639699999</v>
       </c>
       <c r="R39" s="3">
         <v>265.413330078</v>
       </c>
       <c r="S39" s="3">
-        <v>559.671020508</v>
+        <v>559.67102050799997</v>
       </c>
       <c r="T39" s="3">
         <v>21.8864173889</v>
       </c>
       <c r="U39" s="3">
-        <v>0.1450557</v>
+        <v>0.14505570000000001</v>
       </c>
       <c r="V39" s="3">
-        <v>0.2409054</v>
+        <v>0.24090539999999999</v>
       </c>
       <c r="W39" s="3">
-        <v>537.5356</v>
+        <v>537.53560000000004</v>
       </c>
       <c r="X39" s="3">
         <v>184.6455</v>
       </c>
       <c r="Y39" s="3">
-        <v>0.251819014549255</v>
+        <v>0.25181901454925498</v>
       </c>
       <c r="Z39" s="1">
         <v>0.01</v>
@@ -4885,21 +4270,21 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>79</v>
       </c>
       <c r="B40" s="3">
-        <v>112.73892</v>
+        <v>112.73891999999999</v>
       </c>
       <c r="C40" s="3">
-        <v>27.5221</v>
+        <v>27.522099999999998</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E40" s="3">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="F40" s="3">
         <v>101</v>
@@ -4926,40 +4311,40 @@
         <v>34</v>
       </c>
       <c r="N40" s="3">
-        <v>0.320674270391</v>
+        <v>0.32067427039099999</v>
       </c>
       <c r="O40" s="3">
-        <v>0.481054365635</v>
+        <v>0.48105436563499998</v>
       </c>
       <c r="P40" s="3">
-        <v>2641.79272461</v>
+        <v>2641.7927246099998</v>
       </c>
       <c r="Q40" s="3">
-        <v>9.93612766266</v>
+        <v>9.9361276626600006</v>
       </c>
       <c r="R40" s="3">
-        <v>275.167449951</v>
+        <v>275.16744995099998</v>
       </c>
       <c r="S40" s="3">
-        <v>813.635559082</v>
+        <v>813.63555908199999</v>
       </c>
       <c r="T40" s="3">
-        <v>15.94926548</v>
+        <v>15.949265479999999</v>
       </c>
       <c r="U40" s="3">
-        <v>0.1322967</v>
+        <v>0.13229669999999999</v>
       </c>
       <c r="V40" s="3">
         <v>0.1408375</v>
       </c>
       <c r="W40" s="3">
-        <v>359.6536</v>
+        <v>359.65359999999998</v>
       </c>
       <c r="X40" s="3">
-        <v>138.0825</v>
+        <v>138.08250000000001</v>
       </c>
       <c r="Y40" s="3">
-        <v>0.270296007394791</v>
+        <v>0.27029600739479098</v>
       </c>
       <c r="Z40" s="1">
         <v>0.41</v>
@@ -4968,7 +4353,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>80</v>
       </c>
@@ -4976,13 +4361,13 @@
         <v>112.7281</v>
       </c>
       <c r="C41" s="3">
-        <v>27.63875</v>
+        <v>27.638750000000002</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>71</v>
       </c>
       <c r="E41" s="3">
-        <v>18.1</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="F41" s="3">
         <v>97</v>
@@ -5009,19 +4394,19 @@
         <v>30</v>
       </c>
       <c r="N41" s="3">
-        <v>0.39464405179</v>
+        <v>0.39464405179000001</v>
       </c>
       <c r="O41" s="3">
-        <v>0.747964560986</v>
+        <v>0.74796456098599995</v>
       </c>
       <c r="P41" s="3">
         <v>1213.7791748</v>
       </c>
       <c r="Q41" s="3">
-        <v>11.623673439</v>
+        <v>11.623673438999999</v>
       </c>
       <c r="R41" s="3">
-        <v>286.343963623</v>
+        <v>286.34396362299998</v>
       </c>
       <c r="S41" s="3">
         <v>549.595214844</v>
@@ -5030,28 +4415,28 @@
         <v>23.088312149</v>
       </c>
       <c r="U41" s="3">
-        <v>0.1650658</v>
+        <v>0.16506580000000001</v>
       </c>
       <c r="V41" s="3">
-        <v>0.2292414</v>
+        <v>0.22924140000000001</v>
       </c>
       <c r="W41" s="3">
-        <v>370.3206</v>
+        <v>370.32060000000001</v>
       </c>
       <c r="X41" s="3">
-        <v>215.4507</v>
+        <v>215.45070000000001</v>
       </c>
       <c r="Y41" s="3">
-        <v>0.34961000084877</v>
+        <v>0.34961000084876998</v>
       </c>
       <c r="Z41" s="1">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AA41" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>81</v>
       </c>
@@ -5101,16 +4486,16 @@
         <v>1124</v>
       </c>
       <c r="Q42" s="3">
-        <v>8.243</v>
+        <v>8.2430000000000003</v>
       </c>
       <c r="R42" s="3">
-        <v>261.438</v>
+        <v>261.43799999999999</v>
       </c>
       <c r="S42" s="3">
         <v>541</v>
       </c>
       <c r="T42" s="3">
-        <v>22.862</v>
+        <v>22.861999999999998</v>
       </c>
       <c r="U42" s="3">
         <v>0.13</v>
@@ -5134,12 +4519,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>83</v>
       </c>
       <c r="B43" s="3">
-        <v>112.67982</v>
+        <v>112.67982000000001</v>
       </c>
       <c r="C43" s="3">
         <v>27.64142</v>
@@ -5175,7 +4560,7 @@
         <v>33</v>
       </c>
       <c r="N43" s="3">
-        <v>0.430397093296</v>
+        <v>0.43039709329600001</v>
       </c>
       <c r="O43" s="3">
         <v>0.78225672245</v>
@@ -5187,19 +4572,19 @@
         <v>15.103</v>
       </c>
       <c r="R43" s="3">
-        <v>352.147</v>
+        <v>352.14699999999999</v>
       </c>
       <c r="S43" s="3">
         <v>276</v>
       </c>
       <c r="T43" s="3">
-        <v>24.675</v>
+        <v>24.675000000000001</v>
       </c>
       <c r="U43" s="3">
         <v>0.17</v>
       </c>
       <c r="V43" s="3">
-        <v>0.2663637</v>
+        <v>0.26636369999999998</v>
       </c>
       <c r="W43" s="3">
         <v>319</v>
@@ -5217,15 +4602,15 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>84</v>
       </c>
       <c r="B44" s="3">
-        <v>112.75732</v>
+        <v>112.75732000000001</v>
       </c>
       <c r="C44" s="3">
-        <v>27.60231</v>
+        <v>27.602309999999999</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>75</v>
@@ -5264,34 +4649,34 @@
         <v>0.754867434502</v>
       </c>
       <c r="P44" s="3">
-        <v>1307.28833008</v>
+        <v>1307.2883300799999</v>
       </c>
       <c r="Q44" s="3">
         <v>10.0572280884</v>
       </c>
       <c r="R44" s="3">
-        <v>268.452514648</v>
+        <v>268.45251464799998</v>
       </c>
       <c r="S44" s="3">
-        <v>509.759429932</v>
+        <v>509.75942993199999</v>
       </c>
       <c r="T44" s="3">
-        <v>22.9046783447</v>
+        <v>22.904678344699999</v>
       </c>
       <c r="U44" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="V44" s="3">
-        <v>0.1954202</v>
+        <v>0.19542019999999999</v>
       </c>
       <c r="W44" s="3">
-        <v>386.1544</v>
+        <v>386.15440000000001</v>
       </c>
       <c r="X44" s="3">
         <v>249.6035</v>
       </c>
       <c r="Y44" s="3">
-        <v>0.310835003852844</v>
+        <v>0.31083500385284402</v>
       </c>
       <c r="Z44" s="1">
         <v>0.01</v>
@@ -5300,7 +4685,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:27">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>85</v>
       </c>
@@ -5308,7 +4693,7 @@
         <v>112.70487</v>
       </c>
       <c r="C45" s="3">
-        <v>27.60759</v>
+        <v>27.607589999999998</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>76</v>
@@ -5341,25 +4726,25 @@
         <v>30</v>
       </c>
       <c r="N45" s="3">
-        <v>0.339942932129</v>
+        <v>0.33994293212900001</v>
       </c>
       <c r="O45" s="3">
         <v>0.741595864296</v>
       </c>
       <c r="P45" s="3">
-        <v>1228.55810547</v>
+        <v>1228.5581054700001</v>
       </c>
       <c r="Q45" s="3">
-        <v>11.6487970352</v>
+        <v>11.648797035199999</v>
       </c>
       <c r="R45" s="3">
-        <v>281.251800537</v>
+        <v>281.25180053700001</v>
       </c>
       <c r="S45" s="3">
-        <v>495.715362549</v>
+        <v>495.71536254900002</v>
       </c>
       <c r="T45" s="3">
-        <v>22.9636878967</v>
+        <v>22.963687896700002</v>
       </c>
       <c r="U45" s="3">
         <v>0.12</v>
@@ -5368,13 +4753,13 @@
         <v>0.2231728</v>
       </c>
       <c r="W45" s="3">
-        <v>376.0436</v>
+        <v>376.04360000000003</v>
       </c>
       <c r="X45" s="3">
         <v>215.7654</v>
       </c>
       <c r="Y45" s="3">
-        <v>0.290194988250732</v>
+        <v>0.29019498825073198</v>
       </c>
       <c r="Z45" s="1">
         <v>0.31</v>
@@ -5383,7 +4768,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>86</v>
       </c>
@@ -5391,13 +4776,13 @@
         <v>112.69434</v>
       </c>
       <c r="C46" s="3">
-        <v>27.47558</v>
+        <v>27.475580000000001</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E46" s="3">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="F46" s="3">
         <v>67</v>
@@ -5427,22 +4812,22 @@
         <v>0.239345103502</v>
       </c>
       <c r="O46" s="3">
-        <v>0.660265266895</v>
+        <v>0.66026526689499998</v>
       </c>
       <c r="P46" s="3">
-        <v>2775.02416992</v>
+        <v>2775.0241699200001</v>
       </c>
       <c r="Q46" s="3">
-        <v>14.8285865784</v>
+        <v>14.828586578399999</v>
       </c>
       <c r="R46" s="3">
         <v>280.779388428</v>
       </c>
       <c r="S46" s="3">
-        <v>627.782470703</v>
+        <v>627.78247070299994</v>
       </c>
       <c r="T46" s="3">
-        <v>17.925453186</v>
+        <v>17.925453185999999</v>
       </c>
       <c r="U46" s="3">
         <v>0.13</v>
@@ -5454,19 +4839,19 @@
         <v>1574.905</v>
       </c>
       <c r="X46" s="3">
-        <v>128.6922</v>
+        <v>128.69220000000001</v>
       </c>
       <c r="Y46" s="3">
-        <v>0.320161998271942</v>
+        <v>0.32016199827194203</v>
       </c>
       <c r="Z46" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA46" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>87</v>
       </c>
@@ -5474,7 +4859,7 @@
         <v>112.71278</v>
       </c>
       <c r="C47" s="3">
-        <v>27.48063</v>
+        <v>27.480630000000001</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>79</v>
@@ -5507,7 +4892,7 @@
         <v>33</v>
       </c>
       <c r="N47" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O47" s="3">
         <v>0.48</v>
@@ -5516,10 +4901,10 @@
         <v>3468</v>
       </c>
       <c r="Q47" s="3">
-        <v>18.313</v>
+        <v>18.312999999999999</v>
       </c>
       <c r="R47" s="3">
-        <v>289.838</v>
+        <v>289.83800000000002</v>
       </c>
       <c r="S47" s="3">
         <v>841</v>
@@ -5540,7 +4925,7 @@
         <v>107</v>
       </c>
       <c r="Y47" s="3">
-        <v>0.171298995614052</v>
+        <v>0.17129899561405201</v>
       </c>
       <c r="Z47" s="1">
         <v>0.2</v>
@@ -5549,7 +4934,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>88</v>
       </c>
@@ -5599,16 +4984,16 @@
         <v>2125</v>
       </c>
       <c r="Q48" s="3">
-        <v>10.158</v>
+        <v>10.157999999999999</v>
       </c>
       <c r="R48" s="3">
-        <v>276.292</v>
+        <v>276.29199999999997</v>
       </c>
       <c r="S48" s="3">
         <v>251</v>
       </c>
       <c r="T48" s="3">
-        <v>19.469</v>
+        <v>19.469000000000001</v>
       </c>
       <c r="U48" s="3">
         <v>0.13</v>
@@ -5623,24 +5008,24 @@
         <v>154.9434</v>
       </c>
       <c r="Y48" s="3">
-        <v>0.250023007392883</v>
+        <v>0.25002300739288302</v>
       </c>
       <c r="Z48" s="1">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>89</v>
       </c>
       <c r="B49" s="3">
-        <v>112.69598</v>
+        <v>112.69598000000001</v>
       </c>
       <c r="C49" s="3">
-        <v>27.46055</v>
+        <v>27.460550000000001</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>81</v>
@@ -5673,22 +5058,22 @@
         <v>33</v>
       </c>
       <c r="N49" s="3">
-        <v>0.27909758687</v>
+        <v>0.27909758687000003</v>
       </c>
       <c r="O49" s="3">
-        <v>0.742324709892</v>
+        <v>0.74232470989199995</v>
       </c>
       <c r="P49" s="3">
-        <v>2515.89624023</v>
+        <v>2515.8962402299999</v>
       </c>
       <c r="Q49" s="3">
-        <v>13.5811738968</v>
+        <v>13.581173896799999</v>
       </c>
       <c r="R49" s="3">
         <v>276.115966797</v>
       </c>
       <c r="S49" s="3">
-        <v>539.066345215</v>
+        <v>539.06634521499996</v>
       </c>
       <c r="T49" s="3">
         <v>19.0404949188</v>
@@ -5697,13 +5082,13 @@
         <v>0.11</v>
       </c>
       <c r="V49" s="3">
-        <v>0.2663572</v>
+        <v>0.26635720000000002</v>
       </c>
       <c r="W49" s="3">
         <v>1208.212</v>
       </c>
       <c r="X49" s="3">
-        <v>144.3303</v>
+        <v>144.33029999999999</v>
       </c>
       <c r="Y49" s="3">
         <v>0.211068004369736</v>
@@ -5715,15 +5100,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:27">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>145</v>
       </c>
       <c r="B50" s="3">
-        <v>112.71716</v>
+        <v>112.71716000000001</v>
       </c>
       <c r="C50" s="3">
-        <v>27.42391</v>
+        <v>27.423909999999999</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>82</v>
@@ -5756,25 +5141,25 @@
         <v>34</v>
       </c>
       <c r="N50" s="3">
-        <v>0.337470293045</v>
+        <v>0.33747029304499998</v>
       </c>
       <c r="O50" s="3">
-        <v>0.821384727955</v>
+        <v>0.82138472795499995</v>
       </c>
       <c r="P50" s="3">
-        <v>1999.57800293</v>
+        <v>1999.5780029299999</v>
       </c>
       <c r="Q50" s="3">
         <v>12.9589862823</v>
       </c>
       <c r="R50" s="3">
-        <v>260.883361816</v>
+        <v>260.88336181599999</v>
       </c>
       <c r="S50" s="3">
-        <v>483.475646973</v>
+        <v>483.47564697299998</v>
       </c>
       <c r="T50" s="3">
-        <v>23.2219390869</v>
+        <v>23.221939086900001</v>
       </c>
       <c r="U50" s="3">
         <v>0.13</v>
@@ -5783,13 +5168,13 @@
         <v>0.2941899</v>
       </c>
       <c r="W50" s="3">
-        <v>983.3823</v>
+        <v>983.38229999999999</v>
       </c>
       <c r="X50" s="3">
         <v>191.2799</v>
       </c>
       <c r="Y50" s="3">
-        <v>0.297560006380081</v>
+        <v>0.29756000638008101</v>
       </c>
       <c r="Z50" s="1">
         <v>0.23</v>
@@ -5798,7 +5183,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="1:27">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>146</v>
       </c>
@@ -5806,7 +5191,7 @@
         <v>112.71135</v>
       </c>
       <c r="C51" s="3">
-        <v>27.43718</v>
+        <v>27.437180000000001</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>83</v>
@@ -5839,22 +5224,22 @@
         <v>48</v>
       </c>
       <c r="N51" s="3">
-        <v>0.311853945255</v>
+        <v>0.31185394525499999</v>
       </c>
       <c r="O51" s="3">
-        <v>0.790547668934</v>
+        <v>0.79054766893399997</v>
       </c>
       <c r="P51" s="3">
-        <v>2178.31787109</v>
+        <v>2178.3178710900002</v>
       </c>
       <c r="Q51" s="3">
-        <v>13.2635574341</v>
+        <v>13.263557434100001</v>
       </c>
       <c r="R51" s="3">
-        <v>265.128204346</v>
+        <v>265.12820434600002</v>
       </c>
       <c r="S51" s="3">
-        <v>514.099182129</v>
+        <v>514.09918212900004</v>
       </c>
       <c r="T51" s="3">
         <v>22.0089187622</v>
@@ -5863,7 +5248,7 @@
         <v>0.11</v>
       </c>
       <c r="V51" s="3">
-        <v>0.2848431</v>
+        <v>0.28484310000000002</v>
       </c>
       <c r="W51" s="3">
         <v>1109.742</v>
@@ -5872,16 +5257,16 @@
         <v>179.9924</v>
       </c>
       <c r="Y51" s="3">
-        <v>0.349451005458832</v>
+        <v>0.34945100545883201</v>
       </c>
       <c r="Z51" s="1">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA51" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="52" spans="1:27">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>147</v>
       </c>
@@ -5889,7 +5274,7 @@
         <v>112.74218</v>
       </c>
       <c r="C52" s="3">
-        <v>27.42055</v>
+        <v>27.420549999999999</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>84</v>
@@ -5922,40 +5307,40 @@
         <v>30</v>
       </c>
       <c r="N52" s="3">
-        <v>0.379658579826</v>
+        <v>0.37965857982599999</v>
       </c>
       <c r="O52" s="3">
         <v>0.8676648736</v>
       </c>
       <c r="P52" s="3">
-        <v>1695.26782227</v>
+        <v>1695.2678222699999</v>
       </c>
       <c r="Q52" s="3">
-        <v>12.871629715</v>
+        <v>12.871629714999999</v>
       </c>
       <c r="R52" s="3">
-        <v>251.53326416</v>
+        <v>251.53326415999999</v>
       </c>
       <c r="S52" s="3">
         <v>450.84262085</v>
       </c>
       <c r="T52" s="3">
-        <v>26.3198890686</v>
+        <v>26.319889068599998</v>
       </c>
       <c r="U52" s="3">
         <v>0.1270762</v>
       </c>
       <c r="V52" s="3">
-        <v>0.326373</v>
+        <v>0.32637300000000002</v>
       </c>
       <c r="W52" s="3">
-        <v>915.6755</v>
+        <v>915.67550000000006</v>
       </c>
       <c r="X52" s="3">
         <v>213.2406</v>
       </c>
       <c r="Y52" s="3">
-        <v>0.132649004459381</v>
+        <v>0.13264900445938099</v>
       </c>
       <c r="Z52" s="1">
         <v>0.01</v>
@@ -5964,7 +5349,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>14</v>
       </c>
@@ -6005,40 +5390,40 @@
         <v>74</v>
       </c>
       <c r="N53" s="3">
-        <v>0.61401283741</v>
+        <v>0.61401283741000001</v>
       </c>
       <c r="O53" s="3">
-        <v>1.05792856216</v>
+        <v>1.0579285621600001</v>
       </c>
       <c r="P53" s="3">
-        <v>1406.70397949</v>
+        <v>1406.7039794899999</v>
       </c>
       <c r="Q53" s="3">
-        <v>9.25965881348</v>
+        <v>9.2596588134799998</v>
       </c>
       <c r="R53" s="3">
-        <v>265.527618408</v>
+        <v>265.52761840800002</v>
       </c>
       <c r="S53" s="3">
-        <v>890.628723145</v>
+        <v>890.62872314499998</v>
       </c>
       <c r="T53" s="3">
-        <v>24.7413978577</v>
+        <v>24.741397857700001</v>
       </c>
       <c r="U53" s="3">
-        <v>0.1649839</v>
+        <v>0.16498389999999999</v>
       </c>
       <c r="V53" s="3">
         <v>0.3472382</v>
       </c>
       <c r="W53" s="3">
-        <v>198.4467</v>
+        <v>198.44669999999999</v>
       </c>
       <c r="X53" s="3">
         <v>297.3399</v>
       </c>
       <c r="Y53" s="3">
-        <v>0.595664024353027</v>
+        <v>0.59566402435302701</v>
       </c>
       <c r="Z53" s="1">
         <v>0.35</v>
@@ -6047,7 +5432,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>15</v>
       </c>
@@ -6088,22 +5473,22 @@
         <v>52</v>
       </c>
       <c r="N54" s="3">
-        <v>0.60618185997</v>
+        <v>0.60618185996999996</v>
       </c>
       <c r="O54" s="3">
-        <v>1.07933676243</v>
+        <v>1.0793367624300001</v>
       </c>
       <c r="P54" s="3">
-        <v>1334.43383789</v>
+        <v>1334.4338378899999</v>
       </c>
       <c r="Q54" s="3">
-        <v>8.98750019073</v>
+        <v>8.9875001907299996</v>
       </c>
       <c r="R54" s="3">
         <v>266.2265625</v>
       </c>
       <c r="S54" s="3">
-        <v>930.725524902</v>
+        <v>930.72552490199996</v>
       </c>
       <c r="T54" s="3">
         <v>24.8766498566</v>
@@ -6112,16 +5497,16 @@
         <v>0.15</v>
       </c>
       <c r="V54" s="3">
-        <v>0.3114515</v>
+        <v>0.31145149999999999</v>
       </c>
       <c r="W54" s="3">
         <v>200.0292</v>
       </c>
       <c r="X54" s="3">
-        <v>309.3062</v>
+        <v>309.30619999999999</v>
       </c>
       <c r="Y54" s="3">
-        <v>0.631892025470734</v>
+        <v>0.63189202547073398</v>
       </c>
       <c r="Z54" s="1">
         <v>0.15</v>
@@ -6130,15 +5515,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>16</v>
       </c>
       <c r="B55" s="3">
-        <v>112.96949</v>
+        <v>112.96948999999999</v>
       </c>
       <c r="C55" s="3">
-        <v>27.70638</v>
+        <v>27.706379999999999</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>88</v>
@@ -6171,40 +5556,40 @@
         <v>48</v>
       </c>
       <c r="N55" s="3">
-        <v>0.642530858517</v>
+        <v>0.64253085851699998</v>
       </c>
       <c r="O55" s="3">
         <v>1.04926764965</v>
       </c>
       <c r="P55" s="3">
-        <v>1317.48876953</v>
+        <v>1317.4887695299999</v>
       </c>
       <c r="Q55" s="3">
-        <v>9.27410125732</v>
+        <v>9.2741012573199999</v>
       </c>
       <c r="R55" s="3">
         <v>264.536865234</v>
       </c>
       <c r="S55" s="3">
-        <v>871.506530762</v>
+        <v>871.50653076200001</v>
       </c>
       <c r="T55" s="3">
-        <v>25.2314491272</v>
+        <v>25.231449127200001</v>
       </c>
       <c r="U55" s="3">
         <v>0.11</v>
       </c>
       <c r="V55" s="3">
-        <v>0.3504261</v>
+        <v>0.35042610000000002</v>
       </c>
       <c r="W55" s="3">
-        <v>207.1791</v>
+        <v>207.17910000000001</v>
       </c>
       <c r="X55" s="3">
-        <v>303.4528</v>
+        <v>303.45280000000002</v>
       </c>
       <c r="Y55" s="3">
-        <v>0.624216973781586</v>
+        <v>0.62421697378158603</v>
       </c>
       <c r="Z55" s="1">
         <v>0.51</v>
@@ -6213,21 +5598,21 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>17</v>
       </c>
       <c r="B56" s="3">
-        <v>113.02554</v>
+        <v>113.02554000000001</v>
       </c>
       <c r="C56" s="3">
-        <v>27.72883</v>
+        <v>27.728829999999999</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>89</v>
       </c>
       <c r="E56" s="3">
-        <v>9.3</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F56" s="3">
         <v>64</v>
@@ -6248,46 +5633,46 @@
         <v>37</v>
       </c>
       <c r="L56" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M56" s="3">
         <v>62</v>
       </c>
       <c r="N56" s="3">
-        <v>0.535496592522</v>
+        <v>0.53549659252199999</v>
       </c>
       <c r="O56" s="3">
-        <v>1.0592571497</v>
+        <v>1.0592571497000001</v>
       </c>
       <c r="P56" s="3">
-        <v>1673.95727539</v>
+        <v>1673.9572753899999</v>
       </c>
       <c r="Q56" s="3">
-        <v>9.40993404388</v>
+        <v>9.4099340438799999</v>
       </c>
       <c r="R56" s="3">
         <v>267.806884766</v>
       </c>
       <c r="S56" s="3">
-        <v>868.81048584</v>
+        <v>868.81048583999996</v>
       </c>
       <c r="T56" s="3">
-        <v>23.4245433807</v>
+        <v>23.424543380700001</v>
       </c>
       <c r="U56" s="3">
         <v>0.2</v>
       </c>
       <c r="V56" s="3">
-        <v>0.3522388</v>
+        <v>0.35223880000000002</v>
       </c>
       <c r="W56" s="3">
-        <v>177.0594</v>
+        <v>177.05940000000001</v>
       </c>
       <c r="X56" s="3">
         <v>271.7371</v>
       </c>
       <c r="Y56" s="3">
-        <v>0.780978977680206</v>
+        <v>0.78097897768020597</v>
       </c>
       <c r="Z56" s="1">
         <v>1.4</v>
@@ -6296,7 +5681,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="57" spans="1:27">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>19</v>
       </c>
@@ -6304,7 +5689,7 @@
         <v>112.8942</v>
       </c>
       <c r="C57" s="3">
-        <v>27.70836</v>
+        <v>27.708359999999999</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>90</v>
@@ -6337,40 +5722,40 @@
         <v>43</v>
       </c>
       <c r="N57" s="3">
-        <v>0.636824190617</v>
+        <v>0.63682419061700002</v>
       </c>
       <c r="O57" s="3">
-        <v>0.921826481819</v>
+        <v>0.92182648181899995</v>
       </c>
       <c r="P57" s="3">
-        <v>1213.03198242</v>
+        <v>1213.0319824200001</v>
       </c>
       <c r="Q57" s="3">
-        <v>8.96829128265</v>
+        <v>8.9682912826500001</v>
       </c>
       <c r="R57" s="3">
         <v>263.764160156</v>
       </c>
       <c r="S57" s="3">
-        <v>875.352294922</v>
+        <v>875.35229492200006</v>
       </c>
       <c r="T57" s="3">
-        <v>24.5428237915</v>
+        <v>24.542823791499998</v>
       </c>
       <c r="U57" s="3">
         <v>0.11</v>
       </c>
       <c r="V57" s="3">
-        <v>0.283619</v>
+        <v>0.28361900000000001</v>
       </c>
       <c r="W57" s="3">
-        <v>259.9765</v>
+        <v>259.97649999999999</v>
       </c>
       <c r="X57" s="3">
         <v>310.6395</v>
       </c>
       <c r="Y57" s="3">
-        <v>0.512463986873627</v>
+        <v>0.51246398687362704</v>
       </c>
       <c r="Z57" s="1">
         <v>0.32</v>
@@ -6379,7 +5764,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>21</v>
       </c>
@@ -6387,13 +5772,13 @@
         <v>113.01701</v>
       </c>
       <c r="C58" s="3">
-        <v>27.75614</v>
+        <v>27.756139999999998</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E58" s="3">
-        <v>18.1</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="F58" s="3">
         <v>99</v>
@@ -6420,40 +5805,40 @@
         <v>56</v>
       </c>
       <c r="N58" s="3">
-        <v>0.383149236441</v>
+        <v>0.38314923644100002</v>
       </c>
       <c r="O58" s="3">
-        <v>1.08896899223</v>
+        <v>1.0889689922300001</v>
       </c>
       <c r="P58" s="3">
-        <v>2041.93408203</v>
+        <v>2041.9340820299999</v>
       </c>
       <c r="Q58" s="3">
-        <v>9.39663505554</v>
+        <v>9.3966350555399991</v>
       </c>
       <c r="R58" s="3">
-        <v>273.135620117</v>
+        <v>273.13562011699997</v>
       </c>
       <c r="S58" s="3">
-        <v>838.831787109</v>
+        <v>838.83178710899995</v>
       </c>
       <c r="T58" s="3">
-        <v>21.3682518005</v>
+        <v>21.368251800500001</v>
       </c>
       <c r="U58" s="3">
         <v>0.12</v>
       </c>
       <c r="V58" s="3">
-        <v>0.321845</v>
+        <v>0.32184499999999999</v>
       </c>
       <c r="W58" s="3">
-        <v>139.3375</v>
+        <v>139.33750000000001</v>
       </c>
       <c r="X58" s="3">
-        <v>240.8662</v>
+        <v>240.86619999999999</v>
       </c>
       <c r="Y58" s="3">
-        <v>0.761415004730225</v>
+        <v>0.76141500473022505</v>
       </c>
       <c r="Z58" s="1">
         <v>1.8</v>
@@ -6462,7 +5847,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>22</v>
       </c>
@@ -6470,7 +5855,7 @@
         <v>112.834</v>
       </c>
       <c r="C59" s="3">
-        <v>27.70923</v>
+        <v>27.709230000000002</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>92</v>
@@ -6503,22 +5888,22 @@
         <v>40</v>
       </c>
       <c r="N59" s="3">
-        <v>0.687180936337</v>
+        <v>0.68718093633699995</v>
       </c>
       <c r="O59" s="3">
-        <v>0.71180421114</v>
+        <v>0.71180421114000003</v>
       </c>
       <c r="P59" s="3">
-        <v>1474.22729492</v>
+        <v>1474.2272949200001</v>
       </c>
       <c r="Q59" s="3">
-        <v>8.81491756439</v>
+        <v>8.8149175643900008</v>
       </c>
       <c r="R59" s="3">
-        <v>262.202270508</v>
+        <v>262.20227050800003</v>
       </c>
       <c r="S59" s="3">
-        <v>794.539733887</v>
+        <v>794.53973388700001</v>
       </c>
       <c r="T59" s="3">
         <v>21.1249275208</v>
@@ -6527,25 +5912,25 @@
         <v>0.19</v>
       </c>
       <c r="V59" s="3">
-        <v>0.3040874</v>
+        <v>0.30408740000000001</v>
       </c>
       <c r="W59" s="3">
-        <v>434.2852</v>
+        <v>434.28519999999997</v>
       </c>
       <c r="X59" s="3">
-        <v>246.223</v>
+        <v>246.22300000000001</v>
       </c>
       <c r="Y59" s="3">
-        <v>0.226870998740196</v>
+        <v>0.22687099874019601</v>
       </c>
       <c r="Z59" s="1">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>50</v>
       </c>
@@ -6553,7 +5938,7 @@
         <v>112.9032</v>
       </c>
       <c r="C60" s="3">
-        <v>27.7357</v>
+        <v>27.735700000000001</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>93</v>
@@ -6586,19 +5971,19 @@
         <v>46</v>
       </c>
       <c r="N60" s="3">
-        <v>0.609803378582</v>
+        <v>0.60980337858199996</v>
       </c>
       <c r="O60" s="3">
-        <v>1.11725139618</v>
+        <v>1.1172513961799999</v>
       </c>
       <c r="P60" s="3">
-        <v>1174.47802734</v>
+        <v>1174.4780273399999</v>
       </c>
       <c r="Q60" s="3">
-        <v>8.38449954987</v>
+        <v>8.3844995498700001</v>
       </c>
       <c r="R60" s="3">
-        <v>268.941467285</v>
+        <v>268.94146728499999</v>
       </c>
       <c r="S60" s="3">
         <v>1040.57324219</v>
@@ -6616,10 +6001,10 @@
         <v>195.8135</v>
       </c>
       <c r="X60" s="3">
-        <v>332.3568</v>
+        <v>332.35680000000002</v>
       </c>
       <c r="Y60" s="3">
-        <v>0.465604990720749</v>
+        <v>0.46560499072074901</v>
       </c>
       <c r="Z60" s="1">
         <v>0.54</v>
@@ -6628,7 +6013,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:27">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>90</v>
       </c>
@@ -6636,7 +6021,7 @@
         <v>112.86525</v>
       </c>
       <c r="C61" s="3">
-        <v>27.69947</v>
+        <v>27.699470000000002</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>94</v>
@@ -6663,28 +6048,28 @@
         <v>12</v>
       </c>
       <c r="L61" s="3">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M61" s="3">
         <v>36</v>
       </c>
       <c r="N61" s="3">
-        <v>0.661291122437</v>
+        <v>0.66129112243699995</v>
       </c>
       <c r="O61" s="3">
         <v>0.821081519127</v>
       </c>
       <c r="P61" s="3">
-        <v>1213.93139648</v>
+        <v>1213.9313964800001</v>
       </c>
       <c r="Q61" s="3">
-        <v>9.02133464813</v>
+        <v>9.0213346481300007</v>
       </c>
       <c r="R61" s="3">
-        <v>263.637969971</v>
+        <v>263.63796997100002</v>
       </c>
       <c r="S61" s="3">
-        <v>814.313171387</v>
+        <v>814.31317138700001</v>
       </c>
       <c r="T61" s="3">
         <v>23.9147720337</v>
@@ -6693,16 +6078,16 @@
         <v>0.15</v>
       </c>
       <c r="V61" s="3">
-        <v>0.2981924</v>
+        <v>0.29819240000000002</v>
       </c>
       <c r="W61" s="3">
-        <v>363.2049</v>
+        <v>363.20490000000001</v>
       </c>
       <c r="X61" s="3">
         <v>296.3707</v>
       </c>
       <c r="Y61" s="3">
-        <v>0.480020999908447</v>
+        <v>0.48002099990844699</v>
       </c>
       <c r="Z61" s="1">
         <v>0.37</v>
@@ -6711,7 +6096,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:27">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>91</v>
       </c>
@@ -6719,13 +6104,13 @@
         <v>112.95075</v>
       </c>
       <c r="C62" s="3">
-        <v>27.68678</v>
+        <v>27.686779999999999</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>95</v>
       </c>
       <c r="E62" s="3">
-        <v>9.3</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F62" s="3">
         <v>77</v>
@@ -6752,7 +6137,7 @@
         <v>56</v>
       </c>
       <c r="N62" s="3">
-        <v>0.674878537655</v>
+        <v>0.67487853765500005</v>
       </c>
       <c r="O62" s="3">
         <v>1.01815676689</v>
@@ -6761,13 +6146,13 @@
         <v>1207.22265625</v>
       </c>
       <c r="Q62" s="3">
-        <v>9.49544620514</v>
+        <v>9.4954462051400004</v>
       </c>
       <c r="R62" s="3">
-        <v>262.350524902</v>
+        <v>262.35052490200002</v>
       </c>
       <c r="S62" s="3">
-        <v>782.762817383</v>
+        <v>782.76281738299997</v>
       </c>
       <c r="T62" s="3">
         <v>26.0652103424</v>
@@ -6794,7 +6179,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="63" spans="1:27">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>92</v>
       </c>
@@ -6808,7 +6193,7 @@
         <v>96</v>
       </c>
       <c r="E63" s="3">
-        <v>17.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="F63" s="3">
         <v>54</v>
@@ -6835,40 +6220,40 @@
         <v>76</v>
       </c>
       <c r="N63" s="3">
-        <v>0.620311796665</v>
+        <v>0.62031179666500003</v>
       </c>
       <c r="O63" s="3">
-        <v>0.972128987312</v>
+        <v>0.97212898731200004</v>
       </c>
       <c r="P63" s="3">
         <v>1205.8458252</v>
       </c>
       <c r="Q63" s="3">
-        <v>9.27743244171</v>
+        <v>9.2774324417099994</v>
       </c>
       <c r="R63" s="3">
-        <v>262.804962158</v>
+        <v>262.80496215800002</v>
       </c>
       <c r="S63" s="3">
-        <v>821.570068359</v>
+        <v>821.57006835899995</v>
       </c>
       <c r="T63" s="3">
-        <v>25.1954975128</v>
+        <v>25.195497512799999</v>
       </c>
       <c r="U63" s="3">
         <v>0.23</v>
       </c>
       <c r="V63" s="3">
-        <v>0.2895552</v>
+        <v>0.28955520000000001</v>
       </c>
       <c r="W63" s="3">
-        <v>249.6171</v>
+        <v>249.61709999999999</v>
       </c>
       <c r="X63" s="3">
-        <v>310.6818</v>
+        <v>310.68180000000001</v>
       </c>
       <c r="Y63" s="3">
-        <v>0.608035981655121</v>
+        <v>0.60803598165512096</v>
       </c>
       <c r="Z63" s="1">
         <v>0.27</v>
@@ -6877,15 +6262,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:27">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>93</v>
       </c>
       <c r="B64" s="3">
-        <v>112.7065</v>
+        <v>112.70650000000001</v>
       </c>
       <c r="C64" s="3">
-        <v>27.51128</v>
+        <v>27.511279999999999</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>97</v>
@@ -6909,25 +6294,25 @@
         <v>60</v>
       </c>
       <c r="K64" s="3">
-        <v>9.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="L64" s="3">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M64" s="3">
         <v>36</v>
       </c>
       <c r="N64" s="3">
-        <v>0.281073123217</v>
+        <v>0.28107312321700001</v>
       </c>
       <c r="O64" s="3">
-        <v>0.589487850666</v>
+        <v>0.58948785066599996</v>
       </c>
       <c r="P64" s="3">
-        <v>2498.16430664</v>
+        <v>2498.1643066400002</v>
       </c>
       <c r="Q64" s="3">
-        <v>12.8220691681</v>
+        <v>12.822069168100001</v>
       </c>
       <c r="R64" s="3">
         <v>277.0105896</v>
@@ -6936,13 +6321,13 @@
         <v>688.391113281</v>
       </c>
       <c r="T64" s="3">
-        <v>18.1636734009</v>
+        <v>18.163673400899999</v>
       </c>
       <c r="U64" s="3">
         <v>0.18</v>
       </c>
       <c r="V64" s="3">
-        <v>0.2420306</v>
+        <v>0.24203060000000001</v>
       </c>
       <c r="W64" s="3">
         <v>1046.739</v>
@@ -6951,21 +6336,21 @@
         <v>145.4068</v>
       </c>
       <c r="Y64" s="3">
-        <v>0.251668006181717</v>
+        <v>0.25166800618171697</v>
       </c>
       <c r="Z64" s="1">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AA64" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="1:27">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>94</v>
       </c>
       <c r="B65" s="3">
-        <v>112.68425</v>
+        <v>112.68425000000001</v>
       </c>
       <c r="C65" s="3">
         <v>27.54851</v>
@@ -7010,7 +6395,7 @@
         <v>1830</v>
       </c>
       <c r="Q65" s="3">
-        <v>11.014</v>
+        <v>11.013999999999999</v>
       </c>
       <c r="R65" s="3">
         <v>287.399</v>
@@ -7019,10 +6404,10 @@
         <v>586</v>
       </c>
       <c r="T65" s="3">
-        <v>19.153</v>
+        <v>19.152999999999999</v>
       </c>
       <c r="U65" s="3">
-        <v>0.1777606</v>
+        <v>0.17776059999999999</v>
       </c>
       <c r="V65" s="3">
         <v>0.23</v>
@@ -7034,7 +6419,7 @@
         <v>143</v>
       </c>
       <c r="Y65" s="3">
-        <v>0.260134994983673</v>
+        <v>0.26013499498367298</v>
       </c>
       <c r="Z65" s="1">
         <v>0.95</v>
@@ -7043,7 +6428,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="66" spans="1:27">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>96</v>
       </c>
@@ -7051,7 +6436,7 @@
         <v>112.6596</v>
       </c>
       <c r="C66" s="3">
-        <v>27.60046</v>
+        <v>27.600460000000002</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>100</v>
@@ -7096,13 +6481,13 @@
         <v>15.987</v>
       </c>
       <c r="R66" s="3">
-        <v>263.598</v>
+        <v>263.59800000000001</v>
       </c>
       <c r="S66" s="3">
         <v>621</v>
       </c>
       <c r="T66" s="3">
-        <v>24.495</v>
+        <v>24.495000000000001</v>
       </c>
       <c r="U66" s="3">
         <v>0.59</v>
@@ -7117,7 +6502,7 @@
         <v>192</v>
       </c>
       <c r="Y66" s="3">
-        <v>0.368180990219116</v>
+        <v>0.36818099021911599</v>
       </c>
       <c r="Z66" s="1">
         <v>0.24</v>
@@ -7126,12 +6511,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:27">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>97</v>
       </c>
       <c r="B67" s="3">
-        <v>112.70341</v>
+        <v>112.70341000000001</v>
       </c>
       <c r="C67" s="3">
         <v>27.52769</v>
@@ -7167,13 +6552,13 @@
         <v>30</v>
       </c>
       <c r="N67" s="3">
-        <v>0.31048220396</v>
+        <v>0.31048220395999998</v>
       </c>
       <c r="O67" s="3">
-        <v>0.585233807564</v>
+        <v>0.58523380756400001</v>
       </c>
       <c r="P67" s="3">
-        <v>2137.97949219</v>
+        <v>2137.9794921900002</v>
       </c>
       <c r="Q67" s="3">
         <v>11.7898445129</v>
@@ -7182,42 +6567,42 @@
         <v>277.388427734</v>
       </c>
       <c r="S67" s="3">
-        <v>633.156311035</v>
+        <v>633.15631103500004</v>
       </c>
       <c r="T67" s="3">
-        <v>19.0655384064</v>
+        <v>19.065538406400002</v>
       </c>
       <c r="U67" s="3">
-        <v>0.1674898</v>
+        <v>0.16748979999999999</v>
       </c>
       <c r="V67" s="3">
-        <v>0.2216536</v>
+        <v>0.22165360000000001</v>
       </c>
       <c r="W67" s="3">
-        <v>748.1537</v>
+        <v>748.15369999999996</v>
       </c>
       <c r="X67" s="3">
         <v>156.9272</v>
       </c>
       <c r="Y67" s="3">
-        <v>0.317925006151199</v>
+        <v>0.31792500615119901</v>
       </c>
       <c r="Z67" s="1">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AA67" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:27">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>98</v>
       </c>
       <c r="B68" s="3">
-        <v>112.66661</v>
+        <v>112.66661000000001</v>
       </c>
       <c r="C68" s="3">
-        <v>27.58237</v>
+        <v>27.582370000000001</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>102</v>
@@ -7250,10 +6635,10 @@
         <v>38</v>
       </c>
       <c r="N68" s="3">
-        <v>0.433844715357</v>
+        <v>0.43384471535699998</v>
       </c>
       <c r="O68" s="3">
-        <v>0.817561030388</v>
+        <v>0.81756103038799999</v>
       </c>
       <c r="P68" s="3">
         <v>1247.31848145</v>
@@ -7262,25 +6647,25 @@
         <v>13.8229799271</v>
       </c>
       <c r="R68" s="3">
-        <v>273.617004395</v>
+        <v>273.61700439499998</v>
       </c>
       <c r="S68" s="3">
-        <v>554.739318848</v>
+        <v>554.73931884800004</v>
       </c>
       <c r="T68" s="3">
-        <v>22.7551307678</v>
+        <v>22.755130767800001</v>
       </c>
       <c r="U68" s="3">
         <v>0.13</v>
       </c>
       <c r="V68" s="3">
-        <v>0.3093614</v>
+        <v>0.30936140000000001</v>
       </c>
       <c r="W68" s="3">
-        <v>403.8905</v>
+        <v>403.89049999999997</v>
       </c>
       <c r="X68" s="3">
-        <v>182.0413</v>
+        <v>182.04130000000001</v>
       </c>
       <c r="Y68" s="3">
         <v>0.259656012058258</v>
@@ -7292,12 +6677,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="69" spans="1:27">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>99</v>
       </c>
       <c r="B69" s="3">
-        <v>112.63841</v>
+        <v>112.63840999999999</v>
       </c>
       <c r="C69" s="3">
         <v>27.60717</v>
@@ -7336,54 +6721,54 @@
         <v>0.474709689617</v>
       </c>
       <c r="O69" s="3">
-        <v>0.907478034496</v>
+        <v>0.90747803449599995</v>
       </c>
       <c r="P69" s="3">
-        <v>1064.31591797</v>
+        <v>1064.3159179700001</v>
       </c>
       <c r="Q69" s="3">
-        <v>14.6837673187</v>
+        <v>14.683767318699999</v>
       </c>
       <c r="R69" s="3">
-        <v>272.150939941</v>
+        <v>272.15093994099999</v>
       </c>
       <c r="S69" s="3">
-        <v>535.117614746</v>
+        <v>535.11761474599996</v>
       </c>
       <c r="T69" s="3">
-        <v>23.6507930756</v>
+        <v>23.650793075599999</v>
       </c>
       <c r="U69" s="3">
         <v>0.21</v>
       </c>
       <c r="V69" s="3">
-        <v>0.3378942</v>
+        <v>0.33789419999999998</v>
       </c>
       <c r="W69" s="3">
-        <v>316.3508</v>
+        <v>316.35079999999999</v>
       </c>
       <c r="X69" s="3">
-        <v>185.3788</v>
+        <v>185.37880000000001</v>
       </c>
       <c r="Y69" s="3">
-        <v>0.184643000364304</v>
+        <v>0.18464300036430401</v>
       </c>
       <c r="Z69" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA69" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="70" spans="1:27">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>118</v>
       </c>
       <c r="B70" s="3">
-        <v>112.6676</v>
+        <v>112.66759999999999</v>
       </c>
       <c r="C70" s="3">
-        <v>27.5796</v>
+        <v>27.579599999999999</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>104</v>
@@ -7416,37 +6801,37 @@
         <v>32</v>
       </c>
       <c r="N70" s="3">
-        <v>0.413986802101</v>
+        <v>0.41398680210099997</v>
       </c>
       <c r="O70" s="3">
-        <v>0.776284694672</v>
+        <v>0.77628469467200001</v>
       </c>
       <c r="P70" s="3">
-        <v>1318.12426758</v>
+        <v>1318.1242675799999</v>
       </c>
       <c r="Q70" s="3">
-        <v>13.413146019</v>
+        <v>13.413146018999999</v>
       </c>
       <c r="R70" s="3">
-        <v>274.929046631</v>
+        <v>274.92904663100001</v>
       </c>
       <c r="S70" s="3">
-        <v>548.864868164</v>
+        <v>548.86486816399997</v>
       </c>
       <c r="T70" s="3">
-        <v>22.3626441956</v>
+        <v>22.362644195600001</v>
       </c>
       <c r="U70" s="3">
         <v>0.17</v>
       </c>
       <c r="V70" s="3">
-        <v>0.2942076</v>
+        <v>0.29420760000000001</v>
       </c>
       <c r="W70" s="3">
-        <v>435.1754</v>
+        <v>435.17540000000002</v>
       </c>
       <c r="X70" s="3">
-        <v>179.4569</v>
+        <v>179.45689999999999</v>
       </c>
       <c r="Y70" s="3">
         <v>0.259656012058258</v>
@@ -7458,7 +6843,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="71" spans="1:27">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>95</v>
       </c>
@@ -7466,7 +6851,7 @@
         <v>112.5924</v>
       </c>
       <c r="C71" s="3">
-        <v>27.5030873</v>
+        <v>27.503087300000001</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>105</v>
@@ -7505,7 +6890,7 @@
         <v>1.05742776394</v>
       </c>
       <c r="P71" s="3">
-        <v>1333.51000977</v>
+        <v>1333.5100097699999</v>
       </c>
       <c r="Q71" s="3">
         <v>11.3118562698</v>
@@ -7517,19 +6902,19 @@
         <v>242.183105469</v>
       </c>
       <c r="T71" s="3">
-        <v>17.3279132843</v>
+        <v>17.327913284299999</v>
       </c>
       <c r="U71" s="3">
-        <v>0.1864299</v>
+        <v>0.18642990000000001</v>
       </c>
       <c r="V71" s="3">
-        <v>0.1869337</v>
+        <v>0.18693370000000001</v>
       </c>
       <c r="W71" s="3">
-        <v>266.6992</v>
+        <v>266.69920000000002</v>
       </c>
       <c r="X71" s="3">
-        <v>172.1331</v>
+        <v>172.13310000000001</v>
       </c>
       <c r="Y71" s="3">
         <v>0.24049299955368</v>
@@ -7541,7 +6926,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="72" spans="1:27">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>101</v>
       </c>
@@ -7549,13 +6934,13 @@
         <v>112.54892</v>
       </c>
       <c r="C72" s="3">
-        <v>27.49068</v>
+        <v>27.490680000000001</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>107</v>
       </c>
       <c r="E72" s="3">
-        <v>9.7</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F72" s="3">
         <v>54</v>
@@ -7582,13 +6967,13 @@
         <v>52</v>
       </c>
       <c r="N72" s="3">
-        <v>0.262535303831</v>
+        <v>0.26253530383099999</v>
       </c>
       <c r="O72" s="3">
-        <v>0.9884775877</v>
+        <v>0.98847758770000005</v>
       </c>
       <c r="P72" s="3">
-        <v>1239.92919922</v>
+        <v>1239.9291992200001</v>
       </c>
       <c r="Q72" s="3">
         <v>11.1413450241</v>
@@ -7600,7 +6985,7 @@
         <v>183.302825928</v>
       </c>
       <c r="T72" s="3">
-        <v>15.9423160553</v>
+        <v>15.942316055299999</v>
       </c>
       <c r="U72" s="3">
         <v>0.15</v>
@@ -7609,13 +6994,13 @@
         <v>0.1533003</v>
       </c>
       <c r="W72" s="3">
-        <v>205.0125</v>
+        <v>205.01249999999999</v>
       </c>
       <c r="X72" s="3">
-        <v>165.1868</v>
+        <v>165.18680000000001</v>
       </c>
       <c r="Y72" s="3">
-        <v>0.417097002267838</v>
+        <v>0.41709700226783802</v>
       </c>
       <c r="Z72" s="1">
         <v>0.2</v>
@@ -7624,7 +7009,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:27">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>102</v>
       </c>
@@ -7668,34 +7053,34 @@
         <v>0.32984700799</v>
       </c>
       <c r="O73" s="3">
-        <v>0.86085408926</v>
+        <v>0.86085408925999995</v>
       </c>
       <c r="P73" s="3">
         <v>2011.68151855</v>
       </c>
       <c r="Q73" s="3">
-        <v>11.3002500534</v>
+        <v>11.300250053399999</v>
       </c>
       <c r="R73" s="3">
-        <v>271.61630249</v>
+        <v>271.61630249000001</v>
       </c>
       <c r="S73" s="3">
-        <v>354.864715576</v>
+        <v>354.86471557599998</v>
       </c>
       <c r="T73" s="3">
-        <v>19.4064121246</v>
+        <v>19.406412124599999</v>
       </c>
       <c r="U73" s="3">
         <v>0.15</v>
       </c>
       <c r="V73" s="3">
-        <v>0.1923143</v>
+        <v>0.19231429999999999</v>
       </c>
       <c r="W73" s="3">
         <v>498.5412</v>
       </c>
       <c r="X73" s="3">
-        <v>164.1723</v>
+        <v>164.17230000000001</v>
       </c>
       <c r="Y73" s="3">
         <v>0.379088014364243</v>
@@ -7707,15 +7092,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="74" spans="1:27">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>103</v>
       </c>
       <c r="B74" s="3">
-        <v>112.56619</v>
+        <v>112.56619000000001</v>
       </c>
       <c r="C74" s="3">
-        <v>27.46878</v>
+        <v>27.468779999999999</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>109</v>
@@ -7748,22 +7133,22 @@
         <v>40</v>
       </c>
       <c r="N74" s="3">
-        <v>0.294825404882</v>
+        <v>0.29482540488199999</v>
       </c>
       <c r="O74" s="3">
         <v>1.09623503685</v>
       </c>
       <c r="P74" s="3">
-        <v>1312.87646484</v>
+        <v>1312.8764648399999</v>
       </c>
       <c r="Q74" s="3">
         <v>10.8386182785</v>
       </c>
       <c r="R74" s="3">
-        <v>255.226013184</v>
+        <v>255.22601318400001</v>
       </c>
       <c r="S74" s="3">
-        <v>221.93421936</v>
+        <v>221.93421935999999</v>
       </c>
       <c r="T74" s="3">
         <v>17.067199707</v>
@@ -7775,13 +7160,13 @@
         <v>0.1694358</v>
       </c>
       <c r="W74" s="3">
-        <v>269.4657</v>
+        <v>269.46570000000003</v>
       </c>
       <c r="X74" s="3">
-        <v>170.7891</v>
+        <v>170.78909999999999</v>
       </c>
       <c r="Y74" s="3">
-        <v>0.242581993341446</v>
+        <v>0.24258199334144601</v>
       </c>
       <c r="Z74" s="1">
         <v>0.01</v>
@@ -7790,7 +7175,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="75" spans="1:27">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>105</v>
       </c>
@@ -7798,7 +7183,7 @@
         <v>112.56541</v>
       </c>
       <c r="C75" s="3">
-        <v>27.49908</v>
+        <v>27.499079999999999</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>110</v>
@@ -7831,19 +7216,19 @@
         <v>53</v>
       </c>
       <c r="N75" s="3">
-        <v>0.297840744257</v>
+        <v>0.29784074425700002</v>
       </c>
       <c r="O75" s="3">
-        <v>1.36050546169</v>
+        <v>1.3605054616900001</v>
       </c>
       <c r="P75" s="3">
-        <v>1111.20922852</v>
+        <v>1111.2092285199999</v>
       </c>
       <c r="Q75" s="3">
-        <v>10.817404747</v>
+        <v>10.817404746999999</v>
       </c>
       <c r="R75" s="3">
-        <v>256.313568115</v>
+        <v>256.31356811500001</v>
       </c>
       <c r="S75" s="3">
         <v>141.274536133</v>
@@ -7852,10 +7237,10 @@
         <v>15.0040035248</v>
       </c>
       <c r="U75" s="3">
-        <v>0.2189612</v>
+        <v>0.21896119999999999</v>
       </c>
       <c r="V75" s="3">
-        <v>0.1668265</v>
+        <v>0.16682649999999999</v>
       </c>
       <c r="W75" s="3">
         <v>112.8085</v>
@@ -7864,7 +7249,7 @@
         <v>170.136</v>
       </c>
       <c r="Y75" s="3">
-        <v>0.250584989786148</v>
+        <v>0.25058498978614802</v>
       </c>
       <c r="Z75" s="1">
         <v>0.26</v>
@@ -7873,7 +7258,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:27">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>106</v>
       </c>
@@ -7881,7 +7266,7 @@
         <v>112.59841</v>
       </c>
       <c r="C76" s="3">
-        <v>27.4888</v>
+        <v>27.488800000000001</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>111</v>
@@ -7914,7 +7299,7 @@
         <v>34</v>
       </c>
       <c r="N76" s="3">
-        <v>0.298522591591</v>
+        <v>0.29852259159099997</v>
       </c>
       <c r="O76" s="3">
         <v>1.00396859646</v>
@@ -7923,31 +7308,31 @@
         <v>1435.35839844</v>
       </c>
       <c r="Q76" s="3">
-        <v>11.3010883331</v>
+        <v>11.301088333099999</v>
       </c>
       <c r="R76" s="3">
-        <v>255.158843994</v>
+        <v>255.15884399399999</v>
       </c>
       <c r="S76" s="3">
-        <v>272.502502441</v>
+        <v>272.50250244099999</v>
       </c>
       <c r="T76" s="3">
-        <v>17.7761211395</v>
+        <v>17.776121139499999</v>
       </c>
       <c r="U76" s="3">
-        <v>0.1912661</v>
+        <v>0.19126609999999999</v>
       </c>
       <c r="V76" s="3">
         <v>0.1884904</v>
       </c>
       <c r="W76" s="3">
-        <v>331.701</v>
+        <v>331.70100000000002</v>
       </c>
       <c r="X76" s="3">
         <v>171.203</v>
       </c>
       <c r="Y76" s="3">
-        <v>0.183366000652313</v>
+        <v>0.18336600065231301</v>
       </c>
       <c r="Z76" s="1">
         <v>0.31</v>
@@ -7956,7 +7341,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="77" spans="1:27">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>148</v>
       </c>
@@ -7964,7 +7349,7 @@
         <v>112.54252</v>
       </c>
       <c r="C77" s="3">
-        <v>27.44272</v>
+        <v>27.442720000000001</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>112</v>
@@ -8009,7 +7394,7 @@
         <v>9.51</v>
       </c>
       <c r="R77" s="3">
-        <v>275.314</v>
+        <v>275.31400000000002</v>
       </c>
       <c r="S77" s="3">
         <v>249</v>
@@ -8030,7 +7415,7 @@
         <v>175</v>
       </c>
       <c r="Y77" s="3">
-        <v>0.368831008672714</v>
+        <v>0.36883100867271401</v>
       </c>
       <c r="Z77" s="1">
         <v>0.47</v>
@@ -8039,15 +7424,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="78" spans="1:27">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>82</v>
       </c>
       <c r="B78" s="3">
-        <v>112.75906</v>
+        <v>112.75906000000001</v>
       </c>
       <c r="C78" s="3">
-        <v>27.61264</v>
+        <v>27.612639999999999</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>113</v>
@@ -8080,13 +7465,13 @@
         <v>33</v>
       </c>
       <c r="N78" s="3">
-        <v>0.347225904465</v>
+        <v>0.34722590446500001</v>
       </c>
       <c r="O78" s="3">
-        <v>0.7610232234</v>
+        <v>0.76102322339999995</v>
       </c>
       <c r="P78" s="3">
-        <v>1304.74633789</v>
+        <v>1304.7463378899999</v>
       </c>
       <c r="Q78" s="3">
         <v>10.3541908264</v>
@@ -8095,25 +7480,25 @@
         <v>270.006103516</v>
       </c>
       <c r="S78" s="3">
-        <v>501.926940918</v>
+        <v>501.92694091800001</v>
       </c>
       <c r="T78" s="3">
-        <v>23.0410251617</v>
+        <v>23.041025161699999</v>
       </c>
       <c r="U78" s="3">
         <v>0.19</v>
       </c>
       <c r="V78" s="3">
-        <v>0.2061131</v>
+        <v>0.20611309999999999</v>
       </c>
       <c r="W78" s="3">
-        <v>399.0749</v>
+        <v>399.07490000000001</v>
       </c>
       <c r="X78" s="3">
         <v>239.619</v>
       </c>
       <c r="Y78" s="3">
-        <v>0.368526995182037</v>
+        <v>0.36852699518203702</v>
       </c>
       <c r="Z78" s="1">
         <v>0.15</v>
@@ -8122,7 +7507,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="79" spans="1:27">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>107</v>
       </c>
@@ -8130,7 +7515,7 @@
         <v>112.72443</v>
       </c>
       <c r="C79" s="3">
-        <v>27.67872</v>
+        <v>27.678719999999998</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>115</v>
@@ -8163,19 +7548,19 @@
         <v>30</v>
       </c>
       <c r="N79" s="3">
-        <v>0.508787333965</v>
+        <v>0.50878733396499998</v>
       </c>
       <c r="O79" s="3">
-        <v>0.762378096581</v>
+        <v>0.76237809658099998</v>
       </c>
       <c r="P79" s="3">
-        <v>1126.09753418</v>
+        <v>1126.0975341799999</v>
       </c>
       <c r="Q79" s="3">
-        <v>11.6172904968</v>
+        <v>11.617290496800001</v>
       </c>
       <c r="R79" s="3">
-        <v>284.346984863</v>
+        <v>284.34698486299999</v>
       </c>
       <c r="S79" s="3">
         <v>618.37109375</v>
@@ -8187,16 +7572,16 @@
         <v>0.1</v>
       </c>
       <c r="V79" s="3">
-        <v>0.251871</v>
+        <v>0.25187100000000001</v>
       </c>
       <c r="W79" s="3">
-        <v>288.0223</v>
+        <v>288.02229999999997</v>
       </c>
       <c r="X79" s="3">
-        <v>215.2798</v>
+        <v>215.27979999999999</v>
       </c>
       <c r="Y79" s="3">
-        <v>0.279736012220383</v>
+        <v>0.27973601222038302</v>
       </c>
       <c r="Z79" s="1">
         <v>0.3</v>
@@ -8205,7 +7590,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="80" spans="1:27">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>108</v>
       </c>
@@ -8213,7 +7598,7 @@
         <v>112.88952</v>
       </c>
       <c r="C80" s="3">
-        <v>27.62492</v>
+        <v>27.624919999999999</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>116</v>
@@ -8249,7 +7634,7 @@
         <v>0.26</v>
       </c>
       <c r="O80" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P80" s="3">
         <v>983</v>
@@ -8264,19 +7649,19 @@
         <v>166</v>
       </c>
       <c r="T80" s="3">
-        <v>32.977</v>
+        <v>32.976999999999997</v>
       </c>
       <c r="U80" s="3">
         <v>0.18</v>
       </c>
       <c r="V80" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="W80" s="3">
         <v>153</v>
       </c>
       <c r="X80" s="3">
-        <v>277.0981</v>
+        <v>277.09809999999999</v>
       </c>
       <c r="Y80" s="3">
         <v>0.422039985656738</v>
@@ -8288,12 +7673,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="81" spans="1:27">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>109</v>
       </c>
       <c r="B81" s="3">
-        <v>112.79484</v>
+        <v>112.79483999999999</v>
       </c>
       <c r="C81" s="3">
         <v>27.63044</v>
@@ -8302,7 +7687,7 @@
         <v>117</v>
       </c>
       <c r="E81" s="3">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F81" s="3">
         <v>79</v>
@@ -8329,10 +7714,10 @@
         <v>37</v>
       </c>
       <c r="N81" s="3">
-        <v>0.473655611277</v>
+        <v>0.47365561127700001</v>
       </c>
       <c r="O81" s="3">
-        <v>0.816938638687</v>
+        <v>0.81693863868700001</v>
       </c>
       <c r="P81" s="3">
         <v>1294.11364746</v>
@@ -8341,22 +7726,22 @@
         <v>10.5409879684</v>
       </c>
       <c r="R81" s="3">
-        <v>266.013549805</v>
+        <v>266.01354980500003</v>
       </c>
       <c r="S81" s="3">
-        <v>545.068603516</v>
+        <v>545.06860351600005</v>
       </c>
       <c r="T81" s="3">
-        <v>23.2859230042</v>
+        <v>23.285923004200001</v>
       </c>
       <c r="U81" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="V81" s="3">
-        <v>0.246132</v>
+        <v>0.24613199999999999</v>
       </c>
       <c r="W81" s="3">
-        <v>411.4011</v>
+        <v>411.40109999999999</v>
       </c>
       <c r="X81" s="3">
         <v>230.3466</v>
@@ -8371,7 +7756,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="82" spans="1:27">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>110</v>
       </c>
@@ -8379,7 +7764,7 @@
         <v>112.8334</v>
       </c>
       <c r="C82" s="3">
-        <v>27.68276</v>
+        <v>27.682759999999998</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>118</v>
@@ -8421,16 +7806,16 @@
         <v>1092</v>
       </c>
       <c r="Q82" s="3">
-        <v>10.803</v>
+        <v>10.803000000000001</v>
       </c>
       <c r="R82" s="3">
-        <v>264.967</v>
+        <v>264.96699999999998</v>
       </c>
       <c r="S82" s="3">
         <v>575</v>
       </c>
       <c r="T82" s="3">
-        <v>24.155</v>
+        <v>24.155000000000001</v>
       </c>
       <c r="U82" s="3">
         <v>0.2</v>
@@ -8445,7 +7830,7 @@
         <v>288</v>
       </c>
       <c r="Y82" s="3">
-        <v>0.47775200009346</v>
+        <v>0.47775200009346003</v>
       </c>
       <c r="Z82" s="1">
         <v>0.19</v>
@@ -8454,15 +7839,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="83" spans="1:27">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>111</v>
       </c>
       <c r="B83" s="3">
-        <v>112.7429</v>
+        <v>112.74290000000001</v>
       </c>
       <c r="C83" s="3">
-        <v>27.67684</v>
+        <v>27.676839999999999</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>119</v>
@@ -8495,10 +7880,10 @@
         <v>28</v>
       </c>
       <c r="N83" s="3">
-        <v>0.51544547081</v>
+        <v>0.51544547081000003</v>
       </c>
       <c r="O83" s="3">
-        <v>0.76662003994</v>
+        <v>0.76662003994000005</v>
       </c>
       <c r="P83" s="3">
         <v>1188.6126709</v>
@@ -8510,25 +7895,25 @@
         <v>276.640716553</v>
       </c>
       <c r="S83" s="3">
-        <v>655.410217285</v>
+        <v>655.41021728500004</v>
       </c>
       <c r="T83" s="3">
-        <v>22.8936100006</v>
+        <v>22.893610000599999</v>
       </c>
       <c r="U83" s="3">
         <v>0.1522087</v>
       </c>
       <c r="V83" s="3">
-        <v>0.2547472</v>
+        <v>0.25474720000000001</v>
       </c>
       <c r="W83" s="3">
-        <v>296.0871</v>
+        <v>296.08710000000002</v>
       </c>
       <c r="X83" s="3">
-        <v>225.1715</v>
+        <v>225.17150000000001</v>
       </c>
       <c r="Y83" s="3">
-        <v>0.220991998910904</v>
+        <v>0.22099199891090399</v>
       </c>
       <c r="Z83" s="1">
         <v>0.01</v>
@@ -8537,7 +7922,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="84" spans="1:27">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>120</v>
       </c>
@@ -8545,7 +7930,7 @@
         <v>112.89604</v>
       </c>
       <c r="C84" s="3">
-        <v>27.61292</v>
+        <v>27.612919999999999</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>120</v>
@@ -8578,22 +7963,22 @@
         <v>40</v>
       </c>
       <c r="N84" s="3">
-        <v>0.335850059986</v>
+        <v>0.33585005998599998</v>
       </c>
       <c r="O84" s="3">
-        <v>1.07339215279</v>
+        <v>1.0733921527900001</v>
       </c>
       <c r="P84" s="3">
-        <v>993.895812988</v>
+        <v>993.89581298799999</v>
       </c>
       <c r="Q84" s="3">
         <v>10.7238769531</v>
       </c>
       <c r="R84" s="3">
-        <v>255.464706421</v>
+        <v>255.46470642099999</v>
       </c>
       <c r="S84" s="3">
-        <v>216.083679199</v>
+        <v>216.08367919899999</v>
       </c>
       <c r="T84" s="3">
         <v>31.1340808868</v>
@@ -8608,19 +7993,19 @@
         <v>191.5513</v>
       </c>
       <c r="X84" s="3">
-        <v>277.3917</v>
+        <v>277.39170000000001</v>
       </c>
       <c r="Y84" s="3">
-        <v>0.529646992683411</v>
+        <v>0.52964699268341098</v>
       </c>
       <c r="Z84" s="1">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA84" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="85" spans="1:27">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>125</v>
       </c>
@@ -8628,7 +8013,7 @@
         <v>112.90831</v>
       </c>
       <c r="C85" s="3">
-        <v>27.62523</v>
+        <v>27.625229999999998</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>121</v>
@@ -8664,28 +8049,28 @@
         <v>0.384719997644</v>
       </c>
       <c r="O85" s="3">
-        <v>1.06298160553</v>
+        <v>1.0629816055300001</v>
       </c>
       <c r="P85" s="3">
-        <v>996.233947754</v>
+        <v>996.23394775400004</v>
       </c>
       <c r="Q85" s="3">
-        <v>10.655582428</v>
+        <v>10.655582428000001</v>
       </c>
       <c r="R85" s="3">
-        <v>256.128570557</v>
+        <v>256.12857055699999</v>
       </c>
       <c r="S85" s="3">
-        <v>241.750030518</v>
+        <v>241.75003051799999</v>
       </c>
       <c r="T85" s="3">
-        <v>30.755947113</v>
+        <v>30.755947113000001</v>
       </c>
       <c r="U85" s="3">
         <v>0.19</v>
       </c>
       <c r="V85" s="3">
-        <v>0.2123241</v>
+        <v>0.21232409999999999</v>
       </c>
       <c r="W85" s="3">
         <v>194.9007</v>
@@ -8694,24 +8079,24 @@
         <v>280.0385</v>
       </c>
       <c r="Y85" s="3">
-        <v>0.410513997077942</v>
+        <v>0.41051399707794201</v>
       </c>
       <c r="Z85" s="1">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA85" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="86" spans="1:27">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>132</v>
       </c>
       <c r="B86" s="3">
-        <v>112.856</v>
+        <v>112.85599999999999</v>
       </c>
       <c r="C86" s="3">
-        <v>27.647</v>
+        <v>27.646999999999998</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>122</v>
@@ -8738,22 +8123,22 @@
         <v>24</v>
       </c>
       <c r="L86" s="3">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M86" s="3">
         <v>32</v>
       </c>
       <c r="N86" s="3">
-        <v>0.516885995865</v>
+        <v>0.51688599586499995</v>
       </c>
       <c r="O86" s="3">
         <v>0.949348270893</v>
       </c>
       <c r="P86" s="3">
-        <v>1124.37451172</v>
+        <v>1124.3745117200001</v>
       </c>
       <c r="Q86" s="3">
-        <v>10.0970954895</v>
+        <v>10.097095489499999</v>
       </c>
       <c r="R86" s="3">
         <v>258.847747803</v>
@@ -8762,16 +8147,16 @@
         <v>501.511230469</v>
       </c>
       <c r="T86" s="3">
-        <v>26.6666870117</v>
+        <v>26.666687011699999</v>
       </c>
       <c r="U86" s="3">
         <v>0.77</v>
       </c>
       <c r="V86" s="3">
-        <v>0.2532541</v>
+        <v>0.25325409999999998</v>
       </c>
       <c r="W86" s="3">
-        <v>299.2215</v>
+        <v>299.22149999999999</v>
       </c>
       <c r="X86" s="3">
         <v>273.1576</v>
@@ -8786,7 +8171,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="87" spans="1:27">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>100</v>
       </c>
@@ -8857,10 +8242,10 @@
         <v>102</v>
       </c>
       <c r="X87" s="3">
-        <v>170.4987</v>
+        <v>170.49870000000001</v>
       </c>
       <c r="Y87" s="3">
-        <v>0.376370012760162</v>
+        <v>0.37637001276016202</v>
       </c>
       <c r="Z87" s="1">
         <v>1.5</v>
@@ -8869,7 +8254,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="88" spans="1:27">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>104</v>
       </c>
@@ -8877,7 +8262,7 @@
         <v>112.5273</v>
       </c>
       <c r="C88" s="3">
-        <v>27.49675</v>
+        <v>27.496749999999999</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>125</v>
@@ -8910,22 +8295,22 @@
         <v>42</v>
       </c>
       <c r="N88" s="3">
-        <v>0.143541052938</v>
+        <v>0.14354105293800001</v>
       </c>
       <c r="O88" s="3">
-        <v>0.25300347805</v>
+        <v>0.25300347805000001</v>
       </c>
       <c r="P88" s="3">
         <v>1349.89245605</v>
       </c>
       <c r="Q88" s="3">
-        <v>12.0645217896</v>
+        <v>12.064521789600001</v>
       </c>
       <c r="R88" s="3">
-        <v>228.474258423</v>
+        <v>228.47425842300001</v>
       </c>
       <c r="S88" s="3">
-        <v>189.435943604</v>
+        <v>189.43594360399999</v>
       </c>
       <c r="T88" s="3">
         <v>14.4676895142</v>
@@ -8940,19 +8325,19 @@
         <v>316.3202</v>
       </c>
       <c r="X88" s="3">
-        <v>152.39</v>
+        <v>152.38999999999999</v>
       </c>
       <c r="Y88" s="3">
-        <v>0.246365994215012</v>
+        <v>0.24636599421501201</v>
       </c>
       <c r="Z88" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA88" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="89" spans="1:27">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>113</v>
       </c>
@@ -8993,13 +8378,13 @@
         <v>29</v>
       </c>
       <c r="N89" s="3">
-        <v>0.221434146166</v>
+        <v>0.22143414616599999</v>
       </c>
       <c r="O89" s="3">
         <v>0.638826489449</v>
       </c>
       <c r="P89" s="3">
-        <v>1462.48022461</v>
+        <v>1462.4802246100001</v>
       </c>
       <c r="Q89" s="3">
         <v>11.0146980286</v>
@@ -9008,19 +8393,19 @@
         <v>231.816116333</v>
       </c>
       <c r="S89" s="3">
-        <v>208.994613647</v>
+        <v>208.99461364699999</v>
       </c>
       <c r="T89" s="3">
-        <v>18.1130714417</v>
+        <v>18.113071441700001</v>
       </c>
       <c r="U89" s="3">
-        <v>0.1860893</v>
+        <v>0.18608930000000001</v>
       </c>
       <c r="V89" s="3">
-        <v>0.1412309</v>
+        <v>0.14123089999999999</v>
       </c>
       <c r="W89" s="3">
-        <v>323.2113</v>
+        <v>323.21129999999999</v>
       </c>
       <c r="X89" s="3">
         <v>152.4282</v>
@@ -9035,7 +8420,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="90" spans="1:27">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>114</v>
       </c>
@@ -9043,7 +8428,7 @@
         <v>112.52386</v>
       </c>
       <c r="C90" s="3">
-        <v>27.49854</v>
+        <v>27.498539999999998</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>127</v>
@@ -9088,7 +8473,7 @@
         <v>12.378</v>
       </c>
       <c r="R90" s="3">
-        <v>226.253</v>
+        <v>226.25299999999999</v>
       </c>
       <c r="S90" s="3">
         <v>183</v>
@@ -9106,10 +8491,10 @@
         <v>323</v>
       </c>
       <c r="X90" s="3">
-        <v>150.2211</v>
+        <v>150.22110000000001</v>
       </c>
       <c r="Y90" s="3">
-        <v>0.303734987974167</v>
+        <v>0.30373498797416698</v>
       </c>
       <c r="Z90" s="1">
         <v>0.96</v>
@@ -9118,7 +8503,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="91" spans="1:27">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>115</v>
       </c>
@@ -9126,7 +8511,7 @@
         <v>112.51012</v>
       </c>
       <c r="C91" s="3">
-        <v>27.49285</v>
+        <v>27.492850000000001</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>128</v>
@@ -9168,7 +8553,7 @@
         <v>1212</v>
       </c>
       <c r="Q91" s="3">
-        <v>10.374</v>
+        <v>10.374000000000001</v>
       </c>
       <c r="R91" s="3">
         <v>228.447</v>
@@ -9180,7 +8565,7 @@
         <v>17.337</v>
       </c>
       <c r="U91" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="V91" s="3">
         <v>0.17</v>
@@ -9201,7 +8586,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="92" spans="1:27">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>116</v>
       </c>
@@ -9209,13 +8594,13 @@
         <v>112.46529</v>
       </c>
       <c r="C92" s="3">
-        <v>27.5298</v>
+        <v>27.529800000000002</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>129</v>
       </c>
       <c r="E92" s="3">
-        <v>9.7</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F92" s="3">
         <v>59</v>
@@ -9242,19 +8627,19 @@
         <v>45</v>
       </c>
       <c r="N92" s="3">
-        <v>0.253878563643</v>
+        <v>0.25387856364299999</v>
       </c>
       <c r="O92" s="3">
-        <v>0.591655433178</v>
+        <v>0.59165543317799996</v>
       </c>
       <c r="P92" s="3">
         <v>1623.60388184</v>
       </c>
       <c r="Q92" s="3">
-        <v>11.0254554749</v>
+        <v>11.025455474899999</v>
       </c>
       <c r="R92" s="3">
-        <v>231.55758667</v>
+        <v>231.55758667000001</v>
       </c>
       <c r="S92" s="3">
         <v>197.685836792</v>
@@ -9269,13 +8654,13 @@
         <v>0.1239845</v>
       </c>
       <c r="W92" s="3">
-        <v>310.9052</v>
+        <v>310.90519999999998</v>
       </c>
       <c r="X92" s="3">
         <v>162.2696</v>
       </c>
       <c r="Y92" s="3">
-        <v>0.270305007696152</v>
+        <v>0.27030500769615201</v>
       </c>
       <c r="Z92" s="1">
         <v>0.54</v>
@@ -9284,7 +8669,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="93" spans="1:27">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>117</v>
       </c>
@@ -9325,7 +8710,7 @@
         <v>53</v>
       </c>
       <c r="N93" s="3">
-        <v>0.230895236135</v>
+        <v>0.23089523613499999</v>
       </c>
       <c r="O93" s="3">
         <v>0.49</v>
@@ -9334,16 +8719,16 @@
         <v>1856</v>
       </c>
       <c r="Q93" s="3">
-        <v>10.867</v>
+        <v>10.867000000000001</v>
       </c>
       <c r="R93" s="3">
-        <v>227.121</v>
+        <v>227.12100000000001</v>
       </c>
       <c r="S93" s="3">
         <v>180</v>
       </c>
       <c r="T93" s="3">
-        <v>20.861</v>
+        <v>20.861000000000001</v>
       </c>
       <c r="U93" s="3">
         <v>0.16</v>
@@ -9355,10 +8740,10 @@
         <v>335</v>
       </c>
       <c r="X93" s="3">
-        <v>159.4951</v>
+        <v>159.49510000000001</v>
       </c>
       <c r="Y93" s="3">
-        <v>0.458346992731094</v>
+        <v>0.45834699273109403</v>
       </c>
       <c r="Z93" s="1">
         <v>0.35</v>
@@ -9367,7 +8752,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="94" spans="1:27">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>24</v>
       </c>
@@ -9375,7 +8760,7 @@
         <v>112.6538</v>
       </c>
       <c r="C94" s="3">
-        <v>27.7672</v>
+        <v>27.767199999999999</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>131</v>
@@ -9408,22 +8793,22 @@
         <v>31</v>
       </c>
       <c r="N94" s="3">
-        <v>0.580049216747</v>
+        <v>0.58004921674700005</v>
       </c>
       <c r="O94" s="3">
         <v>0.846654117107</v>
       </c>
       <c r="P94" s="3">
-        <v>1121.21069336</v>
+        <v>1121.2106933600001</v>
       </c>
       <c r="Q94" s="3">
         <v>11.4852495193</v>
       </c>
       <c r="R94" s="3">
-        <v>270.351165771</v>
+        <v>270.35116577100001</v>
       </c>
       <c r="S94" s="3">
-        <v>681.541381836</v>
+        <v>681.54138183600003</v>
       </c>
       <c r="T94" s="3">
         <v>22.5580730438</v>
@@ -9432,16 +8817,16 @@
         <v>0.12</v>
       </c>
       <c r="V94" s="3">
-        <v>0.267884</v>
+        <v>0.26788400000000001</v>
       </c>
       <c r="W94" s="3">
-        <v>203.873</v>
+        <v>203.87299999999999</v>
       </c>
       <c r="X94" s="3">
         <v>189.4427</v>
       </c>
       <c r="Y94" s="3">
-        <v>0.3299820125103</v>
+        <v>0.32998201251030002</v>
       </c>
       <c r="Z94" s="1">
         <v>0.5</v>
@@ -9450,15 +8835,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="95" spans="1:27">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>25</v>
       </c>
       <c r="B95" s="3">
-        <v>112.7095</v>
+        <v>112.70950000000001</v>
       </c>
       <c r="C95" s="3">
-        <v>27.7977</v>
+        <v>27.797699999999999</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>133</v>
@@ -9503,16 +8888,16 @@
         <v>10.215</v>
       </c>
       <c r="R95" s="3">
-        <v>269.192</v>
+        <v>269.19200000000001</v>
       </c>
       <c r="S95" s="3">
         <v>303</v>
       </c>
       <c r="T95" s="3">
-        <v>22.534</v>
+        <v>22.533999999999999</v>
       </c>
       <c r="U95" s="3">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="V95" s="3">
         <v>0.27</v>
@@ -9521,10 +8906,10 @@
         <v>302</v>
       </c>
       <c r="X95" s="3">
-        <v>291.5825</v>
+        <v>291.58249999999998</v>
       </c>
       <c r="Y95" s="3">
-        <v>0.340286999940872</v>
+        <v>0.34028699994087203</v>
       </c>
       <c r="Z95" s="1">
         <v>0.39</v>
@@ -9533,7 +8918,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="96" spans="1:27">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>26</v>
       </c>
@@ -9541,7 +8926,7 @@
         <v>112.7295</v>
       </c>
       <c r="C96" s="3">
-        <v>27.7417</v>
+        <v>27.741700000000002</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>134</v>
@@ -9574,22 +8959,22 @@
         <v>21</v>
       </c>
       <c r="N96" s="3">
-        <v>0.630741596222</v>
+        <v>0.63074159622199999</v>
       </c>
       <c r="O96" s="3">
         <v>0.896828949451</v>
       </c>
       <c r="P96" s="3">
-        <v>1202.21020508</v>
+        <v>1202.2102050799999</v>
       </c>
       <c r="Q96" s="3">
         <v>11.4134864807</v>
       </c>
       <c r="R96" s="3">
-        <v>266.50100708</v>
+        <v>266.50100708000002</v>
       </c>
       <c r="S96" s="3">
-        <v>1252.63330078</v>
+        <v>1252.6333007799999</v>
       </c>
       <c r="T96" s="3">
         <v>22.3031177521</v>
@@ -9598,10 +8983,10 @@
         <v>0.2169314</v>
       </c>
       <c r="V96" s="3">
-        <v>0.2911484</v>
+        <v>0.29114839999999997</v>
       </c>
       <c r="W96" s="3">
-        <v>232.9397</v>
+        <v>232.93969999999999</v>
       </c>
       <c r="X96" s="3">
         <v>302.1327</v>
@@ -9616,7 +9001,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="97" spans="1:27">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>27</v>
       </c>
@@ -9624,7 +9009,7 @@
         <v>112.675</v>
       </c>
       <c r="C97" s="3">
-        <v>27.8055</v>
+        <v>27.805499999999999</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>135</v>
@@ -9669,7 +9054,7 @@
         <v>11.871</v>
       </c>
       <c r="R97" s="3">
-        <v>272.743</v>
+        <v>272.74299999999999</v>
       </c>
       <c r="S97" s="3">
         <v>500</v>
@@ -9678,7 +9063,7 @@
         <v>18.82</v>
       </c>
       <c r="U97" s="3">
-        <v>0.2138152</v>
+        <v>0.21381520000000001</v>
       </c>
       <c r="V97" s="3">
         <v>0.26</v>
@@ -9699,7 +9084,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="98" spans="1:27">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>28</v>
       </c>
@@ -9740,10 +9125,10 @@
         <v>42</v>
       </c>
       <c r="N98" s="3">
-        <v>0.610955715179</v>
+        <v>0.61095571517900005</v>
       </c>
       <c r="O98" s="3">
-        <v>0.999259352684</v>
+        <v>0.99925935268400001</v>
       </c>
       <c r="P98" s="3">
         <v>1179.84338379</v>
@@ -9752,28 +9137,28 @@
         <v>11.139755249</v>
       </c>
       <c r="R98" s="3">
-        <v>267.182159424</v>
+        <v>267.18215942400002</v>
       </c>
       <c r="S98" s="3">
-        <v>986.108337402</v>
+        <v>986.10833740199996</v>
       </c>
       <c r="T98" s="3">
-        <v>22.1063404083</v>
+        <v>22.106340408299999</v>
       </c>
       <c r="U98" s="3">
         <v>0.34</v>
       </c>
       <c r="V98" s="3">
-        <v>0.2923271</v>
+        <v>0.29232710000000001</v>
       </c>
       <c r="W98" s="3">
-        <v>239.4839</v>
+        <v>239.48390000000001</v>
       </c>
       <c r="X98" s="3">
-        <v>293.2325</v>
+        <v>293.23250000000002</v>
       </c>
       <c r="Y98" s="3">
-        <v>0.350219011306763</v>
+        <v>0.35021901130676297</v>
       </c>
       <c r="Z98" s="1">
         <v>0.25</v>
@@ -9782,15 +9167,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="99" spans="1:27">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>119</v>
       </c>
       <c r="B99" s="3">
-        <v>112.94214</v>
+        <v>112.94213999999999</v>
       </c>
       <c r="C99" s="3">
-        <v>27.62628</v>
+        <v>27.626280000000001</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>137</v>
@@ -9823,54 +9208,54 @@
         <v>53</v>
       </c>
       <c r="N99" s="3">
-        <v>0.799803316593</v>
+        <v>0.79980331659299997</v>
       </c>
       <c r="O99" s="3">
-        <v>0.982678890228</v>
+        <v>0.98267889022800003</v>
       </c>
       <c r="P99" s="3">
-        <v>969.42980957</v>
+        <v>969.42980956999997</v>
       </c>
       <c r="Q99" s="3">
         <v>10.3912572861</v>
       </c>
       <c r="R99" s="3">
-        <v>259.834594727</v>
+        <v>259.83459472700002</v>
       </c>
       <c r="S99" s="3">
-        <v>383.686737061</v>
+        <v>383.68673706099997</v>
       </c>
       <c r="T99" s="3">
-        <v>28.5531578064</v>
+        <v>28.553157806400002</v>
       </c>
       <c r="U99" s="3">
         <v>0.21</v>
       </c>
       <c r="V99" s="3">
-        <v>0.4650556</v>
+        <v>0.46505560000000001</v>
       </c>
       <c r="W99" s="3">
-        <v>210.4455</v>
+        <v>210.44550000000001</v>
       </c>
       <c r="X99" s="3">
         <v>287.5086</v>
       </c>
       <c r="Y99" s="3">
-        <v>0.773132979869843</v>
+        <v>0.77313297986984297</v>
       </c>
       <c r="Z99" s="1">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AA99" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="100" spans="1:27">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>121</v>
       </c>
       <c r="B100" s="3">
-        <v>112.98659</v>
+        <v>112.98659000000001</v>
       </c>
       <c r="C100" s="3">
         <v>27.61148</v>
@@ -9918,7 +9303,7 @@
         <v>11.026</v>
       </c>
       <c r="R100" s="3">
-        <v>257.415</v>
+        <v>257.41500000000002</v>
       </c>
       <c r="S100" s="3">
         <v>404</v>
@@ -9939,7 +9324,7 @@
         <v>296</v>
       </c>
       <c r="Y100" s="3">
-        <v>0.604122996330261</v>
+        <v>0.60412299633026101</v>
       </c>
       <c r="Z100" s="1">
         <v>0.65</v>
@@ -9948,15 +9333,15 @@
         <v>138</v>
       </c>
     </row>
-    <row r="101" spans="1:27">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>122</v>
       </c>
       <c r="B101" s="3">
-        <v>112.91836</v>
+        <v>112.91836000000001</v>
       </c>
       <c r="C101" s="3">
-        <v>27.64627</v>
+        <v>27.646270000000001</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>140</v>
@@ -9980,7 +9365,7 @@
         <v>81</v>
       </c>
       <c r="K101" s="3">
-        <v>9.3</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="L101" s="3">
         <v>0.59</v>
@@ -9989,19 +9374,19 @@
         <v>41</v>
       </c>
       <c r="N101" s="3">
-        <v>0.518303513527</v>
+        <v>0.51830351352699999</v>
       </c>
       <c r="O101" s="3">
         <v>1.01620900631</v>
       </c>
       <c r="P101" s="3">
-        <v>1068.63500977</v>
+        <v>1068.6350097699999</v>
       </c>
       <c r="Q101" s="3">
-        <v>10.2585411072</v>
+        <v>10.258541107199999</v>
       </c>
       <c r="R101" s="3">
-        <v>258.16595459</v>
+        <v>258.16595459000001</v>
       </c>
       <c r="S101" s="3">
         <v>455.275482178</v>
@@ -10013,16 +9398,16 @@
         <v>0.25</v>
       </c>
       <c r="V101" s="3">
-        <v>0.2881041</v>
+        <v>0.28810409999999997</v>
       </c>
       <c r="W101" s="3">
-        <v>217.4596</v>
+        <v>217.45959999999999</v>
       </c>
       <c r="X101" s="3">
-        <v>287.0707</v>
+        <v>287.07069999999999</v>
       </c>
       <c r="Y101" s="3">
-        <v>0.483709990978241</v>
+        <v>0.48370999097824102</v>
       </c>
       <c r="Z101" s="1">
         <v>0.2</v>
@@ -10031,7 +9416,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="102" spans="1:27">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>123</v>
       </c>
@@ -10039,7 +9424,7 @@
         <v>112.90384</v>
       </c>
       <c r="C102" s="3">
-        <v>27.66336</v>
+        <v>27.663360000000001</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>141</v>
@@ -10072,19 +9457,19 @@
         <v>49</v>
       </c>
       <c r="N102" s="3">
-        <v>0.520785927773</v>
+        <v>0.52078592777300003</v>
       </c>
       <c r="O102" s="3">
-        <v>0.994712233543</v>
+        <v>0.99471223354299998</v>
       </c>
       <c r="P102" s="3">
         <v>1128.5291748</v>
       </c>
       <c r="Q102" s="3">
-        <v>9.97568321228</v>
+        <v>9.9756832122799999</v>
       </c>
       <c r="R102" s="3">
-        <v>258.864929199</v>
+        <v>258.86492919900002</v>
       </c>
       <c r="S102" s="3">
         <v>553.836425781</v>
@@ -10096,16 +9481,16 @@
         <v>0.27</v>
       </c>
       <c r="V102" s="3">
-        <v>0.2674361</v>
+        <v>0.26743610000000001</v>
       </c>
       <c r="W102" s="3">
-        <v>238.902</v>
+        <v>238.90199999999999</v>
       </c>
       <c r="X102" s="3">
         <v>289.1379</v>
       </c>
       <c r="Y102" s="3">
-        <v>0.539444983005524</v>
+        <v>0.53944498300552401</v>
       </c>
       <c r="Z102" s="1">
         <v>1.7</v>
@@ -10114,7 +9499,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="103" spans="1:27">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>124</v>
       </c>
@@ -10122,7 +9507,7 @@
         <v>113.0132</v>
       </c>
       <c r="C103" s="3">
-        <v>27.62732</v>
+        <v>27.627320000000001</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>142</v>
@@ -10149,7 +9534,7 @@
         <v>24</v>
       </c>
       <c r="L103" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M103" s="3">
         <v>46</v>
@@ -10158,34 +9543,34 @@
         <v>1.16855418682</v>
       </c>
       <c r="O103" s="3">
-        <v>0.965763270855</v>
+        <v>0.96576327085500002</v>
       </c>
       <c r="P103" s="3">
-        <v>846.685241699</v>
+        <v>846.68524169900002</v>
       </c>
       <c r="Q103" s="3">
-        <v>10.7219009399</v>
+        <v>10.721900939899999</v>
       </c>
       <c r="R103" s="3">
-        <v>259.716369629</v>
+        <v>259.71636962899998</v>
       </c>
       <c r="S103" s="3">
-        <v>413.268280029</v>
+        <v>413.26828002899998</v>
       </c>
       <c r="T103" s="3">
-        <v>29.4829025269</v>
+        <v>29.482902526899998</v>
       </c>
       <c r="U103" s="3">
         <v>0.24</v>
       </c>
       <c r="V103" s="3">
-        <v>0.663363</v>
+        <v>0.66336300000000004</v>
       </c>
       <c r="W103" s="3">
         <v>166.7938</v>
       </c>
       <c r="X103" s="3">
-        <v>291.8746</v>
+        <v>291.87459999999999</v>
       </c>
       <c r="Y103" s="3">
         <v>0.718195021152496</v>
@@ -10197,7 +9582,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="104" spans="1:27">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>126</v>
       </c>
@@ -10238,40 +9623,40 @@
         <v>46</v>
       </c>
       <c r="N104" s="3">
-        <v>0.993414223194</v>
+        <v>0.99341422319399997</v>
       </c>
       <c r="O104" s="3">
         <v>0.975552737713</v>
       </c>
       <c r="P104" s="3">
-        <v>870.058959961</v>
+        <v>870.05895996100003</v>
       </c>
       <c r="Q104" s="3">
         <v>10.592959404</v>
       </c>
       <c r="R104" s="3">
-        <v>259.355926514</v>
+        <v>259.35592651399998</v>
       </c>
       <c r="S104" s="3">
-        <v>380.97668457</v>
+        <v>380.97668456999997</v>
       </c>
       <c r="T104" s="3">
-        <v>29.0520744324</v>
+        <v>29.052074432400001</v>
       </c>
       <c r="U104" s="3">
         <v>0.2</v>
       </c>
       <c r="V104" s="3">
-        <v>0.5734291</v>
+        <v>0.57342910000000002</v>
       </c>
       <c r="W104" s="3">
         <v>194.4837</v>
       </c>
       <c r="X104" s="3">
-        <v>289.1575</v>
+        <v>289.15750000000003</v>
       </c>
       <c r="Y104" s="3">
-        <v>0.766700029373169</v>
+        <v>0.76670002937316895</v>
       </c>
       <c r="Z104" s="1">
         <v>0.38</v>
@@ -10280,7 +9665,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="105" spans="1:27">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>127</v>
       </c>
@@ -10294,7 +9679,7 @@
         <v>144</v>
       </c>
       <c r="E105" s="3">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="F105" s="3">
         <v>57</v>
@@ -10321,22 +9706,22 @@
         <v>49</v>
       </c>
       <c r="N105" s="3">
-        <v>0.973695933819</v>
+        <v>0.97369593381899999</v>
       </c>
       <c r="O105" s="3">
-        <v>0.978244781494</v>
+        <v>0.97824478149399996</v>
       </c>
       <c r="P105" s="3">
         <v>1010.98358154</v>
       </c>
       <c r="Q105" s="3">
-        <v>10.2986545563</v>
+        <v>10.298654556300001</v>
       </c>
       <c r="R105" s="3">
-        <v>259.585906982</v>
+        <v>259.58590698199998</v>
       </c>
       <c r="S105" s="3">
-        <v>580.459350586</v>
+        <v>580.45935058600003</v>
       </c>
       <c r="T105" s="3">
         <v>28.2129859924</v>
@@ -10345,16 +9730,16 @@
         <v>0.2</v>
       </c>
       <c r="V105" s="3">
-        <v>0.559405</v>
+        <v>0.55940500000000004</v>
       </c>
       <c r="W105" s="3">
         <v>187.3734</v>
       </c>
       <c r="X105" s="3">
-        <v>291.3862</v>
+        <v>291.38619999999997</v>
       </c>
       <c r="Y105" s="3">
-        <v>0.660009026527405</v>
+        <v>0.66000902652740501</v>
       </c>
       <c r="Z105" s="1">
         <v>0.42</v>
@@ -10363,7 +9748,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="106" spans="1:27">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>29</v>
       </c>
@@ -10371,7 +9756,7 @@
         <v>112.6133</v>
       </c>
       <c r="C106" s="3">
-        <v>27.7002</v>
+        <v>27.700199999999999</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>145</v>
@@ -10413,22 +9798,22 @@
         <v>1061</v>
       </c>
       <c r="Q106" s="3">
-        <v>10.217</v>
+        <v>10.217000000000001</v>
       </c>
       <c r="R106" s="3">
-        <v>274.493</v>
+        <v>274.49299999999999</v>
       </c>
       <c r="S106" s="3">
         <v>211</v>
       </c>
       <c r="T106" s="3">
-        <v>20.304</v>
+        <v>20.303999999999998</v>
       </c>
       <c r="U106" s="3">
         <v>0.11</v>
       </c>
       <c r="V106" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="W106" s="3">
         <v>152</v>
@@ -10446,7 +9831,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:27">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>30</v>
       </c>
@@ -10487,7 +9872,7 @@
         <v>36</v>
       </c>
       <c r="N107" s="3">
-        <v>0.484431564808</v>
+        <v>0.48443156480799998</v>
       </c>
       <c r="O107" s="3">
         <v>0.773104429245</v>
@@ -10499,7 +9884,7 @@
         <v>11.2203083038</v>
       </c>
       <c r="R107" s="3">
-        <v>275.740905762</v>
+        <v>275.74090576200001</v>
       </c>
       <c r="S107" s="3">
         <v>439.867431641</v>
@@ -10514,13 +9899,13 @@
         <v>0.2087184</v>
       </c>
       <c r="W107" s="3">
-        <v>228.5501</v>
+        <v>228.55009999999999</v>
       </c>
       <c r="X107" s="3">
-        <v>204.2334</v>
+        <v>204.23339999999999</v>
       </c>
       <c r="Y107" s="3">
-        <v>0.419748991727829</v>
+        <v>0.41974899172782898</v>
       </c>
       <c r="Z107" s="1">
         <v>0.21</v>
@@ -10529,7 +9914,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="108" spans="1:27">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>112</v>
       </c>
@@ -10537,7 +9922,7 @@
         <v>112.61104</v>
       </c>
       <c r="C108" s="3">
-        <v>27.64362</v>
+        <v>27.643619999999999</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>148</v>
@@ -10570,10 +9955,10 @@
         <v>34</v>
       </c>
       <c r="N108" s="3">
-        <v>0.404482394457</v>
+        <v>0.40448239445700002</v>
       </c>
       <c r="O108" s="3">
-        <v>0.727285802364</v>
+        <v>0.72728580236399998</v>
       </c>
       <c r="P108" s="3">
         <v>1031.7532959</v>
@@ -10582,28 +9967,28 @@
         <v>12.2748556137</v>
       </c>
       <c r="R108" s="3">
-        <v>277.532226563</v>
+        <v>277.53222656299999</v>
       </c>
       <c r="S108" s="3">
-        <v>319.384002686</v>
+        <v>319.38400268599997</v>
       </c>
       <c r="T108" s="3">
-        <v>24.008354187</v>
+        <v>24.008354186999998</v>
       </c>
       <c r="U108" s="3">
         <v>0.15</v>
       </c>
       <c r="V108" s="3">
-        <v>0.2100773</v>
+        <v>0.21007729999999999</v>
       </c>
       <c r="W108" s="3">
-        <v>253.2941</v>
+        <v>253.29409999999999</v>
       </c>
       <c r="X108" s="3">
-        <v>169.7129</v>
+        <v>169.71289999999999</v>
       </c>
       <c r="Y108" s="3">
-        <v>0.286280006170273</v>
+        <v>0.28628000617027299</v>
       </c>
       <c r="Z108" s="1">
         <v>0.52</v>
@@ -10612,7 +9997,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="109" spans="1:27">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>128</v>
       </c>
@@ -10620,7 +10005,7 @@
         <v>112.6249</v>
       </c>
       <c r="C109" s="3">
-        <v>27.6725</v>
+        <v>27.672499999999999</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>149</v>
@@ -10653,31 +10038,31 @@
         <v>45</v>
       </c>
       <c r="N109" s="3">
-        <v>0.435503929853</v>
+        <v>0.43550392985300002</v>
       </c>
       <c r="O109" s="3">
-        <v>0.694286227226</v>
+        <v>0.69428622722599997</v>
       </c>
       <c r="P109" s="3">
-        <v>977.190795898</v>
+        <v>977.19079589800003</v>
       </c>
       <c r="Q109" s="3">
-        <v>11.101896286</v>
+        <v>11.101896286000001</v>
       </c>
       <c r="R109" s="3">
-        <v>275.472930908</v>
+        <v>275.47293090800002</v>
       </c>
       <c r="S109" s="3">
-        <v>277.906860352</v>
+        <v>277.90686035200002</v>
       </c>
       <c r="T109" s="3">
-        <v>26.1462745667</v>
+        <v>26.146274566700001</v>
       </c>
       <c r="U109" s="3">
         <v>0.19</v>
       </c>
       <c r="V109" s="3">
-        <v>0.1758524</v>
+        <v>0.17585239999999999</v>
       </c>
       <c r="W109" s="3">
         <v>209.9254</v>
@@ -10686,7 +10071,7 @@
         <v>186.5462</v>
       </c>
       <c r="Y109" s="3">
-        <v>0.328976988792419</v>
+        <v>0.32897698879241899</v>
       </c>
       <c r="Z109" s="1">
         <v>0.87</v>
@@ -10695,7 +10080,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="110" spans="1:27">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>129</v>
       </c>
@@ -10748,16 +10133,16 @@
         <v>10.286</v>
       </c>
       <c r="R110" s="3">
-        <v>265.191</v>
+        <v>265.19099999999997</v>
       </c>
       <c r="S110" s="3">
         <v>167</v>
       </c>
       <c r="T110" s="3">
-        <v>31.702</v>
+        <v>31.702000000000002</v>
       </c>
       <c r="U110" s="3">
-        <v>0.1716031</v>
+        <v>0.17160310000000001</v>
       </c>
       <c r="V110" s="3">
         <v>0.16</v>
@@ -10766,10 +10151,10 @@
         <v>201</v>
       </c>
       <c r="X110" s="3">
-        <v>193.1348</v>
+        <v>193.13480000000001</v>
       </c>
       <c r="Y110" s="3">
-        <v>0.164835005998611</v>
+        <v>0.16483500599861101</v>
       </c>
       <c r="Z110" s="1">
         <v>0.71</v>
@@ -10778,21 +10163,21 @@
         <v>146</v>
       </c>
     </row>
-    <row r="111" spans="1:27">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>130</v>
       </c>
       <c r="B111" s="3">
-        <v>112.6916</v>
+        <v>112.69159999999999</v>
       </c>
       <c r="C111" s="3">
-        <v>27.6744</v>
+        <v>27.674399999999999</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>151</v>
       </c>
       <c r="E111" s="3">
-        <v>143.8</v>
+        <v>143.80000000000001</v>
       </c>
       <c r="F111" s="3">
         <v>167</v>
@@ -10819,10 +10204,10 @@
         <v>31</v>
       </c>
       <c r="N111" s="3">
-        <v>0.485546141863</v>
+        <v>0.48554614186299999</v>
       </c>
       <c r="O111" s="3">
-        <v>0.773772776127</v>
+        <v>0.77377277612700002</v>
       </c>
       <c r="P111" s="3">
         <v>1005.98516846</v>
@@ -10831,37 +10216,37 @@
         <v>12.7773866653</v>
       </c>
       <c r="R111" s="3">
-        <v>302.716430664</v>
+        <v>302.71643066399997</v>
       </c>
       <c r="S111" s="3">
         <v>467.951171875</v>
       </c>
       <c r="T111" s="3">
-        <v>24.1850833893</v>
+        <v>24.185083389300001</v>
       </c>
       <c r="U111" s="3">
         <v>0.23</v>
       </c>
       <c r="V111" s="3">
-        <v>0.2382914</v>
+        <v>0.23829139999999999</v>
       </c>
       <c r="W111" s="3">
-        <v>285.6368</v>
+        <v>285.63679999999999</v>
       </c>
       <c r="X111" s="3">
-        <v>178.3754</v>
+        <v>178.37540000000001</v>
       </c>
       <c r="Y111" s="3">
-        <v>0.0910437032580376</v>
+        <v>9.1043703258037595E-2</v>
       </c>
       <c r="Z111" s="1">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AA111" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="112" spans="1:27">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>131</v>
       </c>
@@ -10902,10 +10287,10 @@
         <v>35</v>
       </c>
       <c r="N112" s="3">
-        <v>0.423798948526</v>
+        <v>0.42379894852599997</v>
       </c>
       <c r="O112" s="3">
-        <v>0.757967352867</v>
+        <v>0.75796735286700001</v>
       </c>
       <c r="P112" s="3">
         <v>997.987792969</v>
@@ -10914,13 +10299,13 @@
         <v>12.3814229965</v>
       </c>
       <c r="R112" s="3">
-        <v>283.817810059</v>
+        <v>283.81781005900001</v>
       </c>
       <c r="S112" s="3">
         <v>331.253814697</v>
       </c>
       <c r="T112" s="3">
-        <v>24.5687484741</v>
+        <v>24.568748474100001</v>
       </c>
       <c r="U112" s="3">
         <v>0.16</v>
@@ -10929,13 +10314,13 @@
         <v>0.2157868</v>
       </c>
       <c r="W112" s="3">
-        <v>251.7247</v>
+        <v>251.72470000000001</v>
       </c>
       <c r="X112" s="3">
         <v>179.2174</v>
       </c>
       <c r="Y112" s="3">
-        <v>0.192809000611305</v>
+        <v>0.19280900061130499</v>
       </c>
       <c r="Z112" s="1">
         <v>0.35</v>
@@ -10944,15 +10329,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="113" spans="1:27">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>23</v>
       </c>
       <c r="B113" s="3">
-        <v>112.8294</v>
+        <v>112.82940000000001</v>
       </c>
       <c r="C113" s="3">
-        <v>27.81619</v>
+        <v>27.816189999999999</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>153</v>
@@ -10985,25 +10370,25 @@
         <v>42</v>
       </c>
       <c r="N113" s="3">
-        <v>0.760500013828</v>
+        <v>0.76050001382800003</v>
       </c>
       <c r="O113" s="3">
         <v>1.04622817039</v>
       </c>
       <c r="P113" s="3">
-        <v>1370.25280762</v>
+        <v>1370.2528076200001</v>
       </c>
       <c r="Q113" s="3">
         <v>10.9440250397</v>
       </c>
       <c r="R113" s="3">
-        <v>248.535736084</v>
+        <v>248.53573608400001</v>
       </c>
       <c r="S113" s="3">
-        <v>2237.34228516</v>
+        <v>2237.3422851599998</v>
       </c>
       <c r="T113" s="3">
-        <v>23.4834899902</v>
+        <v>23.483489990199999</v>
       </c>
       <c r="U113" s="3">
         <v>0.37</v>
@@ -11012,22 +10397,22 @@
         <v>0.2670651</v>
       </c>
       <c r="W113" s="3">
-        <v>252.1107</v>
+        <v>252.11070000000001</v>
       </c>
       <c r="X113" s="3">
-        <v>368.0108</v>
+        <v>368.01080000000002</v>
       </c>
       <c r="Y113" s="3">
-        <v>0.275474011898041</v>
+        <v>0.27547401189804099</v>
       </c>
       <c r="Z113" s="1">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA113" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="114" spans="1:27">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>31</v>
       </c>
@@ -11035,7 +10420,7 @@
         <v>112.737345</v>
       </c>
       <c r="C114" s="3">
-        <v>27.781429</v>
+        <v>27.781428999999999</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>155</v>
@@ -11068,40 +10453,40 @@
         <v>36</v>
       </c>
       <c r="N114" s="3">
-        <v>0.696863412857</v>
+        <v>0.69686341285700004</v>
       </c>
       <c r="O114" s="3">
-        <v>0.930698990822</v>
+        <v>0.93069899082200003</v>
       </c>
       <c r="P114" s="3">
-        <v>1300.62194824</v>
+        <v>1300.6219482399999</v>
       </c>
       <c r="Q114" s="3">
-        <v>12.4604310989</v>
+        <v>12.460431098899999</v>
       </c>
       <c r="R114" s="3">
-        <v>256.674682617</v>
+        <v>256.67468261699997</v>
       </c>
       <c r="S114" s="3">
-        <v>2834.91088867</v>
+        <v>2834.9108886700001</v>
       </c>
       <c r="T114" s="3">
-        <v>21.5797386169</v>
+        <v>21.579738616899999</v>
       </c>
       <c r="U114" s="3">
         <v>0.23</v>
       </c>
       <c r="V114" s="3">
-        <v>0.3327609</v>
+        <v>0.33276090000000003</v>
       </c>
       <c r="W114" s="3">
-        <v>160.8693</v>
+        <v>160.86930000000001</v>
       </c>
       <c r="X114" s="3">
         <v>509.0172</v>
       </c>
       <c r="Y114" s="3">
-        <v>0.302282005548477</v>
+        <v>0.30228200554847701</v>
       </c>
       <c r="Z114" s="1">
         <v>0.24</v>
@@ -11110,7 +10495,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="115" spans="1:27">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>32</v>
       </c>
@@ -11118,7 +10503,7 @@
         <v>112.7403</v>
       </c>
       <c r="C115" s="3">
-        <v>27.8087</v>
+        <v>27.808700000000002</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>156</v>
@@ -11151,25 +10536,25 @@
         <v>55</v>
       </c>
       <c r="N115" s="3">
-        <v>0.687414884567</v>
+        <v>0.68741488456699995</v>
       </c>
       <c r="O115" s="3">
-        <v>0.945747733116</v>
+        <v>0.94574773311600002</v>
       </c>
       <c r="P115" s="3">
-        <v>1265.01867676</v>
+        <v>1265.0186767600001</v>
       </c>
       <c r="Q115" s="3">
-        <v>12.3139696121</v>
+        <v>12.313969612099999</v>
       </c>
       <c r="R115" s="3">
         <v>257.934082031</v>
       </c>
       <c r="S115" s="3">
-        <v>2505.97070313</v>
+        <v>2505.9707031299999</v>
       </c>
       <c r="T115" s="3">
-        <v>21.6237049103</v>
+        <v>21.623704910299999</v>
       </c>
       <c r="U115" s="3">
         <v>0.32</v>
@@ -11178,13 +10563,13 @@
         <v>0.3306501</v>
       </c>
       <c r="W115" s="3">
-        <v>176.1932</v>
+        <v>176.19319999999999</v>
       </c>
       <c r="X115" s="3">
-        <v>467.7247</v>
+        <v>467.72469999999998</v>
       </c>
       <c r="Y115" s="3">
-        <v>0.429556012153625</v>
+        <v>0.42955601215362499</v>
       </c>
       <c r="Z115" s="1">
         <v>0.82</v>
@@ -11193,7 +10578,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="116" spans="1:27">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>33</v>
       </c>
@@ -11201,7 +10586,7 @@
         <v>112.7808</v>
       </c>
       <c r="C116" s="3">
-        <v>27.7979</v>
+        <v>27.797899999999998</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>157</v>
@@ -11237,22 +10622,22 @@
         <v>0.79</v>
       </c>
       <c r="O116" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P116" s="3">
         <v>861</v>
       </c>
       <c r="Q116" s="3">
-        <v>14.075</v>
+        <v>14.074999999999999</v>
       </c>
       <c r="R116" s="3">
-        <v>261.951</v>
+        <v>261.95100000000002</v>
       </c>
       <c r="S116" s="3">
         <v>388</v>
       </c>
       <c r="T116" s="3">
-        <v>21.513</v>
+        <v>21.513000000000002</v>
       </c>
       <c r="U116" s="3">
         <v>0.17</v>
@@ -11267,7 +10652,7 @@
         <v>145</v>
       </c>
       <c r="Y116" s="3">
-        <v>0.349970996379852</v>
+        <v>0.34997099637985202</v>
       </c>
       <c r="Z116" s="1">
         <v>0.82</v>
@@ -11276,7 +10661,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="117" spans="1:27">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>34</v>
       </c>
@@ -11317,40 +10702,40 @@
         <v>44</v>
       </c>
       <c r="N117" s="3">
-        <v>0.738336205482</v>
+        <v>0.73833620548199996</v>
       </c>
       <c r="O117" s="3">
         <v>1.02622842789</v>
       </c>
       <c r="P117" s="3">
-        <v>1118.27478027</v>
+        <v>1118.2747802700001</v>
       </c>
       <c r="Q117" s="3">
-        <v>12.3072786331</v>
+        <v>12.307278633099999</v>
       </c>
       <c r="R117" s="3">
         <v>258.923583984</v>
       </c>
       <c r="S117" s="3">
-        <v>1262.72180176</v>
+        <v>1262.7218017600001</v>
       </c>
       <c r="T117" s="3">
-        <v>22.0832290649</v>
+        <v>22.083229064899999</v>
       </c>
       <c r="U117" s="3">
         <v>0.16</v>
       </c>
       <c r="V117" s="3">
-        <v>0.2824271</v>
+        <v>0.28242709999999999</v>
       </c>
       <c r="W117" s="3">
-        <v>260.4967</v>
+        <v>260.49669999999998</v>
       </c>
       <c r="X117" s="3">
         <v>261.9513</v>
       </c>
       <c r="Y117" s="3">
-        <v>0.477571994066238</v>
+        <v>0.47757199406623801</v>
       </c>
       <c r="Z117" s="1">
         <v>0.96</v>
@@ -11359,7 +10744,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="118" spans="1:27">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>35</v>
       </c>
@@ -11409,7 +10794,7 @@
         <v>1372</v>
       </c>
       <c r="Q118" s="3">
-        <v>12.944</v>
+        <v>12.944000000000001</v>
       </c>
       <c r="R118" s="3">
         <v>252.239</v>
@@ -11418,7 +10803,7 @@
         <v>3725</v>
       </c>
       <c r="T118" s="3">
-        <v>21.345</v>
+        <v>21.344999999999999</v>
       </c>
       <c r="U118" s="3">
         <v>0.18</v>
@@ -11442,7 +10827,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="119" spans="1:27">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>36</v>
       </c>
@@ -11486,19 +10871,19 @@
         <v>0.765289008617</v>
       </c>
       <c r="O119" s="3">
-        <v>1.06110501289</v>
+        <v>1.0611050128899999</v>
       </c>
       <c r="P119" s="3">
-        <v>965.298583984</v>
+        <v>965.29858398399995</v>
       </c>
       <c r="Q119" s="3">
         <v>13.5107898712</v>
       </c>
       <c r="R119" s="3">
-        <v>261.024414063</v>
+        <v>261.02441406299999</v>
       </c>
       <c r="S119" s="3">
-        <v>849.40826416</v>
+        <v>849.40826416000004</v>
       </c>
       <c r="T119" s="3">
         <v>21.5838661194</v>
@@ -11507,16 +10892,16 @@
         <v>0.2</v>
       </c>
       <c r="V119" s="3">
-        <v>0.2752243</v>
+        <v>0.27522429999999998</v>
       </c>
       <c r="W119" s="3">
-        <v>274.9694</v>
+        <v>274.96940000000001</v>
       </c>
       <c r="X119" s="3">
         <v>207.2055</v>
       </c>
       <c r="Y119" s="3">
-        <v>0.294847995042801</v>
+        <v>0.29484799504280101</v>
       </c>
       <c r="Z119" s="1">
         <v>0.39</v>
@@ -11525,15 +10910,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="120" spans="1:27">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>37</v>
       </c>
       <c r="B120" s="3">
-        <v>112.7284</v>
+        <v>112.72839999999999</v>
       </c>
       <c r="C120" s="3">
-        <v>27.7629</v>
+        <v>27.762899999999998</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>161</v>
@@ -11560,28 +10945,28 @@
         <v>16</v>
       </c>
       <c r="L120" s="3">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M120" s="3">
         <v>38</v>
       </c>
       <c r="N120" s="3">
-        <v>0.656145095825</v>
+        <v>0.65614509582500002</v>
       </c>
       <c r="O120" s="3">
-        <v>0.943505585194</v>
+        <v>0.94350558519399996</v>
       </c>
       <c r="P120" s="3">
-        <v>1220.28271484</v>
+        <v>1220.2827148399999</v>
       </c>
       <c r="Q120" s="3">
-        <v>11.6746311188</v>
+        <v>11.674631118800001</v>
       </c>
       <c r="R120" s="3">
-        <v>263.510192871</v>
+        <v>263.51019287100002</v>
       </c>
       <c r="S120" s="3">
-        <v>1636.12084961</v>
+        <v>1636.1208496100001</v>
       </c>
       <c r="T120" s="3">
         <v>21.9861927032</v>
@@ -11590,25 +10975,25 @@
         <v>0.23</v>
       </c>
       <c r="V120" s="3">
-        <v>0.3059185</v>
+        <v>0.30591849999999998</v>
       </c>
       <c r="W120" s="3">
         <v>213.7944</v>
       </c>
       <c r="X120" s="3">
-        <v>368.4595</v>
+        <v>368.45949999999999</v>
       </c>
       <c r="Y120" s="3">
-        <v>0.467056006193161</v>
+        <v>0.46705600619316101</v>
       </c>
       <c r="Z120" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA120" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="121" spans="1:27">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>38</v>
       </c>
@@ -11622,7 +11007,7 @@
         <v>162</v>
       </c>
       <c r="E121" s="3">
-        <v>19.1</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F121" s="3">
         <v>208</v>
@@ -11649,37 +11034,37 @@
         <v>36</v>
       </c>
       <c r="N121" s="3">
-        <v>0.741384506226</v>
+        <v>0.74138450622600005</v>
       </c>
       <c r="O121" s="3">
-        <v>0.987494945526</v>
+        <v>0.98749494552600003</v>
       </c>
       <c r="P121" s="3">
-        <v>1152.86157227</v>
+        <v>1152.8615722699999</v>
       </c>
       <c r="Q121" s="3">
         <v>12.0430545807</v>
       </c>
       <c r="R121" s="3">
-        <v>259.407165527</v>
+        <v>259.40716552700002</v>
       </c>
       <c r="S121" s="3">
-        <v>1194.61889648</v>
+        <v>1194.6188964800001</v>
       </c>
       <c r="T121" s="3">
-        <v>21.7602539063</v>
+        <v>21.760253906300001</v>
       </c>
       <c r="U121" s="3">
         <v>0.19</v>
       </c>
       <c r="V121" s="3">
-        <v>0.2807915</v>
+        <v>0.28079150000000003</v>
       </c>
       <c r="W121" s="3">
-        <v>265.2553</v>
+        <v>265.25529999999998</v>
       </c>
       <c r="X121" s="3">
-        <v>257.5331</v>
+        <v>257.53309999999999</v>
       </c>
       <c r="Y121" s="3">
         <v>0.271605014801025</v>
@@ -11691,7 +11076,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="122" spans="1:27">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>39</v>
       </c>
@@ -11732,10 +11117,10 @@
         <v>48</v>
       </c>
       <c r="N122" s="3">
-        <v>0.794387698174</v>
+        <v>0.79438769817400001</v>
       </c>
       <c r="O122" s="3">
-        <v>1.11926090717</v>
+        <v>1.1192609071699999</v>
       </c>
       <c r="P122" s="3">
         <v>1619.89221191</v>
@@ -11747,10 +11132,10 @@
         <v>235.256347656</v>
       </c>
       <c r="S122" s="3">
-        <v>3395.58886719</v>
+        <v>3395.5888671900002</v>
       </c>
       <c r="T122" s="3">
-        <v>24.9825000763</v>
+        <v>24.982500076299999</v>
       </c>
       <c r="U122" s="3">
         <v>0.12</v>
@@ -11762,10 +11147,10 @@
         <v>249.6985</v>
       </c>
       <c r="X122" s="3">
-        <v>471.4878</v>
+        <v>471.48779999999999</v>
       </c>
       <c r="Y122" s="3">
-        <v>0.59563797712326</v>
+        <v>0.59563797712326005</v>
       </c>
       <c r="Z122" s="1">
         <v>0.52</v>
@@ -11774,7 +11159,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="123" spans="1:27">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>40</v>
       </c>
@@ -11815,25 +11200,25 @@
         <v>39</v>
       </c>
       <c r="N123" s="3">
-        <v>0.746178627014</v>
+        <v>0.74617862701399995</v>
       </c>
       <c r="O123" s="3">
         <v>1.00788557529</v>
       </c>
       <c r="P123" s="3">
-        <v>1219.40576172</v>
+        <v>1219.4057617200001</v>
       </c>
       <c r="Q123" s="3">
         <v>11.6084194183</v>
       </c>
       <c r="R123" s="3">
-        <v>256.084442139</v>
+        <v>256.08444213899998</v>
       </c>
       <c r="S123" s="3">
-        <v>1500.06054688</v>
+        <v>1500.0605468799999</v>
       </c>
       <c r="T123" s="3">
-        <v>22.4014987946</v>
+        <v>22.401498794599998</v>
       </c>
       <c r="U123" s="3">
         <v>0.16</v>
@@ -11845,10 +11230,10 @@
         <v>263.1927</v>
       </c>
       <c r="X123" s="3">
-        <v>290.8575</v>
+        <v>290.85750000000002</v>
       </c>
       <c r="Y123" s="3">
-        <v>0.35079899430275</v>
+        <v>0.35079899430275002</v>
       </c>
       <c r="Z123" s="1">
         <v>0.22</v>
@@ -11857,7 +11242,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="124" spans="1:27">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>41</v>
       </c>
@@ -11865,7 +11250,7 @@
         <v>112.760485</v>
       </c>
       <c r="C124" s="3">
-        <v>27.763205</v>
+        <v>27.763204999999999</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>165</v>
@@ -11892,46 +11277,46 @@
         <v>15</v>
       </c>
       <c r="L124" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M124" s="3">
         <v>42</v>
       </c>
       <c r="N124" s="3">
-        <v>0.696333289146</v>
+        <v>0.69633328914600001</v>
       </c>
       <c r="O124" s="3">
-        <v>0.937690377235</v>
+        <v>0.93769037723500004</v>
       </c>
       <c r="P124" s="3">
-        <v>1215.58740234</v>
+        <v>1215.5874023399999</v>
       </c>
       <c r="Q124" s="3">
-        <v>11.8935375214</v>
+        <v>11.893537521400001</v>
       </c>
       <c r="R124" s="3">
-        <v>261.441436768</v>
+        <v>261.44143676800002</v>
       </c>
       <c r="S124" s="3">
         <v>1663.36901855</v>
       </c>
       <c r="T124" s="3">
-        <v>21.7977733612</v>
+        <v>21.797773361200001</v>
       </c>
       <c r="U124" s="3">
         <v>0.17</v>
       </c>
       <c r="V124" s="3">
-        <v>0.3028259</v>
+        <v>0.30282589999999998</v>
       </c>
       <c r="W124" s="3">
-        <v>222.5738</v>
+        <v>222.57380000000001</v>
       </c>
       <c r="X124" s="3">
         <v>340.72</v>
       </c>
       <c r="Y124" s="3">
-        <v>0.35963898897171</v>
+        <v>0.35963898897170998</v>
       </c>
       <c r="Z124" s="1">
         <v>1.7</v>
@@ -11940,12 +11325,12 @@
         <v>154</v>
       </c>
     </row>
-    <row r="125" spans="1:27">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>18</v>
       </c>
       <c r="B125" s="3">
-        <v>112.97527</v>
+        <v>112.97526999999999</v>
       </c>
       <c r="C125" s="3">
         <v>27.73441</v>
@@ -11981,22 +11366,22 @@
         <v>53</v>
       </c>
       <c r="N125" s="3">
-        <v>0.552502930164</v>
+        <v>0.55250293016399998</v>
       </c>
       <c r="O125" s="3">
         <v>1.08515262604</v>
       </c>
       <c r="P125" s="3">
-        <v>1506.55126953</v>
+        <v>1506.5512695299999</v>
       </c>
       <c r="Q125" s="3">
-        <v>9.14185523987</v>
+        <v>9.1418552398700008</v>
       </c>
       <c r="R125" s="3">
-        <v>267.749237061</v>
+        <v>267.74923706099997</v>
       </c>
       <c r="S125" s="3">
-        <v>949.094360352</v>
+        <v>949.09436035199997</v>
       </c>
       <c r="T125" s="3">
         <v>23.9780845642</v>
@@ -12005,16 +11390,16 @@
         <v>0.19</v>
       </c>
       <c r="V125" s="3">
-        <v>0.3116729</v>
+        <v>0.31167289999999997</v>
       </c>
       <c r="W125" s="3">
-        <v>183.7376</v>
+        <v>183.73759999999999</v>
       </c>
       <c r="X125" s="3">
-        <v>295.3062</v>
+        <v>295.30619999999999</v>
       </c>
       <c r="Y125" s="3">
-        <v>1.48874998092651</v>
+        <v>1.4887499809265099</v>
       </c>
       <c r="Z125" s="1">
         <v>0.45</v>
@@ -12023,12 +11408,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="126" spans="1:27">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>42</v>
       </c>
       <c r="B126" s="3">
-        <v>112.9917</v>
+        <v>112.99169999999999</v>
       </c>
       <c r="C126" s="3">
         <v>27.7774</v>
@@ -12067,46 +11452,46 @@
         <v>0.302066475153</v>
       </c>
       <c r="O126" s="3">
-        <v>1.09788012505</v>
+        <v>1.0978801250500001</v>
       </c>
       <c r="P126" s="3">
-        <v>2258.43212891</v>
+        <v>2258.4321289099998</v>
       </c>
       <c r="Q126" s="3">
-        <v>9.39146327972</v>
+        <v>9.3914632797199999</v>
       </c>
       <c r="R126" s="3">
-        <v>276.166778564</v>
+        <v>276.16677856400003</v>
       </c>
       <c r="S126" s="3">
-        <v>798.079833984</v>
+        <v>798.07983398399995</v>
       </c>
       <c r="T126" s="3">
-        <v>20.2690181732</v>
+        <v>20.269018173199999</v>
       </c>
       <c r="U126" s="3">
         <v>0.23</v>
       </c>
       <c r="V126" s="3">
-        <v>0.3179203</v>
+        <v>0.31792029999999999</v>
       </c>
       <c r="W126" s="3">
         <v>117.7303</v>
       </c>
       <c r="X126" s="3">
-        <v>220.3139</v>
+        <v>220.31389999999999</v>
       </c>
       <c r="Y126" s="3">
-        <v>0.650924980640411</v>
+        <v>0.65092498064041104</v>
       </c>
       <c r="Z126" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AA126" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="127" spans="1:27">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>43</v>
       </c>
@@ -12114,7 +11499,7 @@
         <v>113.006</v>
       </c>
       <c r="C127" s="3">
-        <v>27.7846</v>
+        <v>27.784600000000001</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>169</v>
@@ -12141,7 +11526,7 @@
         <v>16</v>
       </c>
       <c r="L127" s="3">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M127" s="3">
         <v>52</v>
@@ -12150,22 +11535,22 @@
         <v>0.26</v>
       </c>
       <c r="O127" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P127" s="3">
         <v>2374</v>
       </c>
       <c r="Q127" s="3">
-        <v>9.411</v>
+        <v>9.4109999999999996</v>
       </c>
       <c r="R127" s="3">
-        <v>277.838</v>
+        <v>277.83800000000002</v>
       </c>
       <c r="S127" s="3">
         <v>736</v>
       </c>
       <c r="T127" s="3">
-        <v>19.703</v>
+        <v>19.702999999999999</v>
       </c>
       <c r="U127" s="3">
         <v>0.34</v>
@@ -12180,7 +11565,7 @@
         <v>207</v>
       </c>
       <c r="Y127" s="3">
-        <v>0.420751005411148</v>
+        <v>0.42075100541114802</v>
       </c>
       <c r="Z127" s="1">
         <v>0.83</v>
@@ -12189,7 +11574,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>44</v>
       </c>
@@ -12197,7 +11582,7 @@
         <v>112.9211</v>
       </c>
       <c r="C128" s="3">
-        <v>27.757</v>
+        <v>27.757000000000001</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>170</v>
@@ -12230,49 +11615,49 @@
         <v>59</v>
       </c>
       <c r="N128" s="3">
-        <v>0.561578571796</v>
+        <v>0.56157857179600001</v>
       </c>
       <c r="O128" s="3">
-        <v>1.2950848341</v>
+        <v>1.2950848341000001</v>
       </c>
       <c r="P128" s="3">
-        <v>1036.36584473</v>
+        <v>1036.3658447299999</v>
       </c>
       <c r="Q128" s="3">
-        <v>7.60714387894</v>
+        <v>7.6071438789399997</v>
       </c>
       <c r="R128" s="3">
-        <v>277.425109863</v>
+        <v>277.42510986299999</v>
       </c>
       <c r="S128" s="3">
-        <v>826.997009277</v>
+        <v>826.99700927699996</v>
       </c>
       <c r="T128" s="3">
-        <v>25.4979076385</v>
+        <v>25.497907638499999</v>
       </c>
       <c r="U128" s="3">
         <v>0.1</v>
       </c>
       <c r="V128" s="3">
-        <v>0.2504641</v>
+        <v>0.25046410000000002</v>
       </c>
       <c r="W128" s="3">
-        <v>162.9038</v>
+        <v>162.90379999999999</v>
       </c>
       <c r="X128" s="3">
-        <v>337.1384</v>
+        <v>337.13839999999999</v>
       </c>
       <c r="Y128" s="3">
         <v>0.802700996398926</v>
       </c>
       <c r="Z128" s="1">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AA128" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="129" spans="1:27">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>45</v>
       </c>
@@ -12280,7 +11665,7 @@
         <v>112.9208</v>
       </c>
       <c r="C129" s="3">
-        <v>27.7528</v>
+        <v>27.752800000000001</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>171</v>
@@ -12313,7 +11698,7 @@
         <v>65</v>
       </c>
       <c r="N129" s="3">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="O129" s="3">
         <v>1.3</v>
@@ -12322,19 +11707,19 @@
         <v>1029</v>
       </c>
       <c r="Q129" s="3">
-        <v>7.575</v>
+        <v>7.5750000000000002</v>
       </c>
       <c r="R129" s="3">
-        <v>277.781</v>
+        <v>277.78100000000001</v>
       </c>
       <c r="S129" s="3">
         <v>813</v>
       </c>
       <c r="T129" s="3">
-        <v>25.519</v>
+        <v>25.518999999999998</v>
       </c>
       <c r="U129" s="3">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="V129" s="3">
         <v>0.25</v>
@@ -12346,7 +11731,7 @@
         <v>337</v>
       </c>
       <c r="Y129" s="3">
-        <v>0.669085025787354</v>
+        <v>0.66908502578735396</v>
       </c>
       <c r="Z129" s="1">
         <v>0.62</v>
@@ -12355,15 +11740,15 @@
         <v>167</v>
       </c>
     </row>
-    <row r="130" spans="1:27">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>46</v>
       </c>
       <c r="B130" s="3">
-        <v>112.8893</v>
+        <v>112.88930000000001</v>
       </c>
       <c r="C130" s="3">
-        <v>27.7597</v>
+        <v>27.759699999999999</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>172</v>
@@ -12396,34 +11781,34 @@
         <v>74</v>
       </c>
       <c r="N130" s="3">
-        <v>0.650713801384</v>
+        <v>0.65071380138400003</v>
       </c>
       <c r="O130" s="3">
-        <v>1.10274994373</v>
+        <v>1.1027499437299999</v>
       </c>
       <c r="P130" s="3">
-        <v>1280.81103516</v>
+        <v>1280.8110351600001</v>
       </c>
       <c r="Q130" s="3">
-        <v>8.73924732208</v>
+        <v>8.7392473220800007</v>
       </c>
       <c r="R130" s="3">
-        <v>261.731658936</v>
+        <v>261.73165893599997</v>
       </c>
       <c r="S130" s="3">
-        <v>1525.86279297</v>
+        <v>1525.8627929700001</v>
       </c>
       <c r="T130" s="3">
-        <v>24.8538360596</v>
+        <v>24.853836059599999</v>
       </c>
       <c r="U130" s="3">
         <v>0.11</v>
       </c>
       <c r="V130" s="3">
-        <v>0.2582703</v>
+        <v>0.25827030000000001</v>
       </c>
       <c r="W130" s="3">
-        <v>205.9869</v>
+        <v>205.98689999999999</v>
       </c>
       <c r="X130" s="3">
         <v>359.0616</v>
@@ -12438,7 +11823,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="131" spans="1:27">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>47</v>
       </c>
@@ -12446,7 +11831,7 @@
         <v>112.9883</v>
       </c>
       <c r="C131" s="3">
-        <v>27.792</v>
+        <v>27.792000000000002</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>173</v>
@@ -12473,28 +11858,28 @@
         <v>14</v>
       </c>
       <c r="L131" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M131" s="3">
         <v>61</v>
       </c>
       <c r="N131" s="3">
-        <v>0.306165605783</v>
+        <v>0.30616560578300001</v>
       </c>
       <c r="O131" s="3">
-        <v>1.09782719612</v>
+        <v>1.0978271961199999</v>
       </c>
       <c r="P131" s="3">
-        <v>2249.32446289</v>
+        <v>2249.3244628900002</v>
       </c>
       <c r="Q131" s="3">
-        <v>9.39340019226</v>
+        <v>9.3934001922599997</v>
       </c>
       <c r="R131" s="3">
         <v>275.894287109</v>
       </c>
       <c r="S131" s="3">
-        <v>814.298156738</v>
+        <v>814.29815673799999</v>
       </c>
       <c r="T131" s="3">
         <v>20.313533783</v>
@@ -12506,13 +11891,13 @@
         <v>0.3171446</v>
       </c>
       <c r="W131" s="3">
-        <v>118.9304</v>
+        <v>118.93040000000001</v>
       </c>
       <c r="X131" s="3">
         <v>222.2466</v>
       </c>
       <c r="Y131" s="3">
-        <v>0.897009015083313</v>
+        <v>0.89700901508331299</v>
       </c>
       <c r="Z131" s="1">
         <v>0.35</v>
@@ -12521,21 +11906,21 @@
         <v>167</v>
       </c>
     </row>
-    <row r="132" spans="1:27">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>48</v>
       </c>
       <c r="B132" s="3">
-        <v>112.9232</v>
+        <v>112.92319999999999</v>
       </c>
       <c r="C132" s="3">
-        <v>27.7734</v>
+        <v>27.773399999999999</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>174</v>
       </c>
       <c r="E132" s="3">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F132" s="3">
         <v>130</v>
@@ -12556,46 +11941,46 @@
         <v>15</v>
       </c>
       <c r="L132" s="3">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M132" s="3">
         <v>71</v>
       </c>
       <c r="N132" s="3">
-        <v>0.588293552399</v>
+        <v>0.58829355239900005</v>
       </c>
       <c r="O132" s="3">
         <v>1.22705447674</v>
       </c>
       <c r="P132" s="3">
-        <v>1169.09094238</v>
+        <v>1169.0909423799999</v>
       </c>
       <c r="Q132" s="3">
-        <v>8.1310710907</v>
+        <v>8.1310710907000008</v>
       </c>
       <c r="R132" s="3">
-        <v>271.180145264</v>
+        <v>271.18014526399998</v>
       </c>
       <c r="S132" s="3">
         <v>1116.48083496</v>
       </c>
       <c r="T132" s="3">
-        <v>25.1674098969</v>
+        <v>25.167409896900001</v>
       </c>
       <c r="U132" s="3">
         <v>0.17</v>
       </c>
       <c r="V132" s="3">
-        <v>0.2570342</v>
+        <v>0.25703419999999999</v>
       </c>
       <c r="W132" s="3">
-        <v>175.6674</v>
+        <v>175.66739999999999</v>
       </c>
       <c r="X132" s="3">
-        <v>343.8532</v>
+        <v>343.85320000000002</v>
       </c>
       <c r="Y132" s="3">
-        <v>0.886942028999329</v>
+        <v>0.88694202899932895</v>
       </c>
       <c r="Z132" s="1">
         <v>1.2</v>
@@ -12604,7 +11989,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="133" spans="1:27">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>49</v>
       </c>
@@ -12645,25 +12030,25 @@
         <v>74</v>
       </c>
       <c r="N133" s="3">
-        <v>0.570889949799</v>
+        <v>0.57088994979899998</v>
       </c>
       <c r="O133" s="3">
-        <v>1.26045620441</v>
+        <v>1.2604562044100001</v>
       </c>
       <c r="P133" s="3">
         <v>1097.51831055</v>
       </c>
       <c r="Q133" s="3">
-        <v>7.85014438629</v>
+        <v>7.8501443862900002</v>
       </c>
       <c r="R133" s="3">
-        <v>274.913208008</v>
+        <v>274.91320800800003</v>
       </c>
       <c r="S133" s="3">
-        <v>926.563659668</v>
+        <v>926.56365966800001</v>
       </c>
       <c r="T133" s="3">
-        <v>25.3175868988</v>
+        <v>25.317586898799998</v>
       </c>
       <c r="U133" s="3">
         <v>0.37</v>
@@ -12672,13 +12057,13 @@
         <v>0.254658</v>
       </c>
       <c r="W133" s="3">
-        <v>169.1571</v>
+        <v>169.15710000000001</v>
       </c>
       <c r="X133" s="3">
-        <v>337.3502</v>
+        <v>337.35019999999997</v>
       </c>
       <c r="Y133" s="3">
-        <v>5.36148023605347</v>
+        <v>5.3614802360534703</v>
       </c>
       <c r="Z133" s="1">
         <v>2.9</v>
@@ -12687,7 +12072,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="134" spans="1:27">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>51</v>
       </c>
@@ -12695,7 +12080,7 @@
         <v>112.9774</v>
       </c>
       <c r="C134" s="3">
-        <v>27.7678</v>
+        <v>27.767800000000001</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>176</v>
@@ -12728,25 +12113,25 @@
         <v>74</v>
       </c>
       <c r="N134" s="3">
-        <v>0.421761184931</v>
+        <v>0.42176118493100001</v>
       </c>
       <c r="O134" s="3">
         <v>1.10115385056</v>
       </c>
       <c r="P134" s="3">
-        <v>1906.19506836</v>
+        <v>1906.1950683600001</v>
       </c>
       <c r="Q134" s="3">
-        <v>9.24610900879</v>
+        <v>9.2461090087900004</v>
       </c>
       <c r="R134" s="3">
-        <v>271.944946289</v>
+        <v>271.94494628899997</v>
       </c>
       <c r="S134" s="3">
-        <v>959.115966797</v>
+        <v>959.11596679700006</v>
       </c>
       <c r="T134" s="3">
-        <v>21.9587516785</v>
+        <v>21.958751678500001</v>
       </c>
       <c r="U134" s="3">
         <v>0.23</v>
@@ -12758,10 +12143,10 @@
         <v>148.0523</v>
       </c>
       <c r="X134" s="3">
-        <v>260.6252</v>
+        <v>260.62520000000001</v>
       </c>
       <c r="Y134" s="3">
-        <v>0.998089015483856</v>
+        <v>0.99808901548385598</v>
       </c>
       <c r="Z134" s="1">
         <v>1.3</v>
@@ -12770,15 +12155,15 @@
         <v>167</v>
       </c>
     </row>
-    <row r="135" spans="1:27">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>52</v>
       </c>
       <c r="B135" s="3">
-        <v>112.9334</v>
+        <v>112.93340000000001</v>
       </c>
       <c r="C135" s="3">
-        <v>27.777</v>
+        <v>27.777000000000001</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>177</v>
@@ -12811,25 +12196,25 @@
         <v>47</v>
       </c>
       <c r="N135" s="3">
-        <v>0.587970733643</v>
+        <v>0.58797073364300001</v>
       </c>
       <c r="O135" s="3">
-        <v>1.19403219223</v>
+        <v>1.1940321922299999</v>
       </c>
       <c r="P135" s="3">
         <v>1257.71057129</v>
       </c>
       <c r="Q135" s="3">
-        <v>8.39924621582</v>
+        <v>8.3992462158199999</v>
       </c>
       <c r="R135" s="3">
-        <v>269.102874756</v>
+        <v>269.10287475600001</v>
       </c>
       <c r="S135" s="3">
-        <v>1196.06835938</v>
+        <v>1196.0683593799999</v>
       </c>
       <c r="T135" s="3">
-        <v>24.8600463867</v>
+        <v>24.860046386699999</v>
       </c>
       <c r="U135" s="3">
         <v>0.1</v>
@@ -12841,10 +12226,10 @@
         <v>178.6661</v>
       </c>
       <c r="X135" s="3">
-        <v>340.0909</v>
+        <v>340.09089999999998</v>
       </c>
       <c r="Y135" s="3">
-        <v>0.497862994670868</v>
+        <v>0.49786299467086798</v>
       </c>
       <c r="Z135" s="1">
         <v>0.01</v>
@@ -12853,7 +12238,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="136" spans="1:27">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>54</v>
       </c>
@@ -12894,40 +12279,40 @@
         <v>31</v>
       </c>
       <c r="N136" s="3">
-        <v>0.608657181263</v>
+        <v>0.60865718126299995</v>
       </c>
       <c r="O136" s="3">
-        <v>0.928350567818</v>
+        <v>0.92835056781799996</v>
       </c>
       <c r="P136" s="3">
-        <v>1123.61218262</v>
+        <v>1123.6121826200001</v>
       </c>
       <c r="Q136" s="3">
         <v>11.1477689743</v>
       </c>
       <c r="R136" s="3">
-        <v>267.267425537</v>
+        <v>267.26742553700001</v>
       </c>
       <c r="S136" s="3">
-        <v>972.530822754</v>
+        <v>972.53082275400004</v>
       </c>
       <c r="T136" s="3">
-        <v>22.3590526581</v>
+        <v>22.359052658100001</v>
       </c>
       <c r="U136" s="3">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="V136" s="3">
-        <v>0.3473318</v>
+        <v>0.34733180000000002</v>
       </c>
       <c r="W136" s="3">
         <v>218.5865</v>
       </c>
       <c r="X136" s="3">
-        <v>219.7906</v>
+        <v>219.79060000000001</v>
       </c>
       <c r="Y136" s="3">
-        <v>0.309989005327225</v>
+        <v>0.30998900532722501</v>
       </c>
       <c r="Z136" s="1">
         <v>0.23</v>
@@ -12936,15 +12321,15 @@
         <v>179</v>
       </c>
     </row>
-    <row r="137" spans="1:27">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>55</v>
       </c>
       <c r="B137" s="3">
-        <v>112.69827</v>
+        <v>112.69826999999999</v>
       </c>
       <c r="C137" s="3">
-        <v>27.83575</v>
+        <v>27.835750000000001</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>180</v>
@@ -12986,7 +12371,7 @@
         <v>1001</v>
       </c>
       <c r="Q137" s="3">
-        <v>9.754</v>
+        <v>9.7539999999999996</v>
       </c>
       <c r="R137" s="3">
         <v>283.916</v>
@@ -12995,7 +12380,7 @@
         <v>595</v>
       </c>
       <c r="T137" s="3">
-        <v>20.972</v>
+        <v>20.972000000000001</v>
       </c>
       <c r="U137" s="3">
         <v>0.12</v>
@@ -13010,7 +12395,7 @@
         <v>167</v>
       </c>
       <c r="Y137" s="3">
-        <v>0.262578010559082</v>
+        <v>0.26257801055908198</v>
       </c>
       <c r="Z137" s="1">
         <v>0.32</v>
@@ -13019,7 +12404,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="138" spans="1:27">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>56</v>
       </c>
@@ -13033,7 +12418,7 @@
         <v>181</v>
       </c>
       <c r="E138" s="3">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F138" s="3">
         <v>69</v>
@@ -13060,40 +12445,40 @@
         <v>33</v>
       </c>
       <c r="N138" s="3">
-        <v>0.649673879147</v>
+        <v>0.64967387914700003</v>
       </c>
       <c r="O138" s="3">
-        <v>0.93951690197</v>
+        <v>0.93951690197000004</v>
       </c>
       <c r="P138" s="3">
-        <v>1140.28710938</v>
+        <v>1140.2871093799999</v>
       </c>
       <c r="Q138" s="3">
         <v>11.3203878403</v>
       </c>
       <c r="R138" s="3">
-        <v>264.497009277</v>
+        <v>264.49700927700002</v>
       </c>
       <c r="S138" s="3">
-        <v>993.19152832</v>
+        <v>993.19152831999997</v>
       </c>
       <c r="T138" s="3">
-        <v>22.7642250061</v>
+        <v>22.764225006099998</v>
       </c>
       <c r="U138" s="3">
         <v>0.15</v>
       </c>
       <c r="V138" s="3">
-        <v>0.3161715</v>
+        <v>0.31617149999999999</v>
       </c>
       <c r="W138" s="3">
-        <v>207.7918</v>
+        <v>207.79179999999999</v>
       </c>
       <c r="X138" s="3">
-        <v>222.3148</v>
+        <v>222.31479999999999</v>
       </c>
       <c r="Y138" s="3">
-        <v>0.329699993133545</v>
+        <v>0.32969999313354498</v>
       </c>
       <c r="Z138" s="1">
         <v>0.32</v>
@@ -13102,7 +12487,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="139" spans="1:27">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>57</v>
       </c>
@@ -13110,7 +12495,7 @@
         <v>112.6626</v>
       </c>
       <c r="C139" s="3">
-        <v>27.83319</v>
+        <v>27.833189999999998</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>182</v>
@@ -13152,7 +12537,7 @@
         <v>1059</v>
       </c>
       <c r="Q139" s="3">
-        <v>12.672</v>
+        <v>12.672000000000001</v>
       </c>
       <c r="R139" s="3">
         <v>249.19</v>
@@ -13176,7 +12561,7 @@
         <v>198</v>
       </c>
       <c r="Y139" s="3">
-        <v>0.309760987758636</v>
+        <v>0.30976098775863598</v>
       </c>
       <c r="Z139" s="1">
         <v>0.01</v>
@@ -13185,15 +12570,15 @@
         <v>179</v>
       </c>
     </row>
-    <row r="140" spans="1:27">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>58</v>
       </c>
       <c r="B140" s="3">
-        <v>112.716946</v>
+        <v>112.71694599999999</v>
       </c>
       <c r="C140" s="3">
-        <v>27.854853</v>
+        <v>27.854852999999999</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>183</v>
@@ -13226,37 +12611,37 @@
         <v>22</v>
       </c>
       <c r="N140" s="3">
-        <v>0.530979514122</v>
+        <v>0.53097951412199995</v>
       </c>
       <c r="O140" s="3">
-        <v>0.896951794624</v>
+        <v>0.89695179462399999</v>
       </c>
       <c r="P140" s="3">
-        <v>1093.06103516</v>
+        <v>1093.0610351600001</v>
       </c>
       <c r="Q140" s="3">
         <v>10.7673883438</v>
       </c>
       <c r="R140" s="3">
-        <v>272.337341309</v>
+        <v>272.33734130900001</v>
       </c>
       <c r="S140" s="3">
-        <v>889.417358398</v>
+        <v>889.41735839800003</v>
       </c>
       <c r="T140" s="3">
-        <v>21.7732963562</v>
+        <v>21.773296356199999</v>
       </c>
       <c r="U140" s="3">
         <v>0.12</v>
       </c>
       <c r="V140" s="3">
-        <v>0.3967856</v>
+        <v>0.39678560000000002</v>
       </c>
       <c r="W140" s="3">
-        <v>228.4781</v>
+        <v>228.47810000000001</v>
       </c>
       <c r="X140" s="3">
-        <v>210.5041</v>
+        <v>210.50409999999999</v>
       </c>
       <c r="Y140" s="3">
         <v>0.201499998569489</v>
@@ -13268,7 +12653,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="141" spans="1:27">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>59</v>
       </c>
@@ -13276,7 +12661,7 @@
         <v>112.64609</v>
       </c>
       <c r="C141" s="3">
-        <v>27.86218</v>
+        <v>27.862179999999999</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>184</v>
@@ -13309,57 +12694,57 @@
         <v>41</v>
       </c>
       <c r="N141" s="3">
-        <v>0.767770826817</v>
+        <v>0.76777082681700004</v>
       </c>
       <c r="O141" s="3">
-        <v>1.02240407467</v>
+        <v>1.0224040746700001</v>
       </c>
       <c r="P141" s="3">
         <v>1091.0526123</v>
       </c>
       <c r="Q141" s="3">
-        <v>11.8635425568</v>
+        <v>11.863542556800001</v>
       </c>
       <c r="R141" s="3">
-        <v>261.439788818</v>
+        <v>261.43978881800001</v>
       </c>
       <c r="S141" s="3">
-        <v>860.660766602</v>
+        <v>860.66076660199997</v>
       </c>
       <c r="T141" s="3">
-        <v>24.1378631592</v>
+        <v>24.137863159199998</v>
       </c>
       <c r="U141" s="3">
         <v>0.25</v>
       </c>
       <c r="V141" s="3">
-        <v>0.2907911</v>
+        <v>0.29079110000000002</v>
       </c>
       <c r="W141" s="3">
-        <v>182.8359</v>
+        <v>182.83590000000001</v>
       </c>
       <c r="X141" s="3">
-        <v>196.4387</v>
+        <v>196.43870000000001</v>
       </c>
       <c r="Y141" s="3">
         <v>0.191391006112099</v>
       </c>
       <c r="Z141" s="1">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA141" s="3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="142" spans="1:27">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>60</v>
       </c>
       <c r="B142" s="3">
-        <v>112.62283</v>
+        <v>112.62282999999999</v>
       </c>
       <c r="C142" s="3">
-        <v>27.83542</v>
+        <v>27.835419999999999</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>185</v>
@@ -13392,40 +12777,40 @@
         <v>42</v>
       </c>
       <c r="N142" s="3">
-        <v>0.734428167343</v>
+        <v>0.73442816734299998</v>
       </c>
       <c r="O142" s="3">
-        <v>0.979720652103</v>
+        <v>0.97972065210299997</v>
       </c>
       <c r="P142" s="3">
-        <v>1105.30126953</v>
+        <v>1105.3012695299999</v>
       </c>
       <c r="Q142" s="3">
-        <v>11.8291053772</v>
+        <v>11.829105377199999</v>
       </c>
       <c r="R142" s="3">
-        <v>263.050140381</v>
+        <v>263.05014038100001</v>
       </c>
       <c r="S142" s="3">
-        <v>819.422180176</v>
+        <v>819.42218017599998</v>
       </c>
       <c r="T142" s="3">
-        <v>23.7129058838</v>
+        <v>23.712905883800001</v>
       </c>
       <c r="U142" s="3">
         <v>0.13</v>
       </c>
       <c r="V142" s="3">
-        <v>0.2797681</v>
+        <v>0.27976810000000002</v>
       </c>
       <c r="W142" s="3">
-        <v>184.7417</v>
+        <v>184.74170000000001</v>
       </c>
       <c r="X142" s="3">
-        <v>192.6529</v>
+        <v>192.65289999999999</v>
       </c>
       <c r="Y142" s="3">
-        <v>0.211247995495796</v>
+        <v>0.21124799549579601</v>
       </c>
       <c r="Z142" s="1">
         <v>0.27</v>
@@ -13434,7 +12819,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="143" spans="1:27">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>61</v>
       </c>
@@ -13475,40 +12860,40 @@
         <v>41</v>
       </c>
       <c r="N143" s="3">
-        <v>0.615514695644</v>
+        <v>0.61551469564399997</v>
       </c>
       <c r="O143" s="3">
-        <v>0.965274035931</v>
+        <v>0.96527403593100003</v>
       </c>
       <c r="P143" s="3">
-        <v>1173.81982422</v>
+        <v>1173.8198242200001</v>
       </c>
       <c r="Q143" s="3">
-        <v>11.3948831558</v>
+        <v>11.394883155800001</v>
       </c>
       <c r="R143" s="3">
-        <v>265.312194824</v>
+        <v>265.31219482400002</v>
       </c>
       <c r="S143" s="3">
-        <v>1385.90795898</v>
+        <v>1385.9079589800001</v>
       </c>
       <c r="T143" s="3">
-        <v>21.8329200745</v>
+        <v>21.832920074499999</v>
       </c>
       <c r="U143" s="3">
         <v>0.27</v>
       </c>
       <c r="V143" s="3">
-        <v>0.3351493</v>
+        <v>0.33514929999999998</v>
       </c>
       <c r="W143" s="3">
         <v>222.0444</v>
       </c>
       <c r="X143" s="3">
-        <v>319.6637</v>
+        <v>319.66370000000001</v>
       </c>
       <c r="Y143" s="3">
-        <v>0.417939990758896</v>
+        <v>0.41793999075889599</v>
       </c>
       <c r="Z143" s="1">
         <v>0.82</v>
@@ -13517,12 +12902,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="144" spans="1:27">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>133</v>
       </c>
       <c r="B144" s="3">
-        <v>112.8337</v>
+        <v>112.83369999999999</v>
       </c>
       <c r="C144" s="3">
         <v>27.5366</v>
@@ -13558,10 +12943,10 @@
         <v>37</v>
       </c>
       <c r="N144" s="3">
-        <v>0.44242426753</v>
+        <v>0.44242426753000003</v>
       </c>
       <c r="O144" s="3">
-        <v>0.978116810322</v>
+        <v>0.97811681032200004</v>
       </c>
       <c r="P144" s="3">
         <v>1108.62927246</v>
@@ -13570,28 +12955,28 @@
         <v>10.6031084061</v>
       </c>
       <c r="R144" s="3">
-        <v>259.661773682</v>
+        <v>259.66177368199999</v>
       </c>
       <c r="S144" s="3">
-        <v>279.149780273</v>
+        <v>279.14978027299998</v>
       </c>
       <c r="T144" s="3">
-        <v>24.1943778992</v>
+        <v>24.194377899199999</v>
       </c>
       <c r="U144" s="3">
         <v>0.17</v>
       </c>
       <c r="V144" s="3">
-        <v>0.3220295</v>
+        <v>0.32202950000000002</v>
       </c>
       <c r="W144" s="3">
-        <v>430.942</v>
+        <v>430.94200000000001</v>
       </c>
       <c r="X144" s="3">
-        <v>206.806</v>
+        <v>206.80600000000001</v>
       </c>
       <c r="Y144" s="3">
-        <v>0.320526987314224</v>
+        <v>0.32052698731422402</v>
       </c>
       <c r="Z144" s="1">
         <v>0.33</v>
@@ -13600,7 +12985,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="145" spans="1:27">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>134</v>
       </c>
@@ -13608,7 +12993,7 @@
         <v>112.87522</v>
       </c>
       <c r="C145" s="3">
-        <v>27.54506</v>
+        <v>27.545059999999999</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>189</v>
@@ -13650,10 +13035,10 @@
         <v>1027</v>
       </c>
       <c r="Q145" s="3">
-        <v>9.803</v>
+        <v>9.8030000000000008</v>
       </c>
       <c r="R145" s="3">
-        <v>266.145</v>
+        <v>266.14499999999998</v>
       </c>
       <c r="S145" s="3">
         <v>227</v>
@@ -13665,7 +13050,7 @@
         <v>0.15</v>
       </c>
       <c r="V145" s="3">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="W145" s="3">
         <v>723</v>
@@ -13683,15 +13068,15 @@
         <v>188</v>
       </c>
     </row>
-    <row r="146" spans="1:27">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>135</v>
       </c>
       <c r="B146" s="3">
-        <v>112.95279</v>
+        <v>112.95278999999999</v>
       </c>
       <c r="C146" s="3">
-        <v>27.51057</v>
+        <v>27.510570000000001</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>190</v>
@@ -13724,40 +13109,40 @@
         <v>34</v>
       </c>
       <c r="N146" s="3">
-        <v>0.546343266964</v>
+        <v>0.54634326696400004</v>
       </c>
       <c r="O146" s="3">
-        <v>0.975160717964</v>
+        <v>0.97516071796399995</v>
       </c>
       <c r="P146" s="3">
-        <v>866.886474609</v>
+        <v>866.88647460899995</v>
       </c>
       <c r="Q146" s="3">
         <v>10.4352588654</v>
       </c>
       <c r="R146" s="3">
-        <v>266.182189941</v>
+        <v>266.18218994099999</v>
       </c>
       <c r="S146" s="3">
-        <v>299.635955811</v>
+        <v>299.63595581099997</v>
       </c>
       <c r="T146" s="3">
-        <v>25.7076034546</v>
+        <v>25.707603454600001</v>
       </c>
       <c r="U146" s="3">
         <v>0.1802684</v>
       </c>
       <c r="V146" s="3">
-        <v>0.5945438</v>
+        <v>0.59454379999999996</v>
       </c>
       <c r="W146" s="3">
-        <v>258.6213</v>
+        <v>258.62130000000002</v>
       </c>
       <c r="X146" s="3">
         <v>196.4871</v>
       </c>
       <c r="Y146" s="3">
-        <v>0.470551013946533</v>
+        <v>0.47055101394653298</v>
       </c>
       <c r="Z146" s="1">
         <v>0.01</v>
@@ -13766,7 +13151,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="147" spans="1:27">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
         <v>136</v>
       </c>
@@ -13801,7 +13186,7 @@
         <v>16</v>
       </c>
       <c r="L147" s="3">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M147" s="3">
         <v>43</v>
@@ -13816,10 +13201,10 @@
         <v>921</v>
       </c>
       <c r="Q147" s="3">
-        <v>10.626</v>
+        <v>10.625999999999999</v>
       </c>
       <c r="R147" s="3">
-        <v>253.343</v>
+        <v>253.34299999999999</v>
       </c>
       <c r="S147" s="3">
         <v>155</v>
@@ -13840,7 +13225,7 @@
         <v>224.3314</v>
       </c>
       <c r="Y147" s="3">
-        <v>0.370014011859894</v>
+        <v>0.37001401185989402</v>
       </c>
       <c r="Z147" s="1">
         <v>0.37</v>
@@ -13849,7 +13234,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="148" spans="1:27">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>137</v>
       </c>
@@ -13890,34 +13275,34 @@
         <v>56</v>
       </c>
       <c r="N148" s="3">
-        <v>0.50159317255</v>
+        <v>0.50159317255000002</v>
       </c>
       <c r="O148" s="3">
-        <v>1.07097971439</v>
+        <v>1.0709797143899999</v>
       </c>
       <c r="P148" s="3">
-        <v>922.287780762</v>
+        <v>922.28778076200001</v>
       </c>
       <c r="Q148" s="3">
         <v>10.3488054276</v>
       </c>
       <c r="R148" s="3">
-        <v>263.783233643</v>
+        <v>263.78323364300002</v>
       </c>
       <c r="S148" s="3">
-        <v>266.489257813</v>
+        <v>266.48925781299999</v>
       </c>
       <c r="T148" s="3">
-        <v>25.1955127716</v>
+        <v>25.195512771600001</v>
       </c>
       <c r="U148" s="3">
         <v>0.2</v>
       </c>
       <c r="V148" s="3">
-        <v>0.4514768</v>
+        <v>0.45147680000000001</v>
       </c>
       <c r="W148" s="3">
-        <v>385.2579</v>
+        <v>385.25790000000001</v>
       </c>
       <c r="X148" s="3">
         <v>209.5266</v>
@@ -13932,7 +13317,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="149" spans="1:27">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>138</v>
       </c>
@@ -13940,7 +13325,7 @@
         <v>112.93189</v>
       </c>
       <c r="C149" s="3">
-        <v>27.5774</v>
+        <v>27.577400000000001</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>193</v>
@@ -13973,7 +13358,7 @@
         <v>41</v>
       </c>
       <c r="N149" s="3">
-        <v>0.640194177628</v>
+        <v>0.64019417762800002</v>
       </c>
       <c r="O149" s="3">
         <v>1.03731441498</v>
@@ -13988,16 +13373,16 @@
         <v>261.917236328</v>
       </c>
       <c r="S149" s="3">
-        <v>326.954101563</v>
+        <v>326.95410156299999</v>
       </c>
       <c r="T149" s="3">
-        <v>26.7502975464</v>
+        <v>26.750297546399999</v>
       </c>
       <c r="U149" s="3">
         <v>0.17</v>
       </c>
       <c r="V149" s="3">
-        <v>0.4246577</v>
+        <v>0.42465770000000003</v>
       </c>
       <c r="W149" s="3">
         <v>294.4973</v>
@@ -14006,7 +13391,7 @@
         <v>255.8252</v>
       </c>
       <c r="Y149" s="3">
-        <v>0.490125000476837</v>
+        <v>0.49012500047683699</v>
       </c>
       <c r="Z149" s="1">
         <v>0.3</v>
@@ -14015,29 +13400,28 @@
         <v>188</v>
       </c>
     </row>
-    <row r="150" spans="27:27">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.15">
       <c r="AA150" s="7"/>
     </row>
-    <row r="151" spans="27:27">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.15">
       <c r="AA151" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="12.8888888888889"/>
+    <col min="2" max="2" width="12.875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>194</v>
       </c>
@@ -14045,15 +13429,15 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>28</v>
       </c>
       <c r="B2">
-        <v>0.814514829845349</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>0.81451482984534895</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -14061,103 +13445,103 @@
         <v>0.699967736725992</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>41</v>
       </c>
       <c r="B4">
-        <v>0.845359425658857</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>0.84535942565885702</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>48</v>
       </c>
       <c r="B5">
-        <v>0.737663776189564</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>0.73766377618956402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>64</v>
       </c>
       <c r="B6">
-        <v>0.792775690985218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>0.79277569098521805</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>72</v>
       </c>
       <c r="B7">
-        <v>0.73583918682055</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>0.73583918682055005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>78</v>
       </c>
       <c r="B8">
-        <v>0.797377765445261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>0.79737776544526096</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>86</v>
       </c>
       <c r="B9">
-        <v>0.767387902916213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>0.76738790291621295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>98</v>
       </c>
       <c r="B10">
-        <v>0.760970711847086</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>0.76097071184708598</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>106</v>
       </c>
       <c r="B11">
-        <v>0.734509859945956</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>0.73450985994595597</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>114</v>
       </c>
       <c r="B12">
-        <v>0.77948882027307</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>0.77948882027306998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>124</v>
       </c>
       <c r="B13">
-        <v>0.73516539106105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>0.73516539106105006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>132</v>
       </c>
       <c r="B14">
-        <v>0.704943350899933</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>0.70494335089993299</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>138</v>
       </c>
       <c r="B15">
-        <v>0.796998066970485</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>0.79699806697048503</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>146</v>
       </c>
@@ -14165,56 +13549,44 @@
         <v>0.751553173832477</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>154</v>
       </c>
       <c r="B17">
-        <v>0.681858722179214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>0.68185872217921395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>167</v>
       </c>
       <c r="B18">
-        <v>0.770533229138808</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>0.77053322913880795</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>179</v>
       </c>
       <c r="B19">
-        <v>0.76117476717384</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>0.76117476717384003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>188</v>
       </c>
       <c r="B20">
-        <v>0.757989815546813</v>
+        <v>0.75798981554681299</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:B20">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B20">
     <sortCondition ref="A2"/>
   </sortState>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/数据/水稻点位148.xlsx
+++ b/数据/水稻点位148.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Codes\Mission\agricultural-decision-system\数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Codes\agricultural-decision-system\数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2B8229-E8CE-4F79-86C5-E1DE626BE09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF83400-3D58-4D01-A6E0-4633F1F5EDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原始数据" sheetId="1" r:id="rId1"/>
@@ -108,6 +108,516 @@
     </r>
   </si>
   <si>
+    <t>乡镇</t>
+  </si>
+  <si>
+    <t>BS-YB-01-T</t>
+  </si>
+  <si>
+    <t>白石镇</t>
+  </si>
+  <si>
+    <t>BS-YB-02-T</t>
+  </si>
+  <si>
+    <t>BS-YB-03-T</t>
+  </si>
+  <si>
+    <t>BS-YB-05-T</t>
+  </si>
+  <si>
+    <t>BS-WG-06-T</t>
+  </si>
+  <si>
+    <t>CE-WG-02-T</t>
+  </si>
+  <si>
+    <t>茶恩寺镇</t>
+  </si>
+  <si>
+    <t>CE-YB-03-MD-土</t>
+  </si>
+  <si>
+    <t>CE-WG-04-T</t>
+  </si>
+  <si>
+    <t>CE-WG-05-T</t>
+  </si>
+  <si>
+    <t>CE-WG-06-MD-土</t>
+  </si>
+  <si>
+    <t>CE-YB-07-MD-土</t>
+  </si>
+  <si>
+    <t>FS-YB-07-T</t>
+  </si>
+  <si>
+    <t>分水乡</t>
+  </si>
+  <si>
+    <t>FS-WG-01-T</t>
+  </si>
+  <si>
+    <t>FS-WG-02-T</t>
+  </si>
+  <si>
+    <t>FS-WG-03-T</t>
+  </si>
+  <si>
+    <t>FS-YB-05-T</t>
+  </si>
+  <si>
+    <t>FS-WG-06-T</t>
+  </si>
+  <si>
+    <t>HK-WG-01-T</t>
+  </si>
+  <si>
+    <t>河口镇</t>
+  </si>
+  <si>
+    <t>HK-WG-02-T</t>
+  </si>
+  <si>
+    <t>HK-WG-03-T</t>
+  </si>
+  <si>
+    <t>HK-YB-04-T</t>
+  </si>
+  <si>
+    <t>HK-WG-05-T</t>
+  </si>
+  <si>
+    <t>HK-WG-06-T</t>
+  </si>
+  <si>
+    <t>HK-WG-07-T</t>
+  </si>
+  <si>
+    <t>HK-WG-09-T</t>
+  </si>
+  <si>
+    <t>HK-WG-08-T</t>
+  </si>
+  <si>
+    <t>HK-WG-10-T</t>
+  </si>
+  <si>
+    <t>HK-YB-11-T</t>
+  </si>
+  <si>
+    <t>HK-YB-12-T</t>
+  </si>
+  <si>
+    <t>HK-WG-13-T</t>
+  </si>
+  <si>
+    <t>ML-WG-04-T</t>
+  </si>
+  <si>
+    <t>YS-WG-12-T</t>
+  </si>
+  <si>
+    <t>HS-YB-01-T</t>
+  </si>
+  <si>
+    <t>花石镇</t>
+  </si>
+  <si>
+    <t>HS-GK-02-T</t>
+  </si>
+  <si>
+    <t>HS-YB-03-T</t>
+  </si>
+  <si>
+    <t>HS-YB-04-T</t>
+  </si>
+  <si>
+    <t>HS-WG-05-T</t>
+  </si>
+  <si>
+    <t>HS-YB-06-T</t>
+  </si>
+  <si>
+    <t>HS-WG-07-T</t>
+  </si>
+  <si>
+    <t>JS-YB-01-T</t>
+  </si>
+  <si>
+    <t>锦石乡</t>
+  </si>
+  <si>
+    <t>JS-YB-02-T</t>
+  </si>
+  <si>
+    <t>JS-YB-04-T</t>
+  </si>
+  <si>
+    <t>JS-YB-05-T</t>
+  </si>
+  <si>
+    <t>JS-YB-06-T</t>
+  </si>
+  <si>
+    <t>LK-YB-01-T</t>
+  </si>
+  <si>
+    <t>龙口乡</t>
+  </si>
+  <si>
+    <t>LK-YB-02-T</t>
+  </si>
+  <si>
+    <t>LK-WG-04-T</t>
+  </si>
+  <si>
+    <t>LR-YB-06-T</t>
+  </si>
+  <si>
+    <t>LK-YB-05-T</t>
+  </si>
+  <si>
+    <t>LK-YB-03-T</t>
+  </si>
+  <si>
+    <t>LK-YB-07-T</t>
+  </si>
+  <si>
+    <t>ML-WG-03-T</t>
+  </si>
+  <si>
+    <t>梅林桥镇</t>
+  </si>
+  <si>
+    <t>ML-WG-06-T</t>
+  </si>
+  <si>
+    <t>ML-WG-09-T</t>
+  </si>
+  <si>
+    <t>ML-WG-10-T</t>
+  </si>
+  <si>
+    <t>ML-WG-01-T</t>
+  </si>
+  <si>
+    <t>ML-WG-05-T</t>
+  </si>
+  <si>
+    <t>ML-WG-12-T</t>
+  </si>
+  <si>
+    <t>YS-GK-09-T</t>
+  </si>
+  <si>
+    <t>ML-WG-07-T</t>
+  </si>
+  <si>
+    <t>ML-WG-08-T</t>
+  </si>
+  <si>
+    <t>ML-WG-13-T</t>
+  </si>
+  <si>
+    <t>PT-GK-01-T</t>
+  </si>
+  <si>
+    <t>排头乡</t>
+  </si>
+  <si>
+    <t>PT-YB-02-T</t>
+  </si>
+  <si>
+    <t>PT-YB-04-T</t>
+  </si>
+  <si>
+    <t>PT-YB-05-T</t>
+  </si>
+  <si>
+    <t>PT-YB-06-T</t>
+  </si>
+  <si>
+    <t>PT-GK-07-T</t>
+  </si>
+  <si>
+    <t>ST-YB-06-T</t>
+  </si>
+  <si>
+    <t>PT-YB-03-T</t>
+  </si>
+  <si>
+    <t>青山桥镇</t>
+  </si>
+  <si>
+    <t>QS-YB-03-T</t>
+  </si>
+  <si>
+    <t>QS-WG-01-T</t>
+  </si>
+  <si>
+    <t>QS-YB-05-T</t>
+  </si>
+  <si>
+    <t>QS-YB-07-T</t>
+  </si>
+  <si>
+    <t>QS-YB-08-T</t>
+  </si>
+  <si>
+    <t>QS-YB-04-T</t>
+  </si>
+  <si>
+    <t>JS-YB-03-T</t>
+  </si>
+  <si>
+    <t>射埠镇</t>
+  </si>
+  <si>
+    <t>SB-GK-01-T</t>
+  </si>
+  <si>
+    <t>SB-YB-02-T</t>
+  </si>
+  <si>
+    <t>SB-WG-03-T</t>
+  </si>
+  <si>
+    <t>SB-WG-04-T</t>
+  </si>
+  <si>
+    <t>SB-YB-06-T</t>
+  </si>
+  <si>
+    <t>TJ-GK-01-T</t>
+  </si>
+  <si>
+    <t>TJ-GK-10-T</t>
+  </si>
+  <si>
+    <t>WS-YB-06-T</t>
+  </si>
+  <si>
+    <t>QS-YB-02-T</t>
+  </si>
+  <si>
+    <t>石鼓镇</t>
+  </si>
+  <si>
+    <t>QS-YB-06-T</t>
+  </si>
+  <si>
+    <t>SG-WG-01-T</t>
+  </si>
+  <si>
+    <t>SG-YB-02-T</t>
+  </si>
+  <si>
+    <t>SG-WG-04-T</t>
+  </si>
+  <si>
+    <t>SG-WG-06-T</t>
+  </si>
+  <si>
+    <t>SG-YB-03-T</t>
+  </si>
+  <si>
+    <t>ST-YB-01-T</t>
+  </si>
+  <si>
+    <t>石潭镇</t>
+  </si>
+  <si>
+    <t>ST-YB-02-T</t>
+  </si>
+  <si>
+    <t>ST-YB-03-T</t>
+  </si>
+  <si>
+    <t>ST-GK-04-T</t>
+  </si>
+  <si>
+    <t>ST-YB-05-T</t>
+  </si>
+  <si>
+    <t>TJ-GK-14-T</t>
+  </si>
+  <si>
+    <t>谭家山镇</t>
+  </si>
+  <si>
+    <t>TJ-GK-02-T</t>
+  </si>
+  <si>
+    <t>TJ-GK-03-T</t>
+  </si>
+  <si>
+    <t>TJ-GK-09-T</t>
+  </si>
+  <si>
+    <t>TJ-GK-08-T</t>
+  </si>
+  <si>
+    <t>TJ-GK-13-T</t>
+  </si>
+  <si>
+    <t>TJ-GK-12-T</t>
+  </si>
+  <si>
+    <t>WS-YB-04-T</t>
+  </si>
+  <si>
+    <t>乌石镇</t>
+  </si>
+  <si>
+    <t>WS-YB-07-T</t>
+  </si>
+  <si>
+    <t>SB-WG-07-T</t>
+  </si>
+  <si>
+    <t>WS-YB-01-T</t>
+  </si>
+  <si>
+    <t>WS-WG-02-T</t>
+  </si>
+  <si>
+    <t>WS-YB-03-T</t>
+  </si>
+  <si>
+    <t>WS-YB-05-T</t>
+  </si>
+  <si>
+    <t>SB-YB-05-T</t>
+  </si>
+  <si>
+    <t>杨嘉桥镇</t>
+  </si>
+  <si>
+    <t>YJ-WG-05-T</t>
+  </si>
+  <si>
+    <t>YJ-WG-01-T</t>
+  </si>
+  <si>
+    <t>YJ-WG-02-T</t>
+  </si>
+  <si>
+    <t>YJ-YB-03-T</t>
+  </si>
+  <si>
+    <t>YJ-WG-04-T</t>
+  </si>
+  <si>
+    <t>YJ-WG-06-T</t>
+  </si>
+  <si>
+    <t>YJ-WG-07-T</t>
+  </si>
+  <si>
+    <t>YJ-WG-09-T</t>
+  </si>
+  <si>
+    <t>YJ-WG-10-1</t>
+  </si>
+  <si>
+    <t>YJ-WG-11-T</t>
+  </si>
+  <si>
+    <t>YJ-WG-12-T</t>
+  </si>
+  <si>
+    <t>ML-WG-11-T</t>
+  </si>
+  <si>
+    <t>易俗河镇</t>
+  </si>
+  <si>
+    <t>YS-GK-01-T</t>
+  </si>
+  <si>
+    <t>YS-GK-02-T</t>
+  </si>
+  <si>
+    <t>YS-GK-03-T</t>
+  </si>
+  <si>
+    <t>YS-GK-04-T</t>
+  </si>
+  <si>
+    <t>YS-GK-05-T</t>
+  </si>
+  <si>
+    <t>YS-GK-06-T</t>
+  </si>
+  <si>
+    <t>YS-GK-07-T</t>
+  </si>
+  <si>
+    <t>YS-GK-08-T</t>
+  </si>
+  <si>
+    <t>YS-GK-10-T</t>
+  </si>
+  <si>
+    <t>YS-GK-11-T</t>
+  </si>
+  <si>
+    <t>YH-YB-01-T</t>
+  </si>
+  <si>
+    <t>云湖桥镇</t>
+  </si>
+  <si>
+    <t>YH-YB-02-T</t>
+  </si>
+  <si>
+    <t>YH-YB-03-T</t>
+  </si>
+  <si>
+    <t>YH-WG-04-T</t>
+  </si>
+  <si>
+    <t>YH-YB-05-T</t>
+  </si>
+  <si>
+    <t>YH-GK-06-T</t>
+  </si>
+  <si>
+    <t>YH-YB-07-T</t>
+  </si>
+  <si>
+    <t>YH-GK-08-T</t>
+  </si>
+  <si>
+    <t>ZL-YB-03-T</t>
+  </si>
+  <si>
+    <t>中路铺镇</t>
+  </si>
+  <si>
+    <t>ZL-GK-04-T</t>
+  </si>
+  <si>
+    <t>ZL-YB-05-T</t>
+  </si>
+  <si>
+    <t>ZL-YB-02-T</t>
+  </si>
+  <si>
+    <t>ZL-GK-06-T</t>
+  </si>
+  <si>
+    <t>ZL-YB-07-T</t>
+  </si>
+  <si>
+    <t>QH_NAME</t>
+  </si>
+  <si>
+    <t>平均值项:比值</t>
+  </si>
+  <si>
     <r>
       <t>水稻</t>
     </r>
@@ -118,516 +628,7 @@
       </rPr>
       <t>Cd</t>
     </r>
-  </si>
-  <si>
-    <t>乡镇</t>
-  </si>
-  <si>
-    <t>BS-YB-01-T</t>
-  </si>
-  <si>
-    <t>白石镇</t>
-  </si>
-  <si>
-    <t>BS-YB-02-T</t>
-  </si>
-  <si>
-    <t>BS-YB-03-T</t>
-  </si>
-  <si>
-    <t>BS-YB-05-T</t>
-  </si>
-  <si>
-    <t>BS-WG-06-T</t>
-  </si>
-  <si>
-    <t>CE-WG-02-T</t>
-  </si>
-  <si>
-    <t>茶恩寺镇</t>
-  </si>
-  <si>
-    <t>CE-YB-03-MD-土</t>
-  </si>
-  <si>
-    <t>CE-WG-04-T</t>
-  </si>
-  <si>
-    <t>CE-WG-05-T</t>
-  </si>
-  <si>
-    <t>CE-WG-06-MD-土</t>
-  </si>
-  <si>
-    <t>CE-YB-07-MD-土</t>
-  </si>
-  <si>
-    <t>FS-YB-07-T</t>
-  </si>
-  <si>
-    <t>分水乡</t>
-  </si>
-  <si>
-    <t>FS-WG-01-T</t>
-  </si>
-  <si>
-    <t>FS-WG-02-T</t>
-  </si>
-  <si>
-    <t>FS-WG-03-T</t>
-  </si>
-  <si>
-    <t>FS-YB-05-T</t>
-  </si>
-  <si>
-    <t>FS-WG-06-T</t>
-  </si>
-  <si>
-    <t>HK-WG-01-T</t>
-  </si>
-  <si>
-    <t>河口镇</t>
-  </si>
-  <si>
-    <t>HK-WG-02-T</t>
-  </si>
-  <si>
-    <t>HK-WG-03-T</t>
-  </si>
-  <si>
-    <t>HK-YB-04-T</t>
-  </si>
-  <si>
-    <t>HK-WG-05-T</t>
-  </si>
-  <si>
-    <t>HK-WG-06-T</t>
-  </si>
-  <si>
-    <t>HK-WG-07-T</t>
-  </si>
-  <si>
-    <t>HK-WG-09-T</t>
-  </si>
-  <si>
-    <t>HK-WG-08-T</t>
-  </si>
-  <si>
-    <t>HK-WG-10-T</t>
-  </si>
-  <si>
-    <t>HK-YB-11-T</t>
-  </si>
-  <si>
-    <t>HK-YB-12-T</t>
-  </si>
-  <si>
-    <t>HK-WG-13-T</t>
-  </si>
-  <si>
-    <t>ML-WG-04-T</t>
-  </si>
-  <si>
-    <t>YS-WG-12-T</t>
-  </si>
-  <si>
-    <t>HS-YB-01-T</t>
-  </si>
-  <si>
-    <t>花石镇</t>
-  </si>
-  <si>
-    <t>HS-GK-02-T</t>
-  </si>
-  <si>
-    <t>HS-YB-03-T</t>
-  </si>
-  <si>
-    <t>HS-YB-04-T</t>
-  </si>
-  <si>
-    <t>HS-WG-05-T</t>
-  </si>
-  <si>
-    <t>HS-YB-06-T</t>
-  </si>
-  <si>
-    <t>HS-WG-07-T</t>
-  </si>
-  <si>
-    <t>JS-YB-01-T</t>
-  </si>
-  <si>
-    <t>锦石乡</t>
-  </si>
-  <si>
-    <t>JS-YB-02-T</t>
-  </si>
-  <si>
-    <t>JS-YB-04-T</t>
-  </si>
-  <si>
-    <t>JS-YB-05-T</t>
-  </si>
-  <si>
-    <t>JS-YB-06-T</t>
-  </si>
-  <si>
-    <t>LK-YB-01-T</t>
-  </si>
-  <si>
-    <t>龙口乡</t>
-  </si>
-  <si>
-    <t>LK-YB-02-T</t>
-  </si>
-  <si>
-    <t>LK-WG-04-T</t>
-  </si>
-  <si>
-    <t>LR-YB-06-T</t>
-  </si>
-  <si>
-    <t>LK-YB-05-T</t>
-  </si>
-  <si>
-    <t>LK-YB-03-T</t>
-  </si>
-  <si>
-    <t>LK-YB-07-T</t>
-  </si>
-  <si>
-    <t>ML-WG-03-T</t>
-  </si>
-  <si>
-    <t>梅林桥镇</t>
-  </si>
-  <si>
-    <t>ML-WG-06-T</t>
-  </si>
-  <si>
-    <t>ML-WG-09-T</t>
-  </si>
-  <si>
-    <t>ML-WG-10-T</t>
-  </si>
-  <si>
-    <t>ML-WG-01-T</t>
-  </si>
-  <si>
-    <t>ML-WG-05-T</t>
-  </si>
-  <si>
-    <t>ML-WG-12-T</t>
-  </si>
-  <si>
-    <t>YS-GK-09-T</t>
-  </si>
-  <si>
-    <t>ML-WG-07-T</t>
-  </si>
-  <si>
-    <t>ML-WG-08-T</t>
-  </si>
-  <si>
-    <t>ML-WG-13-T</t>
-  </si>
-  <si>
-    <t>PT-GK-01-T</t>
-  </si>
-  <si>
-    <t>排头乡</t>
-  </si>
-  <si>
-    <t>PT-YB-02-T</t>
-  </si>
-  <si>
-    <t>PT-YB-04-T</t>
-  </si>
-  <si>
-    <t>PT-YB-05-T</t>
-  </si>
-  <si>
-    <t>PT-YB-06-T</t>
-  </si>
-  <si>
-    <t>PT-GK-07-T</t>
-  </si>
-  <si>
-    <t>ST-YB-06-T</t>
-  </si>
-  <si>
-    <t>PT-YB-03-T</t>
-  </si>
-  <si>
-    <t>青山桥镇</t>
-  </si>
-  <si>
-    <t>QS-YB-03-T</t>
-  </si>
-  <si>
-    <t>QS-WG-01-T</t>
-  </si>
-  <si>
-    <t>QS-YB-05-T</t>
-  </si>
-  <si>
-    <t>QS-YB-07-T</t>
-  </si>
-  <si>
-    <t>QS-YB-08-T</t>
-  </si>
-  <si>
-    <t>QS-YB-04-T</t>
-  </si>
-  <si>
-    <t>JS-YB-03-T</t>
-  </si>
-  <si>
-    <t>射埠镇</t>
-  </si>
-  <si>
-    <t>SB-GK-01-T</t>
-  </si>
-  <si>
-    <t>SB-YB-02-T</t>
-  </si>
-  <si>
-    <t>SB-WG-03-T</t>
-  </si>
-  <si>
-    <t>SB-WG-04-T</t>
-  </si>
-  <si>
-    <t>SB-YB-06-T</t>
-  </si>
-  <si>
-    <t>TJ-GK-01-T</t>
-  </si>
-  <si>
-    <t>TJ-GK-10-T</t>
-  </si>
-  <si>
-    <t>WS-YB-06-T</t>
-  </si>
-  <si>
-    <t>QS-YB-02-T</t>
-  </si>
-  <si>
-    <t>石鼓镇</t>
-  </si>
-  <si>
-    <t>QS-YB-06-T</t>
-  </si>
-  <si>
-    <t>SG-WG-01-T</t>
-  </si>
-  <si>
-    <t>SG-YB-02-T</t>
-  </si>
-  <si>
-    <t>SG-WG-04-T</t>
-  </si>
-  <si>
-    <t>SG-WG-06-T</t>
-  </si>
-  <si>
-    <t>SG-YB-03-T</t>
-  </si>
-  <si>
-    <t>ST-YB-01-T</t>
-  </si>
-  <si>
-    <t>石潭镇</t>
-  </si>
-  <si>
-    <t>ST-YB-02-T</t>
-  </si>
-  <si>
-    <t>ST-YB-03-T</t>
-  </si>
-  <si>
-    <t>ST-GK-04-T</t>
-  </si>
-  <si>
-    <t>ST-YB-05-T</t>
-  </si>
-  <si>
-    <t>TJ-GK-14-T</t>
-  </si>
-  <si>
-    <t>谭家山镇</t>
-  </si>
-  <si>
-    <t>TJ-GK-02-T</t>
-  </si>
-  <si>
-    <t>TJ-GK-03-T</t>
-  </si>
-  <si>
-    <t>TJ-GK-09-T</t>
-  </si>
-  <si>
-    <t>TJ-GK-08-T</t>
-  </si>
-  <si>
-    <t>TJ-GK-13-T</t>
-  </si>
-  <si>
-    <t>TJ-GK-12-T</t>
-  </si>
-  <si>
-    <t>WS-YB-04-T</t>
-  </si>
-  <si>
-    <t>乌石镇</t>
-  </si>
-  <si>
-    <t>WS-YB-07-T</t>
-  </si>
-  <si>
-    <t>SB-WG-07-T</t>
-  </si>
-  <si>
-    <t>WS-YB-01-T</t>
-  </si>
-  <si>
-    <t>WS-WG-02-T</t>
-  </si>
-  <si>
-    <t>WS-YB-03-T</t>
-  </si>
-  <si>
-    <t>WS-YB-05-T</t>
-  </si>
-  <si>
-    <t>SB-YB-05-T</t>
-  </si>
-  <si>
-    <t>杨嘉桥镇</t>
-  </si>
-  <si>
-    <t>YJ-WG-05-T</t>
-  </si>
-  <si>
-    <t>YJ-WG-01-T</t>
-  </si>
-  <si>
-    <t>YJ-WG-02-T</t>
-  </si>
-  <si>
-    <t>YJ-YB-03-T</t>
-  </si>
-  <si>
-    <t>YJ-WG-04-T</t>
-  </si>
-  <si>
-    <t>YJ-WG-06-T</t>
-  </si>
-  <si>
-    <t>YJ-WG-07-T</t>
-  </si>
-  <si>
-    <t>YJ-WG-09-T</t>
-  </si>
-  <si>
-    <t>YJ-WG-10-1</t>
-  </si>
-  <si>
-    <t>YJ-WG-11-T</t>
-  </si>
-  <si>
-    <t>YJ-WG-12-T</t>
-  </si>
-  <si>
-    <t>ML-WG-11-T</t>
-  </si>
-  <si>
-    <t>易俗河镇</t>
-  </si>
-  <si>
-    <t>YS-GK-01-T</t>
-  </si>
-  <si>
-    <t>YS-GK-02-T</t>
-  </si>
-  <si>
-    <t>YS-GK-03-T</t>
-  </si>
-  <si>
-    <t>YS-GK-04-T</t>
-  </si>
-  <si>
-    <t>YS-GK-05-T</t>
-  </si>
-  <si>
-    <t>YS-GK-06-T</t>
-  </si>
-  <si>
-    <t>YS-GK-07-T</t>
-  </si>
-  <si>
-    <t>YS-GK-08-T</t>
-  </si>
-  <si>
-    <t>YS-GK-10-T</t>
-  </si>
-  <si>
-    <t>YS-GK-11-T</t>
-  </si>
-  <si>
-    <t>YH-YB-01-T</t>
-  </si>
-  <si>
-    <t>云湖桥镇</t>
-  </si>
-  <si>
-    <t>YH-YB-02-T</t>
-  </si>
-  <si>
-    <t>YH-YB-03-T</t>
-  </si>
-  <si>
-    <t>YH-WG-04-T</t>
-  </si>
-  <si>
-    <t>YH-YB-05-T</t>
-  </si>
-  <si>
-    <t>YH-GK-06-T</t>
-  </si>
-  <si>
-    <t>YH-YB-07-T</t>
-  </si>
-  <si>
-    <t>YH-GK-08-T</t>
-  </si>
-  <si>
-    <t>ZL-YB-03-T</t>
-  </si>
-  <si>
-    <t>中路铺镇</t>
-  </si>
-  <si>
-    <t>ZL-GK-04-T</t>
-  </si>
-  <si>
-    <t>ZL-YB-05-T</t>
-  </si>
-  <si>
-    <t>ZL-YB-02-T</t>
-  </si>
-  <si>
-    <t>ZL-GK-06-T</t>
-  </si>
-  <si>
-    <t>ZL-YB-07-T</t>
-  </si>
-  <si>
-    <t>QH_NAME</t>
-  </si>
-  <si>
-    <t>平均值项:比值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -663,15 +664,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -716,12 +719,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1109,11 +1112,11 @@
       <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA1" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
@@ -1127,7 +1130,7 @@
         <v>27.471599999999999</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>10</v>
@@ -1196,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -1210,7 +1213,7 @@
         <v>27.450099999999999</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>12</v>
@@ -1279,7 +1282,7 @@
         <v>0.82</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -1293,7 +1296,7 @@
         <v>27.478300000000001</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3">
         <v>8.9</v>
@@ -1362,7 +1365,7 @@
         <v>0.01</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -1376,7 +1379,7 @@
         <v>27.4815</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3">
         <v>4.5</v>
@@ -1445,7 +1448,7 @@
         <v>0.47</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -1459,7 +1462,7 @@
         <v>27.477900000000002</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3">
         <v>16</v>
@@ -1528,7 +1531,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -1542,7 +1545,7 @@
         <v>27.409099999999999</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3">
         <v>16.5</v>
@@ -1611,7 +1614,7 @@
         <v>0.01</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -1625,7 +1628,7 @@
         <v>27.394528999999999</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" s="3">
         <v>8.3000000000000007</v>
@@ -1694,7 +1697,7 @@
         <v>0.39</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -1708,7 +1711,7 @@
         <v>27.394100000000002</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="3">
         <v>8.9</v>
@@ -1777,7 +1780,7 @@
         <v>0.45</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -1791,7 +1794,7 @@
         <v>27.383900000000001</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" s="3">
         <v>8.5</v>
@@ -1860,7 +1863,7 @@
         <v>0.53</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -1874,7 +1877,7 @@
         <v>27.420666000000001</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3">
         <v>5.3</v>
@@ -1943,7 +1946,7 @@
         <v>0.01</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -1957,7 +1960,7 @@
         <v>27.367321</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" s="3">
         <v>9.3000000000000007</v>
@@ -2026,7 +2029,7 @@
         <v>0.8</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -2040,7 +2043,7 @@
         <v>27.53566</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13" s="3">
         <v>12.1</v>
@@ -2109,7 +2112,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -2123,7 +2126,7 @@
         <v>27.532820000000001</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" s="3">
         <v>7.8</v>
@@ -2192,7 +2195,7 @@
         <v>0.49</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -2206,7 +2209,7 @@
         <v>27.547419999999999</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" s="3">
         <v>17.3</v>
@@ -2275,7 +2278,7 @@
         <v>0.24</v>
       </c>
       <c r="AA15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -2289,7 +2292,7 @@
         <v>27.558800000000002</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16" s="3">
         <v>23.2</v>
@@ -2358,7 +2361,7 @@
         <v>0.1</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -2372,7 +2375,7 @@
         <v>27.542899999999999</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" s="3">
         <v>16.2</v>
@@ -2441,7 +2444,7 @@
         <v>0.61</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -2455,7 +2458,7 @@
         <v>27.55293</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" s="3">
         <v>7.9</v>
@@ -2524,7 +2527,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -2538,7 +2541,7 @@
         <v>27.7728</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" s="3">
         <v>16.600000000000001</v>
@@ -2607,7 +2610,7 @@
         <v>0.91</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -2621,7 +2624,7 @@
         <v>27.706700000000001</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3">
         <v>7.6</v>
@@ -2690,7 +2693,7 @@
         <v>0.34</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -2704,7 +2707,7 @@
         <v>27.726800000000001</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E21" s="3">
         <v>12.7</v>
@@ -2773,7 +2776,7 @@
         <v>2</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -2787,7 +2790,7 @@
         <v>27.800225999999999</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E22" s="3">
         <v>16.2</v>
@@ -2856,7 +2859,7 @@
         <v>0.87</v>
       </c>
       <c r="AA22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -2870,7 +2873,7 @@
         <v>27.747900000000001</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" s="3">
         <v>8.9</v>
@@ -2939,7 +2942,7 @@
         <v>0.42</v>
       </c>
       <c r="AA23" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -2953,7 +2956,7 @@
         <v>27.710799999999999</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" s="3">
         <v>9.1</v>
@@ -3022,7 +3025,7 @@
         <v>0.97</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -3036,7 +3039,7 @@
         <v>27.751200000000001</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" s="3">
         <v>11.2</v>
@@ -3105,7 +3108,7 @@
         <v>0.32</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -3119,7 +3122,7 @@
         <v>27.761600000000001</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E26" s="3">
         <v>9.1</v>
@@ -3188,7 +3191,7 @@
         <v>0.87</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -3202,7 +3205,7 @@
         <v>27.761500000000002</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" s="3">
         <v>12</v>
@@ -3271,7 +3274,7 @@
         <v>0.35</v>
       </c>
       <c r="AA27" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -3285,7 +3288,7 @@
         <v>27.723800000000001</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" s="3">
         <v>179.9</v>
@@ -3354,7 +3357,7 @@
         <v>0.01</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -3368,7 +3371,7 @@
         <v>27.779399999999999</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" s="3">
         <v>7</v>
@@ -3437,7 +3440,7 @@
         <v>0.86</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -3451,7 +3454,7 @@
         <v>27.771999999999998</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" s="3">
         <v>4.7</v>
@@ -3520,7 +3523,7 @@
         <v>0.99</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -3534,7 +3537,7 @@
         <v>27.742799999999999</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" s="3">
         <v>5.3</v>
@@ -3603,7 +3606,7 @@
         <v>0.12</v>
       </c>
       <c r="AA31" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -3617,7 +3620,7 @@
         <v>27.717700000000001</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" s="3">
         <v>8.8000000000000007</v>
@@ -3686,7 +3689,7 @@
         <v>0.01</v>
       </c>
       <c r="AA32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -3700,7 +3703,7 @@
         <v>27.761299999999999</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E33" s="3">
         <v>37.9</v>
@@ -3769,7 +3772,7 @@
         <v>1.9</v>
       </c>
       <c r="AA33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -3783,7 +3786,7 @@
         <v>27.5489</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E34" s="3">
         <v>18.100000000000001</v>
@@ -3852,7 +3855,7 @@
         <v>0.95</v>
       </c>
       <c r="AA34" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -3866,7 +3869,7 @@
         <v>27.51146</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E35" s="3">
         <v>27.4</v>
@@ -3935,7 +3938,7 @@
         <v>0.71</v>
       </c>
       <c r="AA35" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -3949,7 +3952,7 @@
         <v>27.582609999999999</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E36" s="3">
         <v>17.3</v>
@@ -4018,7 +4021,7 @@
         <v>0.42</v>
       </c>
       <c r="AA36" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -4032,7 +4035,7 @@
         <v>27.4666</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E37" s="3">
         <v>5.3</v>
@@ -4101,7 +4104,7 @@
         <v>0.84</v>
       </c>
       <c r="AA37" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.2">
@@ -4115,7 +4118,7 @@
         <v>27.538129999999999</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E38" s="3">
         <v>4.0999999999999996</v>
@@ -4184,7 +4187,7 @@
         <v>1.8</v>
       </c>
       <c r="AA38" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.2">
@@ -4198,7 +4201,7 @@
         <v>27.527280000000001</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E39" s="3">
         <v>323.10000000000002</v>
@@ -4267,7 +4270,7 @@
         <v>0.01</v>
       </c>
       <c r="AA39" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.2">
@@ -4281,7 +4284,7 @@
         <v>27.522099999999998</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E40" s="3">
         <v>8.3000000000000007</v>
@@ -4350,7 +4353,7 @@
         <v>0.41</v>
       </c>
       <c r="AA40" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.2">
@@ -4364,7 +4367,7 @@
         <v>27.638750000000002</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E41" s="3">
         <v>18.100000000000001</v>
@@ -4433,7 +4436,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="AA41" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.2">
@@ -4447,7 +4450,7 @@
         <v>27.58484</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E42" s="3">
         <v>10.4</v>
@@ -4516,7 +4519,7 @@
         <v>0.01</v>
       </c>
       <c r="AA42" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.2">
@@ -4530,7 +4533,7 @@
         <v>27.64142</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E43" s="3">
         <v>20</v>
@@ -4599,7 +4602,7 @@
         <v>0.25</v>
       </c>
       <c r="AA43" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
@@ -4613,7 +4616,7 @@
         <v>27.602309999999999</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E44" s="3">
         <v>160.5</v>
@@ -4682,7 +4685,7 @@
         <v>0.01</v>
       </c>
       <c r="AA44" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.2">
@@ -4696,7 +4699,7 @@
         <v>27.607589999999998</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E45" s="3">
         <v>15.9</v>
@@ -4765,7 +4768,7 @@
         <v>0.31</v>
       </c>
       <c r="AA45" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.2">
@@ -4779,7 +4782,7 @@
         <v>27.475580000000001</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E46" s="3">
         <v>19.600000000000001</v>
@@ -4848,7 +4851,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="AA46" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.2">
@@ -4862,7 +4865,7 @@
         <v>27.480630000000001</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E47" s="3">
         <v>10.6</v>
@@ -4931,7 +4934,7 @@
         <v>0.2</v>
       </c>
       <c r="AA47" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.2">
@@ -4945,7 +4948,7 @@
         <v>27.46528</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E48" s="3">
         <v>14.6</v>
@@ -5014,7 +5017,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="AA48" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.2">
@@ -5028,7 +5031,7 @@
         <v>27.460550000000001</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E49" s="3">
         <v>6.8</v>
@@ -5097,7 +5100,7 @@
         <v>0.3</v>
       </c>
       <c r="AA49" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.2">
@@ -5111,7 +5114,7 @@
         <v>27.423909999999999</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E50" s="3">
         <v>13.9</v>
@@ -5180,7 +5183,7 @@
         <v>0.23</v>
       </c>
       <c r="AA50" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.2">
@@ -5194,7 +5197,7 @@
         <v>27.437180000000001</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E51" s="3">
         <v>16</v>
@@ -5263,7 +5266,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="AA51" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.2">
@@ -5277,7 +5280,7 @@
         <v>27.420549999999999</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E52" s="3">
         <v>28.4</v>
@@ -5346,7 +5349,7 @@
         <v>0.01</v>
       </c>
       <c r="AA52" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.2">
@@ -5360,7 +5363,7 @@
         <v>27.7148</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E53" s="3">
         <v>20.7</v>
@@ -5429,7 +5432,7 @@
         <v>0.35</v>
       </c>
       <c r="AA53" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.2">
@@ -5443,7 +5446,7 @@
         <v>27.71932</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E54" s="3">
         <v>13.1</v>
@@ -5512,7 +5515,7 @@
         <v>0.15</v>
       </c>
       <c r="AA54" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.2">
@@ -5526,7 +5529,7 @@
         <v>27.706379999999999</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E55" s="3">
         <v>10</v>
@@ -5595,7 +5598,7 @@
         <v>0.51</v>
       </c>
       <c r="AA55" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.2">
@@ -5609,7 +5612,7 @@
         <v>27.728829999999999</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E56" s="3">
         <v>9.3000000000000007</v>
@@ -5678,7 +5681,7 @@
         <v>1.4</v>
       </c>
       <c r="AA56" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.2">
@@ -5692,7 +5695,7 @@
         <v>27.708359999999999</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E57" s="3">
         <v>29.5</v>
@@ -5761,7 +5764,7 @@
         <v>0.32</v>
       </c>
       <c r="AA57" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.2">
@@ -5775,7 +5778,7 @@
         <v>27.756139999999998</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E58" s="3">
         <v>18.100000000000001</v>
@@ -5844,7 +5847,7 @@
         <v>1.8</v>
       </c>
       <c r="AA58" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.2">
@@ -5858,7 +5861,7 @@
         <v>27.709230000000002</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E59" s="3">
         <v>137.1</v>
@@ -5927,7 +5930,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AA59" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.2">
@@ -5941,7 +5944,7 @@
         <v>27.735700000000001</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E60" s="3">
         <v>6.2</v>
@@ -6010,7 +6013,7 @@
         <v>0.54</v>
       </c>
       <c r="AA60" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.2">
@@ -6024,7 +6027,7 @@
         <v>27.699470000000002</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E61" s="3">
         <v>9.9</v>
@@ -6093,7 +6096,7 @@
         <v>0.37</v>
       </c>
       <c r="AA61" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.2">
@@ -6107,7 +6110,7 @@
         <v>27.686779999999999</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E62" s="3">
         <v>9.3000000000000007</v>
@@ -6176,7 +6179,7 @@
         <v>1.3</v>
       </c>
       <c r="AA62" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.2">
@@ -6190,7 +6193,7 @@
         <v>27.69547</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E63" s="3">
         <v>17.899999999999999</v>
@@ -6259,7 +6262,7 @@
         <v>0.27</v>
       </c>
       <c r="AA63" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.2">
@@ -6273,7 +6276,7 @@
         <v>27.511279999999999</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E64" s="3">
         <v>4.7</v>
@@ -6342,7 +6345,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AA64" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.2">
@@ -6356,7 +6359,7 @@
         <v>27.54851</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E65" s="3">
         <v>31.6</v>
@@ -6425,7 +6428,7 @@
         <v>0.95</v>
       </c>
       <c r="AA65" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.2">
@@ -6439,7 +6442,7 @@
         <v>27.600460000000002</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E66" s="3">
         <v>21.3</v>
@@ -6508,7 +6511,7 @@
         <v>0.24</v>
       </c>
       <c r="AA66" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.2">
@@ -6522,7 +6525,7 @@
         <v>27.52769</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E67" s="3">
         <v>27.4</v>
@@ -6591,7 +6594,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="AA67" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.2">
@@ -6605,7 +6608,7 @@
         <v>27.582370000000001</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E68" s="3">
         <v>21.3</v>
@@ -6674,7 +6677,7 @@
         <v>0.31</v>
       </c>
       <c r="AA68" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.2">
@@ -6688,7 +6691,7 @@
         <v>27.60717</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E69" s="3">
         <v>15.2</v>
@@ -6757,7 +6760,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="AA69" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.2">
@@ -6771,7 +6774,7 @@
         <v>27.579599999999999</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E70" s="3">
         <v>19.2</v>
@@ -6840,7 +6843,7 @@
         <v>0.36</v>
       </c>
       <c r="AA70" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.2">
@@ -6854,7 +6857,7 @@
         <v>27.503087300000001</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E71" s="3">
         <v>191.8</v>
@@ -6923,7 +6926,7 @@
         <v>0.01</v>
       </c>
       <c r="AA71" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.2">
@@ -6937,7 +6940,7 @@
         <v>27.490680000000001</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E72" s="3">
         <v>9.6999999999999993</v>
@@ -7006,7 +7009,7 @@
         <v>0.2</v>
       </c>
       <c r="AA72" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.2">
@@ -7020,7 +7023,7 @@
         <v>27.47757</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E73" s="3">
         <v>5.4</v>
@@ -7089,7 +7092,7 @@
         <v>0.22</v>
       </c>
       <c r="AA73" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.2">
@@ -7103,7 +7106,7 @@
         <v>27.468779999999999</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E74" s="3">
         <v>17.3</v>
@@ -7172,7 +7175,7 @@
         <v>0.01</v>
       </c>
       <c r="AA74" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.2">
@@ -7186,7 +7189,7 @@
         <v>27.499079999999999</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E75" s="3">
         <v>21.9</v>
@@ -7255,7 +7258,7 @@
         <v>0.26</v>
       </c>
       <c r="AA75" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.2">
@@ -7269,7 +7272,7 @@
         <v>27.488800000000001</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E76" s="3">
         <v>14.8</v>
@@ -7338,7 +7341,7 @@
         <v>0.31</v>
       </c>
       <c r="AA76" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.2">
@@ -7352,7 +7355,7 @@
         <v>27.442720000000001</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E77" s="3">
         <v>6</v>
@@ -7421,7 +7424,7 @@
         <v>0.47</v>
       </c>
       <c r="AA77" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.2">
@@ -7435,7 +7438,7 @@
         <v>27.612639999999999</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E78" s="3">
         <v>16.5</v>
@@ -7504,7 +7507,7 @@
         <v>0.15</v>
       </c>
       <c r="AA78" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.2">
@@ -7518,7 +7521,7 @@
         <v>27.678719999999998</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E79" s="3">
         <v>21.7</v>
@@ -7587,7 +7590,7 @@
         <v>0.3</v>
       </c>
       <c r="AA79" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:27" x14ac:dyDescent="0.2">
@@ -7601,7 +7604,7 @@
         <v>27.624919999999999</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E80" s="3">
         <v>12</v>
@@ -7670,7 +7673,7 @@
         <v>0.73</v>
       </c>
       <c r="AA80" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:27" x14ac:dyDescent="0.2">
@@ -7684,7 +7687,7 @@
         <v>27.63044</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E81" s="3">
         <v>5.0999999999999996</v>
@@ -7753,7 +7756,7 @@
         <v>0.66</v>
       </c>
       <c r="AA81" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:27" x14ac:dyDescent="0.2">
@@ -7767,7 +7770,7 @@
         <v>27.682759999999998</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E82" s="3">
         <v>15.2</v>
@@ -7836,7 +7839,7 @@
         <v>0.19</v>
       </c>
       <c r="AA82" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.2">
@@ -7850,7 +7853,7 @@
         <v>27.676839999999999</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E83" s="3">
         <v>55.8</v>
@@ -7919,7 +7922,7 @@
         <v>0.01</v>
       </c>
       <c r="AA83" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:27" x14ac:dyDescent="0.2">
@@ -7933,7 +7936,7 @@
         <v>27.612919999999999</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E84" s="3">
         <v>9.1</v>
@@ -8002,7 +8005,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="AA84" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.2">
@@ -8016,7 +8019,7 @@
         <v>27.625229999999998</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E85" s="3">
         <v>10</v>
@@ -8085,7 +8088,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="AA85" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.2">
@@ -8099,7 +8102,7 @@
         <v>27.646999999999998</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E86" s="3">
         <v>24</v>
@@ -8167,8 +8170,8 @@
       <c r="Z86" s="1">
         <v>0.54</v>
       </c>
-      <c r="AA86" s="6" t="s">
-        <v>114</v>
+      <c r="AA86" s="5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.2">
@@ -8182,7 +8185,7 @@
         <v>27.50177</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E87" s="3">
         <v>11.8</v>
@@ -8251,7 +8254,7 @@
         <v>1.5</v>
       </c>
       <c r="AA87" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.2">
@@ -8265,7 +8268,7 @@
         <v>27.496749999999999</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E88" s="3">
         <v>62.3</v>
@@ -8334,7 +8337,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="AA88" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.2">
@@ -8348,7 +8351,7 @@
         <v>27.50346</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E89" s="3">
         <v>62.9</v>
@@ -8417,7 +8420,7 @@
         <v>0.01</v>
       </c>
       <c r="AA89" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.2">
@@ -8431,7 +8434,7 @@
         <v>27.498539999999998</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E90" s="3">
         <v>12.5</v>
@@ -8500,7 +8503,7 @@
         <v>0.96</v>
       </c>
       <c r="AA90" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.2">
@@ -8514,7 +8517,7 @@
         <v>27.492850000000001</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E91" s="3">
         <v>11.6</v>
@@ -8583,7 +8586,7 @@
         <v>0.2</v>
       </c>
       <c r="AA91" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.2">
@@ -8597,7 +8600,7 @@
         <v>27.529800000000002</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E92" s="3">
         <v>9.6999999999999993</v>
@@ -8666,7 +8669,7 @@
         <v>0.54</v>
       </c>
       <c r="AA92" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.2">
@@ -8680,7 +8683,7 @@
         <v>27.52854</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E93" s="3">
         <v>19</v>
@@ -8749,7 +8752,7 @@
         <v>0.35</v>
       </c>
       <c r="AA93" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.2">
@@ -8763,7 +8766,7 @@
         <v>27.767199999999999</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E94" s="3">
         <v>6.2</v>
@@ -8832,7 +8835,7 @@
         <v>0.5</v>
       </c>
       <c r="AA94" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.2">
@@ -8846,7 +8849,7 @@
         <v>27.797699999999999</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E95" s="3">
         <v>40.4</v>
@@ -8915,7 +8918,7 @@
         <v>0.39</v>
       </c>
       <c r="AA95" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.2">
@@ -8929,7 +8932,7 @@
         <v>27.741700000000002</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E96" s="3">
         <v>330.8</v>
@@ -8998,7 +9001,7 @@
         <v>0.01</v>
       </c>
       <c r="AA96" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.2">
@@ -9012,7 +9015,7 @@
         <v>27.805499999999999</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E97" s="3">
         <v>7</v>
@@ -9081,7 +9084,7 @@
         <v>0.71</v>
       </c>
       <c r="AA97" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.2">
@@ -9095,7 +9098,7 @@
         <v>27.7744</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E98" s="3">
         <v>4.7</v>
@@ -9164,7 +9167,7 @@
         <v>0.25</v>
       </c>
       <c r="AA98" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.2">
@@ -9178,7 +9181,7 @@
         <v>27.626280000000001</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E99" s="3">
         <v>12.3</v>
@@ -9247,7 +9250,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="AA99" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.2">
@@ -9261,7 +9264,7 @@
         <v>27.61148</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E100" s="3">
         <v>16.7</v>
@@ -9330,7 +9333,7 @@
         <v>0.65</v>
       </c>
       <c r="AA100" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.2">
@@ -9344,7 +9347,7 @@
         <v>27.646270000000001</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E101" s="3">
         <v>14.4</v>
@@ -9413,7 +9416,7 @@
         <v>0.2</v>
       </c>
       <c r="AA101" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.2">
@@ -9427,7 +9430,7 @@
         <v>27.663360000000001</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E102" s="3">
         <v>19.2</v>
@@ -9496,7 +9499,7 @@
         <v>1.7</v>
       </c>
       <c r="AA102" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.2">
@@ -9510,7 +9513,7 @@
         <v>27.627320000000001</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E103" s="3">
         <v>51.6</v>
@@ -9579,7 +9582,7 @@
         <v>0.17</v>
       </c>
       <c r="AA103" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.2">
@@ -9593,7 +9596,7 @@
         <v>27.61121</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E104" s="3">
         <v>11.2</v>
@@ -9662,7 +9665,7 @@
         <v>0.38</v>
       </c>
       <c r="AA104" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.2">
@@ -9676,7 +9679,7 @@
         <v>27.6568</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E105" s="3">
         <v>10.199999999999999</v>
@@ -9745,7 +9748,7 @@
         <v>0.42</v>
       </c>
       <c r="AA105" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" spans="1:27" x14ac:dyDescent="0.2">
@@ -9759,7 +9762,7 @@
         <v>27.700199999999999</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E106" s="3">
         <v>13.9</v>
@@ -9828,7 +9831,7 @@
         <v>0.25</v>
       </c>
       <c r="AA106" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="107" spans="1:27" x14ac:dyDescent="0.2">
@@ -9842,7 +9845,7 @@
         <v>27.71</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E107" s="3">
         <v>13.7</v>
@@ -9911,7 +9914,7 @@
         <v>0.21</v>
       </c>
       <c r="AA107" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.2">
@@ -9925,7 +9928,7 @@
         <v>27.643619999999999</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E108" s="3">
         <v>20</v>
@@ -9994,7 +9997,7 @@
         <v>0.52</v>
       </c>
       <c r="AA108" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="109" spans="1:27" x14ac:dyDescent="0.2">
@@ -10008,7 +10011,7 @@
         <v>27.672499999999999</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E109" s="3">
         <v>24</v>
@@ -10077,7 +10080,7 @@
         <v>0.87</v>
       </c>
       <c r="AA109" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="110" spans="1:27" x14ac:dyDescent="0.2">
@@ -10091,7 +10094,7 @@
         <v>27.6952</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E110" s="3">
         <v>11.4</v>
@@ -10160,7 +10163,7 @@
         <v>0.71</v>
       </c>
       <c r="AA110" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="111" spans="1:27" x14ac:dyDescent="0.2">
@@ -10174,7 +10177,7 @@
         <v>27.674399999999999</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E111" s="3">
         <v>143.80000000000001</v>
@@ -10243,7 +10246,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="AA111" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.2">
@@ -10257,7 +10260,7 @@
         <v>27.6479</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E112" s="3">
         <v>11.5</v>
@@ -10326,7 +10329,7 @@
         <v>0.35</v>
       </c>
       <c r="AA112" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="113" spans="1:27" x14ac:dyDescent="0.2">
@@ -10340,7 +10343,7 @@
         <v>27.816189999999999</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E113" s="3">
         <v>18.8</v>
@@ -10409,7 +10412,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="AA113" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="114" spans="1:27" x14ac:dyDescent="0.2">
@@ -10423,7 +10426,7 @@
         <v>27.781428999999999</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E114" s="3">
         <v>22.3</v>
@@ -10492,7 +10495,7 @@
         <v>0.24</v>
       </c>
       <c r="AA114" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="115" spans="1:27" x14ac:dyDescent="0.2">
@@ -10506,7 +10509,7 @@
         <v>27.808700000000002</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E115" s="3">
         <v>7.6</v>
@@ -10575,7 +10578,7 @@
         <v>0.82</v>
       </c>
       <c r="AA115" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.2">
@@ -10589,7 +10592,7 @@
         <v>27.797899999999998</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E116" s="3">
         <v>15.8</v>
@@ -10658,7 +10661,7 @@
         <v>0.82</v>
       </c>
       <c r="AA116" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="117" spans="1:27" x14ac:dyDescent="0.2">
@@ -10672,7 +10675,7 @@
         <v>27.8262</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E117" s="3">
         <v>14.8</v>
@@ -10741,7 +10744,7 @@
         <v>0.96</v>
       </c>
       <c r="AA117" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.2">
@@ -10755,7 +10758,7 @@
         <v>27.7913</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E118" s="3">
         <v>25.7</v>
@@ -10824,7 +10827,7 @@
         <v>0.01</v>
       </c>
       <c r="AA118" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.2">
@@ -10838,7 +10841,7 @@
         <v>27.8081</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E119" s="3">
         <v>7</v>
@@ -10907,7 +10910,7 @@
         <v>0.39</v>
       </c>
       <c r="AA119" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:27" x14ac:dyDescent="0.2">
@@ -10921,7 +10924,7 @@
         <v>27.762899999999998</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E120" s="3">
         <v>46.7</v>
@@ -10990,7 +10993,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="AA120" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="121" spans="1:27" x14ac:dyDescent="0.2">
@@ -11004,7 +11007,7 @@
         <v>27.7761</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E121" s="3">
         <v>19.100000000000001</v>
@@ -11073,7 +11076,7 @@
         <v>0.01</v>
       </c>
       <c r="AA121" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="122" spans="1:27" x14ac:dyDescent="0.2">
@@ -11087,7 +11090,7 @@
         <v>27.8156</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E122" s="3">
         <v>6.6</v>
@@ -11156,7 +11159,7 @@
         <v>0.52</v>
       </c>
       <c r="AA122" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="123" spans="1:27" x14ac:dyDescent="0.2">
@@ -11170,7 +11173,7 @@
         <v>27.7928</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E123" s="3">
         <v>8.1</v>
@@ -11239,7 +11242,7 @@
         <v>0.22</v>
       </c>
       <c r="AA123" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.2">
@@ -11253,7 +11256,7 @@
         <v>27.763204999999999</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E124" s="3">
         <v>8.9</v>
@@ -11322,7 +11325,7 @@
         <v>1.7</v>
       </c>
       <c r="AA124" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.2">
@@ -11336,7 +11339,7 @@
         <v>27.73441</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E125" s="3">
         <v>3.2</v>
@@ -11405,7 +11408,7 @@
         <v>0.45</v>
       </c>
       <c r="AA125" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="126" spans="1:27" x14ac:dyDescent="0.2">
@@ -11419,7 +11422,7 @@
         <v>27.7774</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E126" s="3">
         <v>20.7</v>
@@ -11488,7 +11491,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="AA126" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="127" spans="1:27" x14ac:dyDescent="0.2">
@@ -11502,7 +11505,7 @@
         <v>27.784600000000001</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E127" s="3">
         <v>21.9</v>
@@ -11571,7 +11574,7 @@
         <v>0.83</v>
       </c>
       <c r="AA127" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="128" spans="1:27" x14ac:dyDescent="0.2">
@@ -11585,7 +11588,7 @@
         <v>27.757000000000001</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E128" s="3">
         <v>8.5</v>
@@ -11654,7 +11657,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="AA128" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="129" spans="1:27" x14ac:dyDescent="0.2">
@@ -11668,7 +11671,7 @@
         <v>27.752800000000001</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E129" s="3">
         <v>8.1</v>
@@ -11737,7 +11740,7 @@
         <v>0.62</v>
       </c>
       <c r="AA129" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="130" spans="1:27" x14ac:dyDescent="0.2">
@@ -11751,7 +11754,7 @@
         <v>27.759699999999999</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E130" s="3">
         <v>37.9</v>
@@ -11820,7 +11823,7 @@
         <v>1</v>
       </c>
       <c r="AA130" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="131" spans="1:27" x14ac:dyDescent="0.2">
@@ -11834,7 +11837,7 @@
         <v>27.792000000000002</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E131" s="3">
         <v>3.9</v>
@@ -11903,7 +11906,7 @@
         <v>0.35</v>
       </c>
       <c r="AA131" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="132" spans="1:27" x14ac:dyDescent="0.2">
@@ -11917,7 +11920,7 @@
         <v>27.773399999999999</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E132" s="3">
         <v>16.899999999999999</v>
@@ -11986,7 +11989,7 @@
         <v>1.2</v>
       </c>
       <c r="AA132" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="133" spans="1:27" x14ac:dyDescent="0.2">
@@ -12000,7 +12003,7 @@
         <v>27.7621</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E133" s="3">
         <v>12.5</v>
@@ -12069,7 +12072,7 @@
         <v>2.9</v>
       </c>
       <c r="AA133" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="134" spans="1:27" x14ac:dyDescent="0.2">
@@ -12083,7 +12086,7 @@
         <v>27.767800000000001</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E134" s="3">
         <v>15</v>
@@ -12152,7 +12155,7 @@
         <v>1.3</v>
       </c>
       <c r="AA134" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="135" spans="1:27" x14ac:dyDescent="0.2">
@@ -12166,7 +12169,7 @@
         <v>27.777000000000001</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E135" s="3">
         <v>26.1</v>
@@ -12235,7 +12238,7 @@
         <v>0.01</v>
       </c>
       <c r="AA135" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="136" spans="1:27" x14ac:dyDescent="0.2">
@@ -12249,7 +12252,7 @@
         <v>27.89</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E136" s="3">
         <v>189.2</v>
@@ -12318,7 +12321,7 @@
         <v>0.23</v>
       </c>
       <c r="AA136" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="137" spans="1:27" x14ac:dyDescent="0.2">
@@ -12332,7 +12335,7 @@
         <v>27.835750000000001</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E137" s="3">
         <v>7.2</v>
@@ -12401,7 +12404,7 @@
         <v>0.32</v>
       </c>
       <c r="AA137" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="138" spans="1:27" x14ac:dyDescent="0.2">
@@ -12415,7 +12418,7 @@
         <v>27.92041</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E138" s="3">
         <v>4.9000000000000004</v>
@@ -12484,7 +12487,7 @@
         <v>0.32</v>
       </c>
       <c r="AA138" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="139" spans="1:27" x14ac:dyDescent="0.2">
@@ -12498,7 +12501,7 @@
         <v>27.833189999999998</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E139" s="3">
         <v>11.4</v>
@@ -12567,7 +12570,7 @@
         <v>0.01</v>
       </c>
       <c r="AA139" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="140" spans="1:27" x14ac:dyDescent="0.2">
@@ -12581,7 +12584,7 @@
         <v>27.854852999999999</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E140" s="3">
         <v>6.8</v>
@@ -12650,7 +12653,7 @@
         <v>0.17</v>
       </c>
       <c r="AA140" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="141" spans="1:27" x14ac:dyDescent="0.2">
@@ -12664,7 +12667,7 @@
         <v>27.862179999999999</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E141" s="3">
         <v>7.1</v>
@@ -12733,7 +12736,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="AA141" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="142" spans="1:27" x14ac:dyDescent="0.2">
@@ -12747,7 +12750,7 @@
         <v>27.835419999999999</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E142" s="3">
         <v>6.8</v>
@@ -12816,7 +12819,7 @@
         <v>0.27</v>
       </c>
       <c r="AA142" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="143" spans="1:27" x14ac:dyDescent="0.2">
@@ -12830,7 +12833,7 @@
         <v>27.82254</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E143" s="3">
         <v>12.7</v>
@@ -12899,7 +12902,7 @@
         <v>0.82</v>
       </c>
       <c r="AA143" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="144" spans="1:27" x14ac:dyDescent="0.2">
@@ -12913,7 +12916,7 @@
         <v>27.5366</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E144" s="3">
         <v>10.8</v>
@@ -12982,7 +12985,7 @@
         <v>0.33</v>
       </c>
       <c r="AA144" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="145" spans="1:27" x14ac:dyDescent="0.2">
@@ -12996,7 +12999,7 @@
         <v>27.545059999999999</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E145" s="3">
         <v>11.8</v>
@@ -13065,7 +13068,7 @@
         <v>0.98</v>
       </c>
       <c r="AA145" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="146" spans="1:27" x14ac:dyDescent="0.2">
@@ -13079,7 +13082,7 @@
         <v>27.510570000000001</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E146" s="3">
         <v>256.3</v>
@@ -13148,7 +13151,7 @@
         <v>0.01</v>
       </c>
       <c r="AA146" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="147" spans="1:27" x14ac:dyDescent="0.2">
@@ -13162,7 +13165,7 @@
         <v>27.57</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E147" s="3">
         <v>24.2</v>
@@ -13231,7 +13234,7 @@
         <v>0.37</v>
       </c>
       <c r="AA147" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="148" spans="1:27" x14ac:dyDescent="0.2">
@@ -13245,7 +13248,7 @@
         <v>27.54054</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E148" s="3">
         <v>13.7</v>
@@ -13314,7 +13317,7 @@
         <v>0.3</v>
       </c>
       <c r="AA148" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="149" spans="1:27" x14ac:dyDescent="0.2">
@@ -13328,7 +13331,7 @@
         <v>27.577400000000001</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E149" s="3">
         <v>29.9</v>
@@ -13397,17 +13400,17 @@
         <v>0.3</v>
       </c>
       <c r="AA149" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="AA150" s="7"/>
+      <c r="AA150" s="6"/>
     </row>
     <row r="151" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="AA151" s="7"/>
+      <c r="AA151" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -13423,15 +13426,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" t="s">
         <v>194</v>
-      </c>
-      <c r="B1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>0.81451482984534895</v>
@@ -13439,7 +13442,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>0.699967736725992</v>
@@ -13447,7 +13450,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>0.84535942565885702</v>
@@ -13455,7 +13458,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5">
         <v>0.73766377618956402</v>
@@ -13463,7 +13466,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0.79277569098521805</v>
@@ -13471,7 +13474,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7">
         <v>0.73583918682055005</v>
@@ -13479,7 +13482,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8">
         <v>0.79737776544526096</v>
@@ -13487,7 +13490,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9">
         <v>0.76738790291621295</v>
@@ -13495,7 +13498,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10">
         <v>0.76097071184708598</v>
@@ -13503,7 +13506,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11">
         <v>0.73450985994595597</v>
@@ -13511,7 +13514,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12">
         <v>0.77948882027306998</v>
@@ -13519,7 +13522,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B13">
         <v>0.73516539106105006</v>
@@ -13527,7 +13530,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B14">
         <v>0.70494335089993299</v>
@@ -13535,7 +13538,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B15">
         <v>0.79699806697048503</v>
@@ -13543,7 +13546,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B16">
         <v>0.751553173832477</v>
@@ -13551,7 +13554,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17">
         <v>0.68185872217921395</v>
@@ -13559,7 +13562,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B18">
         <v>0.77053322913880795</v>
@@ -13567,7 +13570,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B19">
         <v>0.76117476717384003</v>
@@ -13575,7 +13578,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B20">
         <v>0.75798981554681299</v>
@@ -13585,7 +13588,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B20">
     <sortCondition ref="A2"/>
   </sortState>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
